--- a/IITA climate publications - COMPLETE.xlsx
+++ b/IITA climate publications - COMPLETE.xlsx
@@ -5197,13 +5197,13 @@
 Highlights need for more robust data, better regional climate models, and expanded research on neglected crops and farming systems.</v>
       </c>
       <c r="T53" t="str">
-        <v/>
+        <v>10.1088/1748-9326/ac61c8</v>
       </c>
       <c r="U53" t="str">
-        <v/>
+        <v>Agriculture in West Africa faces the challenge of meeting the rising demand for food as national incomes and populations increase while production becomes more uncertain due to climate change. Adaptation strategies (such as optimised planting dates, use of fertilisers and climate-resilient crop varieties) to mitigate the effects of climate change on crop yields. We systematically searched two databases for literature published between 2005 and 2020 and identified 35 relevant studies. We analysed yield changes of major staple crops (maize, sorghum, rice, millet, yam, cassava and groundnuts) caused by different climate change and field management scenarios. Yields declined by a median of 6% (−8% to +2% depending on the crop) due to climate change in all scenarios analysed. We show that the common adaptation strategies could increase crop yields affected by climate change by 13% (−4% to +19% depending on the strategy) as compared to business-as-usual field management practices.</v>
       </c>
       <c r="V53" t="str">
-        <v/>
+        <v>Climate change, West Africa, adaptation strategies, crop yields, systematic review</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -5289,13 +5289,13 @@
 Paper highlights how informal institutions can be key entry points for climate adaptation planning in forest-dependent regions.</v>
       </c>
       <c r="T54" t="str">
-        <v/>
+        <v>10.1080/17565529.2017.1291409</v>
       </c>
       <c r="U54" t="str">
-        <v/>
+        <v>Surveys of 232 people from 13 villages, in three regions of Cameroon, provided insight about the role that internal village institutions can play in fostering community resilience. Almost all villagers, both men and women, are members of at least one group and the membership of these groups is very diverse in terms of family relations, gender, occupation, age, and level of education. While the groups were not currently working together to respond to climate change, the diverse social networks that villagers have in these groups have already fostered exchange of knowledge. Their existence in villages provides opportunities for developing and sharing of knowledge that can be important for climate change adaptation in the future. Community resilience could be better fostered through a deliberate action-reflection process that includes both men and women, and builds on the social capital present in communities.</v>
       </c>
       <c r="V54" t="str">
-        <v/>
+        <v>Climate change, community resilience, village institutions, social capital, Cameroon</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -5385,13 +5385,13 @@
 Demonstrates the usefulness of bioeconomic agent-based models in climate and food security policy design.</v>
       </c>
       <c r="T55" t="str">
-        <v/>
+        <v>10.1111/agec.12358</v>
       </c>
       <c r="U55" t="str">
-        <v/>
+        <v>Climate variability with unexpected droughts and floods causes serious production losses and worsens food security, especially in Sub-Saharan Africa. This study applies stochastic bioeconomic modeling to analyze smallholder adaptation to climate and price variability in Ethiopia. It uses the agent-based simulation package Mathematical Programming-based Multi-Agent Systems (MPMAS) to capture nonseparable production and consumption decisions at household level, considering livestock and eucalyptus sales for consumption smoothing. The study found the promotion of new maize and wheat varieties to be an effective adaptation option, on average, especially when accompanied by policy interventions such as credit and fertilizer subsidy. The effectiveness of available adaptation options is quite different across the heterogeneous smallholder population in Ethiopia. This implies that policy assessments based on average farm households may mislead policy makers to adhere to interventions that are beneficial on average albeit ineffective in addressing the particular needs of poor and food insecure farmers.</v>
       </c>
       <c r="V55" t="str">
-        <v/>
+        <v>Climate adaptation, agent-based modeling, Ethiopia, smallholder farmers, policy interventions</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
@@ -5469,13 +5469,13 @@
 Supports the use of molecular phylogeography in conservation and disease vector management strategies in Sub-Saharan Africa.</v>
       </c>
       <c r="T56" t="str">
-        <v/>
+        <v>10.1002/ece3.3668</v>
       </c>
       <c r="U56" t="str">
-        <v/>
+        <v>The primary aim was to determine whether historical climate change has impacted the evolutionary history of African Aedes mosquitoes. The study used a comparative phylogeographic approach to investigate the population histories of four species of Aedes (Stegomyia) mosquitoes. Inference of the demographic history of Ae. aegypti within Africa from nuclear sequence data revealed that this could have been influenced by past climatic change with historical divergence and admixture dated to the late Pleistocene and early Holocene, consistent with demography being shaped by historical changes in forest distribution.</v>
       </c>
       <c r="V56" t="str">
-        <v/>
+        <v>Aedes mosquitoes, phylogeography, climate change, Africa, evolution</v>
       </c>
     </row>
     <row r="57" xml:space="preserve">
@@ -5561,13 +5561,13 @@
 Funded by the Royal Norwegian Embassy in Mali; conducted in collaboration with IITA and national partners.</v>
       </c>
       <c r="T57" t="str">
-        <v/>
+        <v>10.3390/agriculture12111853</v>
       </c>
       <c r="U57" t="str">
-        <v/>
+        <v>Climate change is negatively affecting agricultural production in the Sahel region. Climate-Smart Agricultural Technologies (CSATs) are disseminated to reduce these negative effects, and particularly those on resource-poor farm households. This article investigates the distributional impacts of the adoption of CSAT on-farm households' welfare using a dataset that covers four regions, 32 communes, 320 villages, and 2240 households in Mali. Using an instrumental variable quantile treatment effects model, the paper addresses the potential endogeneity arising from the selection bias and the heterogeneity of the effect across the quantiles of the outcome variables' distribution. The results show that the adoption of CSAT is positively associated with improved households' welfare.</v>
       </c>
       <c r="V57" t="str">
-        <v/>
+        <v>Climate-smart agriculture, Mali, household welfare, adoption, technology</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -5643,13 +5643,13 @@
         <v>Robust use of GYGA datasets and local agronomist input; results support cultivar-focused adaptation as a policy strategy. Study was part of CGIAR Excellence in Agronomy and Climate Resilience initiatives.</v>
       </c>
       <c r="T58" t="str">
-        <v/>
+        <v>10.1016/j.eja.2024.127137</v>
       </c>
       <c r="U58" t="str">
-        <v/>
+        <v>Sub-Saharan Africa's (SSA) demand for cereals is projected to more than double by 2050. Climate change is generally assumed to add to the future challenges of the needed productivity increase. This study aimed to assess (i) the potential climate change impact on four key rainfed cereals (maize, millet, sorghum and wheat) in ten SSA countries namely Burkina Faso, Ghana, Mali, Niger, Nigeria, Ethiopia, Kenya, Tanzania, Uganda, and Zambia using local data and national expertise, and (ii) the potential of cultivar adaptation to climate change for the four crops. The researchers assessed effects on rainfed potential cereal yields per crop and aggregated these to regional level in West (WA), East and Southern Africa (ESA), using a rigorous agronomic dataset for 120 locations in the ten countries with simulations using bias-corrected climate data from five GCMs, three time periods and two scenarios. Key findings show that by 2050, climate change impact on rainfed potential yields was insignificant in West and modest in East and Southern Africa, while by 2090, average impacts were much higher in West than in East and Southern Africa.</v>
       </c>
       <c r="V58" t="str">
-        <v/>
+        <v>Climate change, cereal crops, sub-Saharan Africa, rainfed agriculture, adaptation</v>
       </c>
     </row>
     <row r="59" xml:space="preserve">
@@ -5723,13 +5723,13 @@
         <v>Research funded by IITA and part of CGIAR programs on Climate Change, Agriculture and Food Security (CCAFS) and Cocoa Soils. Supports integration of cocoa agroforestry into carbon credit schemes.</v>
       </c>
       <c r="T59" t="str">
-        <v/>
+        <v>10.22302/ICCRI.JUR.PELITAPERKEBUNAN.V37I1.395</v>
       </c>
       <c r="U59" t="str">
-        <v/>
+        <v>Shade grown cocoa systems have been credited with stocking high quantities of carbon and therefore possess the potential to mitigate climate change and help achieve targets of the United Nations Collaborative Program on Reduced Emissions from Deforestation and Forest Degradation (REDD+). This study quantifies and compares carbon stored as well as estimated cocoa yields in two shade management types (i.e., shaded and full sun) across three agroecological zones: Dry Semi-Deciduous Fire Zone (DSFZ), Moist Evergreen Zone (MEZ) and Upland Evergreen Moist Zone (UEMZ) in Ghana. Results show that Soil organic carbon (SOC) stored decreased with increasing soil depth across all agroecological zones. Cocoa farms with shade trees stored 6 times more soil carbon (35.90±1.56 Mg C ha-1) compared to the full sun systems (5.98±1.56 Mg C ha-1).</v>
       </c>
       <c r="V59" t="str">
-        <v/>
+        <v>Carbon storage, cocoa agroforestry, agroecological zones, Ghana, climate change mitigation</v>
       </c>
     </row>
     <row r="60" xml:space="preserve">
@@ -5803,13 +5803,13 @@
         <v>Serves as an introduction to a curated research topic; provides insight into key innovations and interventions promoted by IITA and partners in SSA.</v>
       </c>
       <c r="T60" t="str">
-        <v/>
+        <v>10.3389/fsufs.2022.959604</v>
       </c>
       <c r="U60" t="str">
-        <v/>
+        <v>Agriculture is the mainstay of the economies of sub-Saharan Africa as it employs 60% of the active population and contributes up to 35% of the GDP. Improving and maintaining soil fertility is critical for sub-Saharan Africa to achieve the sustainable development goals (SDGs) and, in particular, contribute to eradicating poverty (SDG 1), and ending hunger, achieving food security, improving nutrition and promoting sustainable agriculture (SDG 2).</v>
       </c>
       <c r="V60" t="str">
-        <v/>
+        <v>Soil fertility management, sub-Saharan Africa, sustainable agriculture, food production, SDGs</v>
       </c>
     </row>
     <row r="61" xml:space="preserve">
@@ -5885,13 +5885,13 @@
         <v>Model integrates empirical life table data with GIS for pest forecasting. Supported by BMZ/GIZ and IITA. Contributes to climate-smart pest management.</v>
       </c>
       <c r="T61" t="str">
-        <v/>
+        <v>10.1080/14735903.2025.2513790</v>
       </c>
       <c r="U61" t="str">
-        <v/>
+        <v>Adoption of Climate-smart Agricultural Practices (CSA) enhances crop productivity and livelihoods. Smallholder coffee farmers in Uganda receive training on good agricultural practices (GAPs) through extension programs, but adoption remains low. Adopting all 'best practices' at once may be unrealistic for resource-limited, risk-averse smallholders. This study tested a Stepwise approach, breaking GAPs into manageable, incremental investments. Field trials were conducted in Luweero (Central) and Sironko (East) districts of Uganda, with 16 demonstration sites using randomized treatments divided into four steps. Each site served 25-30 farmers through experiential learning. Results from two harvests (2018-2019) showed significant cumulative yield gains over the control.</v>
       </c>
       <c r="V61" t="str">
-        <v/>
+        <v>climate-smart agriculture, coffee production, Uganda, stepwise approach, smallholder farmers, adoption</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
@@ -5967,13 +5967,13 @@
         <v>Supports the CGIAR GENDER Impact Platform. Recommends systemic reforms including gender-responsive policy design, intersectional analysis, and recognition of women's roles in fisheries and aquaculture value chains globally.</v>
       </c>
       <c r="T62" t="str">
-        <v/>
+        <v>10.3390/su6096125</v>
       </c>
       <c r="U62" t="str">
-        <v/>
+        <v>Cameroon is committed to reducing emissions from deforestation and forest degradation plus conservation, sustainable management of forests and enhancement of carbon stocks (REDD+). To achieve this goal, the government has introduced a series of policy reforms and formulated key strategic planning documents to advance the REDD+ readiness process. This paper assesses the extent to which major cross-sectoral policies support or impede the development and implementation of an optimal REDD+ strategy in Cameroon from a comparative multi-criteria perspective. Study results reveal that a majority of the policy instruments reviewed appeared to be less prescriptive in terms of any tangible REDD+ strategy, as they do not have provisions for tangible measures to reduce deforestation and forest degradation.</v>
       </c>
       <c r="V62" t="str">
-        <v/>
+        <v>multi-criteria analysis, policy instruments, GIS, REDD+, decision-support tool</v>
       </c>
     </row>
     <row r="63" xml:space="preserve">
@@ -6045,13 +6045,13 @@
         <v>Funded by BMZ; links to CGIAR climate programs; relevance for West Africa's cocoa adaptation planning under climate change.</v>
       </c>
       <c r="T63" t="str">
-        <v/>
+        <v>10.3920/WMJ2016.2130</v>
       </c>
       <c r="U63" t="str">
-        <v/>
+        <v>Aflatoxin contamination of crops is frequent in warm regions across the globe, including large areas in sub-Saharan Africa, and crop contamination with these dangerous toxins transcends health, food security, and trade sectors. Carefully selected atoxigenic genotypes in biological control (biocontrol) formulations efficiently reduce aflatoxin contamination of crops when applied prior to flowering in the field. The technology has been improved for use in sub-Saharan Africa, where efforts are under way to develop biocontrol products. Benefits of aflatoxin biocontrol technologies are discussed along with potential challenges, including climate change, likely to be faced during the scaling-up of Aflasafe products.</v>
       </c>
       <c r="V63" t="str">
-        <v/>
+        <v>aflatoxin, biological control, climate change, food safety, sub-Saharan Africa, Aflasafe</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -6123,13 +6123,13 @@
         <v>Research supported by IITA, CGIAR's CCAFS and FTA programs, with funding from the German Ministry for Economic Cooperation and Development (BMZ).</v>
       </c>
       <c r="T64" t="str">
-        <v/>
+        <v>10.1111/pbi.12467</v>
       </c>
       <c r="U64" t="str">
-        <v/>
+        <v>Agriculture is now facing the 'perfect storm' of climate change, increasing costs of fertilizer and rising food demands from a larger and wealthier human population. These factors point to a global food deficit unless the efficiency and resilience of crop production is increased. The intensification of agriculture has focused on improving production under optimized conditions, with significant agronomic inputs. A new agricultural paradigm is required, reducing dependence on high inputs and increasing crop diversity, yield stability and environmental resilience. Genomics offers unprecedented opportunities to increase crop yield, quality and stability of production through advanced breeding strategies, enhancing the resilience of major crops to climate variability, and increasing the productivity and range of minor crops to diversify the food supply.</v>
       </c>
       <c r="V64" t="str">
-        <v/>
+        <v>genomics, climate change, agricultural intensification, crop improvement, breeding, resilience</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
@@ -6193,13 +6193,13 @@
         <v>Study promotes low-cost, scalable drought assessment tools like handheld infrared thermometers and recommends best practices for banana phenotyping in the field.</v>
       </c>
       <c r="T65" t="str">
-        <v/>
+        <v>10.1094/PDIS-01-23-0166-FE</v>
       </c>
       <c r="U65" t="str">
-        <v/>
+        <v>The Global Plant Health Assessment (GPHA) is a collective, volunteer-based effort to assemble expert opinions on plant health and disease impacts on ecosystem services based on published scientific evidence. The GPHA considers a range of forest, agricultural, and urban systems worldwide. Among the 33 (Ecoregion × Plant System) considered, 18 are assessed as in fair or poor health, and 20 as in declining health. Much of the observed state of plant health and its trends are driven by a combination of forces, including climate change, species invasions, and human management. Healthy plants ensure (i) provisioning, (ii) regulation, and (iii) cultural ecosystem services.</v>
       </c>
       <c r="V65" t="str">
-        <v/>
+        <v>plant health, ecosystem services, climate change, disease, global assessment, food security</v>
       </c>
     </row>
     <row r="66" xml:space="preserve">
@@ -6273,13 +6273,13 @@
         <v>Chickpea offers off-season growth potential. Common bean is least water-limited and most widely grown legume in region. Calls for more data on legume intercropping systems.</v>
       </c>
       <c r="T66" t="str">
-        <v/>
+        <v>10.1016/j.crsust.2023.100219</v>
       </c>
       <c r="U66" t="str">
-        <v/>
+        <v>This study examines how gender norms mediate crop farmers' responsive approaches to rapid climate warming, focusing on men and women crop smallholder farmers in Nasarawa state who experience the impacts of rapid climate warming differently. There has been an additional increase of 1.14°C in the minimum temperature over the study period. 63% of respondents perceived both heatwaves and dry spells. Major adaptation strategies used by farmers are traditional irrigation (56%), sustainable forestry (44%), and cover cropping (54%). 66% of women adopted traditional irrigation and 75% practiced cover cropping, while 74% of men practiced sustainable forestry. Gender norms constrain the adoption of responsive approaches due to unequal access to climate interventions in agriculture.</v>
       </c>
       <c r="V66" t="str">
-        <v/>
+        <v>gender, climate warming, smallholder farmers, adaptation strategies, Nigeria, gender norms</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -6367,13 +6367,13 @@
 Understory vegetation management in CAF contributes significantly to soil carbon</v>
       </c>
       <c r="T67" t="str">
-        <v/>
+        <v>10.1007/s10584-019-02447-0</v>
       </c>
       <c r="U67" t="str">
-        <v/>
+        <v>Gender mainstreaming was acknowledged as an indispensable strategy for achieving gender equality at the 1995 Beijing Platform for Action. This study analyzes the extent of gender integration in agricultural and natural resource policies in Uganda and Tanzania, and how gender is budgeted for in implementation plans at district and lower governance levels. A total of 155 policy documents, development plans, and annual action plans from national, district, and sub-county/ward levels were reviewed. Results show that whereas there is increasing gender responsiveness, (i) gender issues are still interpreted as 'women issues,' (ii) there is disharmony in gender mainstreaming across governance levels, (iii) budgeting for gender is not yet fully embraced, (iv) allocations to gender at sub-national level remain inconsistently low, and (v) gender activities do not address structural inequalities.</v>
       </c>
       <c r="V67" t="str">
-        <v/>
+        <v>gender mainstreaming, climate change policy, agriculture policy, East Africa, Uganda, Tanzania</v>
       </c>
     </row>
     <row r="68" xml:space="preserve">
@@ -6463,13 +6463,13 @@
 Provides detailed catalog of genotyping and molecular breeding efforts for multiple legumes</v>
       </c>
       <c r="T68" t="str">
-        <v/>
+        <v>10.1038/s41467-023-39338-z</v>
       </c>
       <c r="U68" t="str">
-        <v/>
+        <v>Anthropogenic activities profoundly impact soil organic carbon (SOC), affecting its contribution to ecosystem services such as climate regulation. This study conducted a thorough review of the impacts of land-use change, land management, and climate change on SOC using second-order meta-analysis, synthesizing findings from 230 first-order meta-analyses comprising over 25,000 primary studies. The study shows that: (i) land conversion for crop production leads to high SOC loss that can be partially restored through land management practices, particularly by introducing trees and incorporating exogenous carbon in the form of biochar or organic amendments, (ii) land management practices implemented in forests generally result in depletion of SOC, and (iii) indirect effects of climate change, such as through wildfires, have a greater impact on SOC than direct climate change effects.</v>
       </c>
       <c r="V68" t="str">
-        <v/>
+        <v>soil organic carbon, land-use change, climate change, Anthropocene, meta-analysis, carbon sequestration</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
@@ -6551,13 +6551,13 @@
 Points to CRISPR/Cas9 as a future tool to reduce anti-nutritional factors, improve cooking time, and enhance stress tolerance.</v>
       </c>
       <c r="T69" t="str">
-        <v/>
+        <v>10.1111/mec.13762</v>
       </c>
       <c r="U69" t="str">
-        <v/>
+        <v>The study applied approximate Bayesian computation to sequence data from four nuclear and one mitochondrial marker, revealing that African populations of Aedes aegypti best fit a demographic model of lineage diversification, historical admixture and recent population structuring. ABC analysis and haplotype networks support earlier inferences of a single out-of-Africa colonization event, while a cline of decreasing genetic diversity indicates that Ae. aegypti moved first from Africa to the Americas and then to Asia. By increasing genetic diversity and forming novel allelic combinations, divergence and historical admixture within Africa could have provided the adaptive potential needed for the successful worldwide spread of Ae. aegypti.</v>
       </c>
       <c r="V69" t="str">
-        <v/>
+        <v>Pleistocene climatic change, approximate Bayesian computation, arbovirus, domestication, forest fragmentation, invasive species</v>
       </c>
     </row>
     <row r="70" xml:space="preserve">
@@ -6651,13 +6651,13 @@
 Focused on smallholder rice systems in ESA but methods applicable to other crops.</v>
       </c>
       <c r="T70" t="str">
-        <v/>
+        <v>10.1080/00207233.2017.1398432</v>
       </c>
       <c r="U70" t="str">
-        <v/>
+        <v>This paper evaluates the socio-technical interactions of REDD+ (Reducing Emissions from Deforestation and Forest Degradation) and measurement, reporting and verification (MRV) systems, particularly focusing on the degree of inclusiveness of transnational advocacy networks (TANs) and the empowerment of African state and non-state actors within these systems. The study examines forest governance challenges in Central Africa and proposes a participatory model to increase stakeholder involvement in carbon markets, addressing issues of equity, benefit sharing, and institutional capacity for effective REDD+ implementation in the context of climate change mitigation.</v>
       </c>
       <c r="V70" t="str">
-        <v/>
+        <v>REDD+, forest governance, participatory model, carbon markets, Central Africa, climate change mitigation</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
@@ -6751,13 +6751,13 @@
 Funded by Gates Foundation and WASCAL.</v>
       </c>
       <c r="T71" t="str">
-        <v/>
+        <v>10.1002/fes3.172</v>
       </c>
       <c r="U71" t="str">
-        <v/>
+        <v>This study undertakes an ex-ante evaluation of the effects of alternative technology and policy options on soybean supply and demand in sub-Saharan Africa (SSA) to 2050. Current soybean consumption in SSA is dominated by cooking oil followed by soybean cake used as animal feed. Due to weak processing sectors and low soybean yields, the region is currently importing about 70% of its consumption requirements. Sub-Saharan Africa spends more than US$1 billion on net imports of soybean-based agricultural products. A combination of promising innovations affecting the soybean value chain across SSA would be required to close the future soybean demand gap.</v>
       </c>
       <c r="V71" t="str">
-        <v/>
+        <v>climate change, geospatial bio-economic modeling, IMPACT, import dependency, soybean, sub-Saharan Africa</v>
       </c>
     </row>
     <row r="72" xml:space="preserve">
@@ -6841,13 +6841,13 @@
 Funded by USAID via Africa RISING under Feed the Future</v>
       </c>
       <c r="T72" t="str">
-        <v/>
+        <v>10.1016/j.heliyon.2023.e20199</v>
       </c>
       <c r="U72" t="str">
-        <v/>
+        <v>Ricinodendron heudelotii is an important nutraceutical reservoir whose sustainable exploitation requires information on its potential distribution in the current context of rapid population growth and climate change threats. This study aimed to map suitable areas for its domestication and conservation under current and future climate conditions in Benin. Currently, about four percent (5082 km²) of the country's area mainly located in the sub-humid and humid zones were potentially suitable. Under future climatic conditions, the potentially suitable areas were mainly in the sub-humid zone, but almost all highly suitable areas in the humid zone will become medium suitable by 2055 and 2085. This species will migrate following its ecological requirements linked mainly to isothermality, mean annual rainfall, and soil sand content.</v>
       </c>
       <c r="V72" t="str">
-        <v/>
+        <v>biodiversity, modelling, climate change, habitats, spatial distribution</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
@@ -6933,13 +6933,13 @@
 Emphasizes combining conventional and modern tools to accelerate cassava improvement</v>
       </c>
       <c r="T73" t="str">
-        <v/>
+        <v>10.17660/ActaHortic.2018.1225.4</v>
       </c>
       <c r="U73" t="str">
-        <v/>
+        <v>This paper examines the sustainability of African vegetable production in the face of future climatic uncertainty and increasing biotic stressors. Climate change is expected to significantly affect vegetable production systems across Africa through changes in temperature, precipitation patterns, and increased pest and disease pressure. The study discusses how these factors will influence crop productivity, food security, and livelihoods of smallholder farmers. Adaptation strategies and the potential role of climate-resilient vegetable varieties are explored to address these challenges.</v>
       </c>
       <c r="V73" t="str">
-        <v/>
+        <v>African vegetables, climate change, biotic stress, food security, sustainability, adaptation</v>
       </c>
     </row>
     <row r="74" xml:space="preserve">
@@ -7027,13 +7027,13 @@
 Potential for root traits to contribute to cost-effective breeding in resource-limited environments</v>
       </c>
       <c r="T74" t="str">
-        <v/>
+        <v>10.1080/17429145.2019.1643934</v>
       </c>
       <c r="U74" t="str">
-        <v/>
+        <v>The study examined how seasonal variations in microclimate and coffee leaf rust (CLR) incidence across different altitudes and shading systems affect coffee production. At mid and high altitudes, high CLR incidence occurred in the shading system showing a low diurnal temperature range and a high dew point temperature. The findings demonstrate that microclimate conditions created by shading systems significantly influence disease pressure and must be considered in climate adaptation strategies for coffee production.</v>
       </c>
       <c r="V74" t="str">
-        <v/>
+        <v>coffee leaf rust, climate variability, altitude, microclimate, shading systems, agroforestry</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
@@ -7123,13 +7123,13 @@
 Stresses the need to bridge researchâ€“practice divides through stakeholder co-production of knowledge</v>
       </c>
       <c r="T75" t="str">
-        <v/>
+        <v>10.3390/su15010190</v>
       </c>
       <c r="U75" t="str">
-        <v/>
+        <v>The paper advances a gender equality and social inclusion (GESI) framework for incorporating climate information services (CIS), which is becoming central due to ongoing climate change and climate variability. Gender is understood as a social construct of who women and men are supposed to be. Gender inequalities seem to be enduring such that, despite innovations in agricultural and climate information technologies, unequal gender power dynamics will still emerge. The framework has five indicators: (1) gender targeting by intentional design, (2) collection of sex-disaggregated data, (3) conduct analysis of sex-disaggregated data, (4) dissemination of technological options, and (5) continuous monitoring of gender and ongoing empowerment evaluation.</v>
       </c>
       <c r="V75" t="str">
-        <v/>
+        <v>gender equality, social inclusion, climate information services, climate change adaptation, gender mainstreaming, Africa</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -7215,13 +7215,13 @@
 Suggests shift in EU protein crop strategy for health, sustainability, and climate resilience</v>
       </c>
       <c r="T76" t="str">
-        <v/>
+        <v>10.1016/j.jssas.2024.06.004</v>
       </c>
       <c r="U76" t="str">
-        <v/>
+        <v>This study evaluated farmers' knowledge of soil quality and yield assessment among cassava farmers in southwestern Nigeria. Data were collected on farmers' demography, farming experience, criteria for selecting sites for cassava cultivation, and methods of yield prediction. Farmers use a combination of soil and vegetation-based criteria to assess soil quality from which the decision to cultivate a given land is made. Among the soil-based criteria, soil drainage, colour, and depth rank the most and are most used. The study highlights the importance of integrating local knowledge with scientific approaches for sustainable cassava production under changing climatic conditions.</v>
       </c>
       <c r="V76" t="str">
-        <v/>
+        <v>soil quality, cassava, farmer assessment, indigenous knowledge, yield prediction, Nigeria</v>
       </c>
     </row>
     <row r="77" xml:space="preserve">
@@ -7305,13 +7305,13 @@
 Highlights pest-climate-resource dynamics as critical under climate change</v>
       </c>
       <c r="T77" t="str">
-        <v/>
+        <v>10.3390/genes11091054</v>
       </c>
       <c r="U77" t="str">
-        <v/>
+        <v>Genetic adaptation of maize to the increasingly unpredictable climatic conditions is an essential prerequisite for achievement of food security and sustainable development goals in sub-Saharan Africa. The landraces of maize, which have not served as sources of improved germplasm, are invaluable sources of novel genetic variability crucial for achieving this objective. The overall goal of this study was to assess the genetic diversity and population structure of a maize panel of 208 accessions, comprising landrace gene pools from Burkina Faso (58), Ghana (43), and Togo (89), together with reference populations (18) from the International Institute of Tropical Agriculture (IITA). Genotyping with 5974 DArTseq-SNP markers revealed immense genetic diversity indicated by average expected heterozygosity (0.36), observed heterozygosity (0.5), and polymorphic information content (0.29).</v>
       </c>
       <c r="V77" t="str">
-        <v/>
+        <v>landraces, genetic diversity, population structure, West Africa, maize improvement, DArTseq markers</v>
       </c>
     </row>
     <row r="78" xml:space="preserve">
@@ -7403,13 +7403,13 @@
 Planned indicators: root biomass, microbial biomass, mineral-associated SOC, yield-SOC tradeoffs</v>
       </c>
       <c r="T78" t="str">
-        <v/>
+        <v>10.1371/journal.pone.0222941</v>
       </c>
       <c r="U78" t="str">
-        <v/>
+        <v>Scapsipedus icipe Hugel and Tanga (Orthoptera: Gryllidae) is a newly described edible cricket species. Although there is substantial interest in mass production of S. icipe for human food and animal feed, no information exists on the impact of temperature on their bionomics. Temperature-dependent development, survival, reproductive and life table parameters of S. icipe was generated and integrated into advanced Insect Life Cycle Modeling software to describe relative S. icipe population increase and spatial spread based on nine constant temperature conditions. The lowest developmental threshold temperatures was 14.3, 12.67 and 19.12°C and the thermal constants for development were 185.2, 1111.1 and 40.7 degree days for egg, nymph and pre-adult stages, respectively. The highest total fecundity, intrinsic rate of natural increase, net reproductive rate and shortest doubling time was recorded at 30°C.</v>
       </c>
       <c r="V78" t="str">
-        <v/>
+        <v>edible cricket, Scapsipedus icipe, temperature-dependent development, life table, climate modeling, Africa</v>
       </c>
     </row>
     <row r="79" xml:space="preserve">
@@ -7501,13 +7501,13 @@
 Strong call for iterative modeling plus localized rural diagnostics</v>
       </c>
       <c r="T79" t="str">
-        <v/>
+        <v>10.3389/fpls.2022.782140</v>
       </c>
       <c r="U79" t="str">
-        <v/>
+        <v>Dietary diversification and incorporation of resilient crop species such as under-exploited leguminous species referred to as orphan, minor, or underutilized into food systems in Sub-Saharan Africa (SSA) is critical for addressing the current challenges of malnutrition, food insecurity, and climate change. These crops have great potential for improved food security and nutrition, yet they remain neglected and underutilized despite their nutritional and health benefits. The exploitation of orphan legumes can contribute significantly to the achievement of the Sustainable Development Goals (SDGs), particularly those related to zero hunger, good health and well-being, and climate action.</v>
       </c>
       <c r="V79" t="str">
-        <v/>
+        <v>climate change, food security, malnutrition, orphan legumes, sustainable development goals</v>
       </c>
     </row>
     <row r="80" xml:space="preserve">
@@ -7599,13 +7599,13 @@
 Funded in part by CCAFS and the NextGen Cassava project</v>
       </c>
       <c r="T80" t="str">
-        <v/>
+        <v>10.1094/PHYTO-03-17-0082-FI</v>
       </c>
       <c r="U80" t="str">
-        <v/>
+        <v>Resistance genes are a major tool for managing crop diseases. The networks of crop breeders who exchange resistance genes and deploy them in varieties help to determine the global landscape of resistance and epidemics, an important system for maintaining food security. These networks function as a complex adaptive system, with associated strengths and vulnerabilities, and implications for policies to support resistance gene deployment strategies. Extensions of epidemic network analysis can be used to evaluate the multilayer agricultural networks that support and influence crop breeding networks. Here, we evaluate the general structure of crop breeding networks for cassava, potato, rice, and wheat. All four are clustered due to phytosanitary and intellectual property regulations, and linked through CGIAR hubs. Cassava networks primarily include public breeding groups, whereas others are more mixed.</v>
       </c>
       <c r="V80" t="str">
-        <v/>
+        <v>resistance genes, crop breeding networks, disease resistance, cassava, potato, rice, wheat, CGIAR, phytopathology</v>
       </c>
     </row>
     <row r="81" xml:space="preserve">
@@ -7683,13 +7683,13 @@
 Highlights the need for additional research into evolutionary and ecological resilience in tropical species.</v>
       </c>
       <c r="T81" t="str">
-        <v/>
+        <v>10.1242/bio.058619</v>
       </c>
       <c r="U81" t="str">
-        <v/>
+        <v>Thermal adaptation to habitat variability can determine species vulnerability to environmental change. For example, physiological tolerance to naturally low thermal variation in tropical forests species may alter their vulnerability to climate change impacts, compared with open habitat species. The study investigated the role of habitat in structuring thermal limits, critical thermal maximum (CTmax) and minimum (CTmin), for Bicyclus dorothea (Cramer, 1779), a nymphalid butterfly found in both forest and ecotone habitats in many tropical African countries.</v>
       </c>
       <c r="V81" t="str">
-        <v/>
+        <v>thermal tolerance, climate change, tropical butterfly, habitat adaptation, Bicyclus dorothea, Africa</v>
       </c>
     </row>
     <row r="82" xml:space="preserve">
@@ -7771,13 +7771,13 @@
 Open-access data can be linked with agronomic or socioeconomic datasets for future impact studies.</v>
       </c>
       <c r="T82" t="str">
-        <v/>
+        <v>10.5194/essd-13-4133-2021</v>
       </c>
       <c r="U82" t="str">
-        <v/>
+        <v>The African Tropics are hotspots of modern-day land use change and are, at the same time, of great relevance for the cycling of carbon (C) and nutrients between plants, soils, and the atmosphere. However, the consequences of land conversion on biogeochemical cycles are still largely unknown as they are not studied in a landscape context that defines the geomorphic, geochemical, and pedological framework in which biological processes take place. Thus, the response of tropical soils to disturbance by erosion and land conversion is one of the great uncertainties in assessing the carrying capacity of tropical landscapes to grow food for future generations and in predicting greenhouse gas fluxes from soils to the atmosphere and, hence, future earth system dynamics. Here we describe version 1.0 of an open-access database created as part of the project Tropical soil organic carbon dynamics along erosional disturbance gradients in relation to variability in soil geochemistry and land use (TropSOC). TropSOC v1.0 contains spatially and temporally explicit data on soil, vegetation, environmental properties, and land management collected from 136 pristine tropical forest and cropland plots between 2017 and 2020 as part of monitoring and sampling campaigns in the eastern Congo Basin and the East African Rift Valley system.</v>
       </c>
       <c r="V82" t="str">
-        <v/>
+        <v>soil organic carbon, tropical soils, land use change, geochemistry, TropSOC, Africa, cropland, forest</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
@@ -7863,13 +7863,13 @@
 Recommends further refinement of repellent use and integration of biocontrol agents in net house systems.</v>
       </c>
       <c r="T83" t="str">
-        <v/>
+        <v>10.1016/j.cropro.2020.105449</v>
       </c>
       <c r="U83" t="str">
-        <v/>
+        <v>The study investigated a push-pull strategy to prevent small insect pest outbreaks in a net house, where the push component consisted of two stimulus plants (Cymbopogon citratus and Tagetes minuta), and the pull stimuli consisted of visual cues from blue and yellow sticky traps. Field experiments were set up in central Kenya and conducted during a rainy and a dry season. Net house and net house + push-pull reduced insect pest infestations, except Aphis craccivora in the dry period. The push-pull strategy reduced Empoasca sp. infestations in the rainy period. Cowpea pod yields and quality were higher in the net house treatments in both periods. Cowpea pod and grain yield and quality were higher in the net house and net house + push-pull treatments than in the control irrespective of the period.</v>
       </c>
       <c r="V83" t="str">
-        <v/>
+        <v>push-pull strategy, cowpea, integrated pest management, net houses, Cymbopogon citratus, Tagetes minuta, Kenya</v>
       </c>
     </row>
     <row r="84" xml:space="preserve">
@@ -7961,13 +7961,13 @@
 IITA is identified as a central hub for research, diagnostics, and capacity development through its Nairobi office and broader regional platforms.</v>
       </c>
       <c r="T84" t="str">
-        <v/>
+        <v>10.1146/annurev-phyto-080417-045833</v>
       </c>
       <c r="U84" t="str">
-        <v/>
+        <v>Challenges in Sub-Saharan Africa including low agricultural productivity, exploding populations, and escalating urbanization have led to declining per capita food availability. Crop production intensification brings elevated threats from pests and diseases, including plant-parasitic nematodes. This review examines the impact of plant-parasitic nematodes on food security in Sub-Saharan Africa.</v>
       </c>
       <c r="V84" t="str">
-        <v/>
+        <v>plant-parasitic nematodes, food security, Sub-Saharan Africa, agricultural productivity, crop pests</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
@@ -8059,13 +8059,13 @@
 Emphasizes seed system innovations and partnerships to accelerate delivery and adoption of new varieties.</v>
       </c>
       <c r="T85" t="str">
-        <v/>
+        <v>10.1111/pbr.12682</v>
       </c>
       <c r="U85" t="str">
-        <v/>
+        <v>Formal public sector soybean breeding in Africa spans over four decades, and it was initiated by the International Institute of Tropical Agricultural (IITA). As the demand of soybean continues to outstrip production, strategic projects such the Tropical Legume (TL) were initiated, in which the main goal was to enhance the productivity of soybean in the farmers' fields in Sub-Saharan Africa. One of the strategies to enhance the productivity of soybean in the farmers' fields is through developing and deploying improved soybean varieties in the target countries. Through the TL I and TL II projects, a number of varieties were released in the target countries, Kenya, Nigeria, Malawi and Mozambique by employing participatory variety selection (PVS). This review provides highlights of the achievements made by IITA breeding programme and insights of what needs to be done to enhance yield improvement for soybean in Africa using demand-driven breeding approaches.</v>
       </c>
       <c r="V85" t="str">
-        <v/>
+        <v>soybean breeding, Glycine max, African tropics, IITA, Tropical Legume project, cultivar development, participatory variety selection</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
@@ -8135,13 +8135,13 @@
         <v>Funded by the European Commission Erasmus Mundus program and CGIAR Roots, Tubers and Bananas. Suggests use of multi-species models for future studies.</v>
       </c>
       <c r="T86" t="str">
-        <v/>
+        <v>10.1007/s10340-018-1059-9</v>
       </c>
       <c r="U86" t="str">
-        <v/>
+        <v>Whiteflies (Hemiptera: Aleyrodidae) are important insect pests causing serious damage to plants and transmitting hundreds of plant viruses. Climate change is expected to influence life history and trophic interactions among plants, whiteflies and their natural enemies. Here, we review the potential impacts of climate change on whiteflies and the likely consequences for agricultural systems. This review concludes that while climatic stress tends to negatively affect life history traits, the effects differ with the tolerance of the whiteflies and the amount of stress experienced. Whiteflies also differ in their adaptability. Better adapted species will likely experience increased distribution and abundance provided their tolerance limits are not exceeded, while species with lower tolerance and adaptation limits will suffer reduced fitness, which will have overall effects on their distribution and abundance in space.</v>
       </c>
       <c r="V86" t="str">
-        <v/>
+        <v>whiteflies, climate change, plant viruses, Bemisia tabaci, pest management, temperature tolerance</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
@@ -8211,13 +8211,13 @@
         <v>Funded by the International Potato Center and CGIAR. Results contribute to predictive modeling of pest behavior under climate change scenarios.</v>
       </c>
       <c r="T87" t="str">
-        <v/>
+        <v>10.1007/s10340-020-01249-z</v>
       </c>
       <c r="U87" t="str">
-        <v/>
+        <v>The whiteflies belonging to the species group Bemisia tabaci transmit viruses that are the greatest constraint to the production of cassava, Africa's most important food security crop. The study examined the life history of an endemic African population of B. tabaci SSA-ESA at six constant temperatures (16, 20, 24, 28, 32, 36 °C) in controlled environment chambers, and for 10 generations in the field. Oviposition occurred between 20 and 28 °C, with highest fecundity (114.5 ± 88.2) eggs per female at 20 °C. Similarly, B. tabaci adult females average survival time was longest (19.7 days) at 24 °C, and shortest (8.5 days) at 36 °C. Immature development time decreased with increasing temperature from 59.3 days at 16 °C to 16.3 days at 28 °C, and increased above 28 °C. A constant temperature of 36 °C was lethal to eggs and first instars and no immature stage developed further to adults at this temperature.</v>
       </c>
       <c r="V87" t="str">
-        <v/>
+        <v>Bemisia tabaci, cassava, whiteflies, temperature dependence, life history, climate change, SSA-ESA</v>
       </c>
     </row>
     <row r="88" xml:space="preserve">
@@ -8291,13 +8291,13 @@
         <v>Study funded by Erasmus Mundus Joint Doctorate and supported by CGIAR-RTB. Emphasizes need for national adaptation strategies linked to cassava health.</v>
       </c>
       <c r="T88" t="str">
-        <v/>
+        <v>10.31817/vjas.2021.4.1.03</v>
       </c>
       <c r="U88" t="str">
-        <v/>
+        <v>Study on production characteristics and adaptation strategies for managing cassava whiteflies and viruses under climate change conditions in Tanzania.</v>
       </c>
       <c r="V88" t="str">
-        <v/>
+        <v>cassava, climate change, whiteflies, viruses, Tanzania, adaptation strategies, Bemisia tabaci</v>
       </c>
     </row>
     <row r="89" xml:space="preserve">
@@ -8377,13 +8377,13 @@
         <v>Backed by Gates Foundation and Stress Tolerant Maize for Africa (STMA) initiative. Data available via IITA CKAN repository.</v>
       </c>
       <c r="T89" t="str">
-        <v/>
+        <v>10.3389/fsufs.2023.1238776</v>
       </c>
       <c r="U89" t="str">
-        <v/>
+        <v>In West and Central Africa (WCA), drought and low soil nitrogen (low N) impede increased maize (Zea mays L.) productivity and production. Due to climate change, the two stresses usually occur together, leading to food, nutritional, and economic insecurity in the sub-region. Moderate to high estimates of heritability were observed for most of the measured traits under stress conditions, indicating that the traits could be easily transmitted to the progenies. Fifty-seven out of the 96 QPM inbreds evaluated exhibited varying degrees of resilience to drought and low N.</v>
       </c>
       <c r="V89" t="str">
-        <v/>
+        <v>climate change, drought, indirect selection for high yield, low soil nitrogen, quality protein maize, stress resilient maize</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -8469,13 +8469,13 @@
         <v>Funded by USAID and CGIAR Roots, Tubers and Bananas (RTB). Highlights knowledge gaps in pathogen-host dynamics and need for multi-environment resistance screening protocols.</v>
       </c>
       <c r="T90" t="str">
-        <v/>
+        <v>10.1111/ppa.12824</v>
       </c>
       <c r="U90" t="str">
-        <v/>
+        <v>Banana and plantain (Musa spp.) are important food crops in tropical and subtropical regions of the world where they generate millions of dollars annually to both subsistence farmers and exporters. Since 1902, Pseudocercospora banana pathogens, Pseudocercospora fijiensis, P. musae and P. eumusae, have emerged as major production constraints to banana and plantain. Despite concerted efforts to counter these pathogens, they have continued to negatively impact banana yield. In this review, the economic importance, distribution and the interactions between Pseudocercospora banana pathogens and Musa species are discussed. Interactions are further scrutinized in the light of an emerging climate change scenario and efforts towards the development of resistant banana germplasm are discussed.</v>
       </c>
       <c r="V90" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
@@ -8553,13 +8553,13 @@
         <v>First national study assessing small grain mycotoxin risks in Zimbabwe. Supports regional policy reforms for grain safety and storage.</v>
       </c>
       <c r="T91" t="str">
-        <v/>
+        <v>10.3390/foods10020287</v>
       </c>
       <c r="U91" t="str">
-        <v/>
+        <v>Maize and three small grain cereals (sorghum, pearl millet, and finger millet) produced by smallholder farmers in Zimbabwe during 2016 and 2017 were examined for fungal community structure, and total aflatoxin (AF) and fumonisin (FM) content. A total of 800 maize and 180 small grain samples were collected at harvest and during storage from four agroecological zones. Fusarium spp. dominated the fungi associated with maize. Across crops, Aspergillus flavus constituted the main Aspergillus spp. Small grain cereals were less susceptible to both AF and FM. AF (52%) and FM (89%) prevalence was higher in maize than in small grains (13–25% for AF and 0–32% for FM). Less than 2% of small grain samples exceeded the EU regulatory limit for AF (4 µg/kg), while &lt;10% exceeded the EU regulatory limit for FM (1000 µg/kg).</v>
       </c>
       <c r="V91" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="92" xml:space="preserve">
@@ -8633,13 +8633,13 @@
         <v>Supports selection and development of drought- and heat-tolerant cowpea varieties suited to low-input environments in West Africa.</v>
       </c>
       <c r="T92" t="str">
-        <v/>
+        <v>10.25081/jpsp.2022.v8.7896</v>
       </c>
       <c r="U92" t="str">
-        <v/>
+        <v>The study investigated the morpho-physiological responses of two cowpea varieties (IT89KD-288 and IT99K573-1-1) to a combination of stresses (water deficit stress and high light intensity) at different growth stages. Exposure to W4 under L1 considerably reduced cowpea yield by 80% compared to those grown under L3 and full watering. Reduced light intensity enhanced cowpea grain yield irrespective of water deficit stress and IT89KD-288 was superior to IT99K573-1-1. In conclusion, reduced light intensity enhanced cowpea tolerance to water deficit and increased yield. Cowpea response was dependent on growth stage, variety and severity of stress.</v>
       </c>
       <c r="V92" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
@@ -8709,13 +8709,13 @@
         <v>Highlights ideational power in shaping resistance to gender policy in climate adaptation; relevant to broader gender policy efforts beyond Uganda.</v>
       </c>
       <c r="T93" t="str">
-        <v/>
+        <v>10.1111/dpr.12458</v>
       </c>
       <c r="U93" t="str">
-        <v/>
+        <v>Expectations that gender-mainstreaming efforts would effectively advance gender equality have been disappointed in contemporary sub-Saharan Africa. Examining this apparent disconnect, we focus on the narratives through which policy-makers relate to, and dis/engage with, gender issues. The research found that narrative shifts exercise four distinct power effects: They (1) shift blame for ineffective gender implementation; (2) legitimize policy inaction; (3) foreground and naturalize patriarchy; and (4) promote the diversion of resources.</v>
       </c>
       <c r="V93" t="str">
-        <v/>
+        <v>Africa, climate change, gender mainstreaming, ideational power, policy narrative, Uganda</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -8788,13 +8788,13 @@
         <v>Part of CGIAR Climate Change, Agriculture and Food Security (CCAFS) and Forest, Trees and Agroforestry (FTA) programs.</v>
       </c>
       <c r="T94" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2020.102812</v>
       </c>
       <c r="U94" t="str">
-        <v/>
+        <v>Improving management practices of cocoa (Theobroma cacao L.) cultivation especially under future climate change requires knowledge of yield gaps and their determining factors. The study assessed yield gaps and their determining factors through multiple regression modelling in smallholder cocoa agroforestry systems in Ghana along a climatic gradient. The studied zones referred to as dry, mid and wet with annual rainfall of 1200, 1200–1400 and 1400–2000 mm respectively. High relative yield gap in dry zone due to low intensification and climatic risk. Labour and available P significantly determined yield gap in the dry and mid zones. Access to trainings and use of hybrid seeds reduced yield gaps in the wet zone.</v>
       </c>
       <c r="V94" t="str">
-        <v/>
+        <v>theobroma cacao; yield gap; yield factors; climate change; smallholders; intensification</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -8872,13 +8872,13 @@
         <v>Religious and spiritual beliefs influence climate perceptions. Radio/TV is the main source of climate info. The study suggests scaling up institutional support to enhance resilience.</v>
       </c>
       <c r="T95" t="str">
-        <v/>
+        <v>10.3390/su14052847</v>
       </c>
       <c r="U95" t="str">
-        <v/>
+        <v>Sahelian countries, particularly Niger, are more vulnerable to climate change due to the high dependence of most of their populations on rain-fed agriculture and limited capacities to respond to climate variability and change. This paper examines the factors influencing climate change adaptation strategies and the impacts on household income and food security in rural Niger. The results showed that crop diversification (72.74%), income diversification (67.97%) and changing planting times (55%) are the main adaptation strategies adopted by households. The majority of respondents had noticed changes in rain patterns (93.21%), in the amount of rain (91.25%) and in the intensity of rain (81.82%) during the last five years.</v>
       </c>
       <c r="V95" t="str">
-        <v/>
+        <v>adaptation strategies; climate change; households; logit regression; matching techniques</v>
       </c>
     </row>
     <row r="96" xml:space="preserve">
@@ -8956,13 +8956,13 @@
         <v>Stresses need for integrated, tailored adaptation packages and policies that consider inequality. Highlights the role of livestock as coping assets and the limitations of self-reliance in the face of compound shocks.</v>
       </c>
       <c r="T96" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2017.02.006</v>
       </c>
       <c r="U96" t="str">
-        <v/>
+        <v>This paper provides an ex-ante assessment of the impacts of climate and price variability on household income and food security in Ethiopia and Ghana. The study applies an agent-based modelling approach to highlight the role of coping and adaptation strategies under climate and price variability. Our simulation results show that climate and price variability adversely affects income and food security of households in both countries. Self-coping mechanisms are found to be important but insufficient to mitigate the adverse effects of variability, implying the need for policy interventions. Adaptation strategies composed of a portfolio of actions such as the provision of production credit and access to improved seeds are found to be effective in reducing the impacts of climate and price variability in Ethiopia.</v>
       </c>
       <c r="V96" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="97" xml:space="preserve">
@@ -9054,13 +9054,13 @@
 Strong connection to farmer memory recall and context-specific responses to climate threats</v>
       </c>
       <c r="T97" t="str">
-        <v/>
+        <v>10.1007/s10113-012-0351-0</v>
       </c>
       <c r="U97" t="str">
-        <v/>
+        <v>The savanna region of Africa is a potential breadbasket of the continent but is severely affected by climate change. Understanding farmers' perceptions of climate change and the types of adjustments they have made in their farming practices in response to these changes will offer some insights into necessary interventions to ensure a successful adaptation in the region. This paper explores how smallholder farmers in the Nigerian savanna perceive and adapt to climate change. The results show that most of the farmers have noticed changes in climate and have consequently adjusted their farming practices to adapt. There are no large differences in the adaptation practices across the region, but farmers in Sudan savanna agro-ecological zone are more likely to adapt to changes in temperature than those in northern Guinea savanna.</v>
       </c>
       <c r="V97" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="98" xml:space="preserve">
@@ -9140,13 +9140,13 @@
 Grounded in national policy relevance (SDGs 1, 2, and 13)</v>
       </c>
       <c r="T98" t="str">
-        <v/>
+        <v>10.1016/j.jclepro.2018.06.221</v>
       </c>
       <c r="U98" t="str">
-        <v/>
+        <v>The paper explores the nexus of rainfall variability and food poverty, which is important for appropriate understanding of the temporal and spatial conditions of the situation, and for policy intervention for Nigeria, which is Africa's most populous and largest economy. The study focuses on Nigeria's agrarian economy which is largely rain-fed, noting that changes in the mean and variability of rainfall affect the hydrological cycle (onset and cessation) of rainfall, with significant effects on rain-fed agricultural and food production systems, and that variability in rainfall can be expected to intensify the cycle of poverty in an agrarian economy like Nigeria.</v>
       </c>
       <c r="V98" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="99" xml:space="preserve">
@@ -9238,13 +9238,13 @@
 Emphasizes value of African breeding programs using IITA germplasm in drought-prone zones.</v>
       </c>
       <c r="T99" t="str">
-        <v/>
+        <v>10.3389/fphys.2013.00093</v>
       </c>
       <c r="U99" t="str">
-        <v/>
+        <v>Cassava is an important crop in Africa, Asia, Latin America, and the Caribbean. Cassava can be produced adequately in drought conditions making it the ideal food security crop in marginal environments. Although cassava can tolerate drought stress, it can be genetically improved to enhance productivity in such environments. Drought adaptation studies in over three decades in cassava have identified relevant mechanisms which have been explored in conventional breeding. This paper highlights some modified traits suitable for early-growth phase phenotyping that may be used to reduce drought phenotyping cycle in cassava. The need for metabolite profiling, improved phenomics to take advantage of next generation sequencing technologies and high throughput phenotyping are basic steps for future direction to improve genetic gain and maximize speed for drought tolerance breeding.</v>
       </c>
       <c r="V99" t="str">
-        <v/>
+        <v>adaptation; drought tolerance; modern breeding; phenotyping; storage roots</v>
       </c>
     </row>
     <row r="100" xml:space="preserve">
@@ -9328,13 +9328,13 @@
 A rare example of interdisciplinary agenda-setting within agricultural science.</v>
       </c>
       <c r="T100" t="str">
-        <v/>
+        <v>10.1111/wre.12304</v>
       </c>
       <c r="U100" t="str">
-        <v/>
+        <v>Weedy plants pose a major threat to food security, biodiversity, ecosystem services and consequently to human health and wellbeing. However, many currently used weed management approaches are increasingly unsustainable. To address this knowledge and practice gap, in June 2014, 35 weed and invasion ecologists, weed scientists, evolutionary biologists and social scientists convened a workshop to explore current and future perspectives and approaches in weed ecology and management. A horizon scanning exercise ranked a list of 124 pre-submitted questions to identify a priority list of 30 questions.</v>
       </c>
       <c r="V100" t="str">
-        <v/>
+        <v>agroecology; integrated weed management; invasive plants; transdisciplinary research; weed adaptation</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
@@ -9418,13 +9418,13 @@
 Supports use of ex-ante modeling for climate-resilient agricultural investments</v>
       </c>
       <c r="T101" t="str">
-        <v/>
+        <v>10.1016/j.gfs.2016.08.003</v>
       </c>
       <c r="U101" t="str">
-        <v/>
+        <v>Achieving and maintaining global food security is challenged by changes in population, income, and climate, among other drivers. Assessing these threats and weighing possible solutions requires a robust multidisciplinary approach. The paper uses the IMPACT system of models to run alternative scenarios for drought and heat tolerant crop varieties under two extreme future climate scenarios. Detailed, location-specific data on climate, soil type, and physiological crop parameters are incorporated into the DSSAT crop models. The structural approach captures key knowledge across multiple areas of expertise. Economic responses reduce yield shocks from crop models. Drought and heat tolerant crops improve productivity with or without climate change.</v>
       </c>
       <c r="V101" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="102" xml:space="preserve">
@@ -9510,13 +9510,13 @@
 Recommends integrating indigenous knowledge with scientific forecasts for better targeting of adaptation policies</v>
       </c>
       <c r="T102" t="str">
-        <v/>
+        <v>10.1080/17565529.2017.1374236</v>
       </c>
       <c r="U102" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
       <c r="V102" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="103" xml:space="preserve">
@@ -9606,13 +9606,13 @@
 Suggests that adaptation will require moving coffee production upslope, which may threaten biodiversity conservation areas.</v>
       </c>
       <c r="T103" t="str">
-        <v/>
+        <v>10.1016/j.agrformet.2015.03.005</v>
       </c>
       <c r="U103" t="str">
-        <v/>
+        <v>Coffee is the world's most valuable tropical export crop. Recent studies predict severe climate change impacts on Coffea arabica (C. arabica) production. However, quantitative production figures are necessary to provide coffee stakeholders and policy makers with evidence to justify immediate action. Using data from the northern Tanzanian highlands, we demonstrate for the first time that increasing night time (Tmin) temperature is the most significant climatic variable responsible for diminishing C. arabica yields between 1961 and 2012. Projecting this forward, every 1 °C rise in Tmin will result in annual yield losses of 137 ± 16.87 kg ha−1. According to our ARIMA model, average coffee production will drop to 145 ± 41 kg ha−1 by 2060. Consequently, without adequate adaptation strategies and/or substantial external inputs, coffee production will be severely reduced in the Tanzanian highlands in the near future.</v>
       </c>
       <c r="V103" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="104" xml:space="preserve">
@@ -9692,13 +9692,13 @@
         <v>Supports climate-smart decision-making for sorghum intensification. Combines APSIM modeling, field trials, and policy relevance. Funded through CGIAR and TAMASA initiative.</v>
       </c>
       <c r="T104" t="str">
-        <v/>
+        <v>10.3390/agronomy13030727</v>
       </c>
       <c r="U104" t="str">
-        <v/>
+        <v>In the context of climate change, the sowing date and cultivar choice can influence the productivity of sorghum, especially where production is constrained by low soil fertility and early terminal drought across the challenging agro-ecologies of north-eastern Nigeria. The APSIM crop model was calibrated and validated to simulate the growth and yield of sorghum cultivars with differing maturing periods sown within varying planting time windows under improved agricultural practices. The seasonal climate simulations across sites and AEZs suggested increased yields when using adapted sorghum cultivars based on the average grain yield threshold of ≥1500 kgha−1. The optimal PWs ranged from 25 May to 30 June for some cultivars while the PWs could be extended to 10 July for others.</v>
       </c>
       <c r="V104" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="105" xml:space="preserve">
@@ -9780,13 +9780,13 @@
 Highlights role of human-induced disturbance in driving rapid forest composition shifts</v>
       </c>
       <c r="T105" t="str">
-        <v/>
+        <v>10.1038/s41586-021-03483-6</v>
       </c>
       <c r="U105" t="str">
-        <v/>
+        <v>Africa is forecasted to experience large and rapid climate change and population growth during the twenty-first century, which threatens the world's second largest rainforest. Protecting and sustainably managing these African forests requires an increased understanding of their compositional heterogeneity, the environmental drivers of forest composition and their vulnerability to ongoing changes. The study uses a dataset of 6 million trees in more than 180,000 field plots to jointly model the distribution in abundance of the most dominant tree taxa in central Africa, producing continuous maps of the floristic and functional composition of central African forests. The results show that the uncertainty in taxon-specific distributions averages out at the community level, and reveal highly deterministic assemblages.</v>
       </c>
       <c r="V105" t="str">
-        <v/>
+        <v>Climate-change impacts; Community ecology; Forest ecology; Tropical ecology; Floristic composition of forest; Functional composition of forest; Soil types; Anthropogenic gradients; African rainforest</v>
       </c>
     </row>
     <row r="106" xml:space="preserve">
@@ -9878,13 +9878,13 @@
 The project linked closely with Africa RISINGâ€™s technology park and on-farm trials</v>
       </c>
       <c r="T106" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
       <c r="U106" t="str">
-        <v/>
+        <v>Smallholder farmers in Northern Ghana regularly face shocks, challenging the sustainability of their farms and livelihoods. Different farm households and household members may be differently affected and respond with different coping strategies. We combined whole-farm modelling and farmer consultations to investigate the vulnerability, buffer and adaptive capacity of three farm types in Northern Ghana towards severe climate, economic and social shocks. Our model results indicate that the drought shock would most severely affect all farm types, drastically reducing their operating profits and soil organic matter balance.</v>
       </c>
       <c r="V106" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="107" xml:space="preserve">
@@ -9966,13 +9966,13 @@
 Highlights relevance for informing early warning, planning, and climate adaptation priorities in vulnerable Sahelian states</v>
       </c>
       <c r="T107" t="str">
-        <v/>
+        <v>10.1080/01431161.2023.2234094</v>
       </c>
       <c r="U107" t="str">
-        <v/>
+        <v>Agricultural drought is a complex phenomenon with numerous consequences and negative implications for agriculture and food systems. The Sahel is frequently affected by severe droughts, leading to significant losses in agricultural yields. The study develops a new multivariate agricultural drought vulnerability index (MADVI) that combines static and dynamic factors extracted from satellite data. The results showed statistical agreement between the predicted MADVI spatial variability and the reference model (R=0.86 for RF). The overall vulnerability situation in the watershed is 21.8% extreme, 10% very high, 16.8% high, 27.7% moderate, 22.2% low and 1.5% relatively low.</v>
       </c>
       <c r="V107" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="108" xml:space="preserve">
@@ -10060,13 +10060,13 @@
 IITAâ€™s support of this research underlines its focus on resilience and sustainable development in smallholder agriculture in Sub-Saharan Africa.</v>
       </c>
       <c r="T108" t="str">
-        <v/>
+        <v>10.3390/su16135766</v>
       </c>
       <c r="U108" t="str">
-        <v/>
+        <v>Smallholder farmers in Ethiopia face increasing challenges from climate change and variability, which threaten their food security and livelihoods. The study focuses on how climate change adaptation strategies impact household vulnerability to food insecurity in Southwest Ethiopia.</v>
       </c>
       <c r="V108" t="str">
-        <v/>
+        <v>climate change adaptation; food insecurity; vulnerability; multinomial endogenous treatment effect; smallholder farmers; Ethiopia</v>
       </c>
     </row>
     <row r="109" xml:space="preserve">
@@ -10134,13 +10134,13 @@
         <v>Suggests spatial self-organization may be useful for resilience monitoring, but transient effects mean these systems need long-term observation and caution in interpretation.</v>
       </c>
       <c r="T109" t="str">
-        <v/>
+        <v>10.1111/ecog.06139</v>
       </c>
       <c r="U109" t="str">
-        <v/>
+        <v>Regular vegetation patterns have been predicted to indicate a system slowing down and possibly desertification of drylands. However, these predictions have not yet been observed in dryland vegetation due to the inherent logistic difficulty to gather longer-term in situ data. Here, we evaluate the theoretical prediction that regular vegetation patterns are associated with empirically derived temporal indicators of critical slowing down in a dryland ecosystem in Sudan using different remote sensing products. Overall, three temporal indicators show slowing down as vegetation patterns change from gaps to labyrinths to spots towards more arid conditions. Our findings suggest that spatial self-organization of dryland vegetation is associated with critical slowing down, but this transition towards reduced resilience happens in a non-linear way.</v>
       </c>
       <c r="V109" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="110" xml:space="preserve">
@@ -10234,13 +10234,13 @@
 Emphasizes integrated approaches across institutions, geographies, and farming systems</v>
       </c>
       <c r="T110" t="str">
-        <v/>
+        <v>10.1016/j.wace.2014.04.004</v>
       </c>
       <c r="U110" t="str">
-        <v/>
+        <v>Agriculture and the economies of Sub-Saharan Africa (SSA) are highly sensitive to climatic variability. Drought, in particular, represents one of the most important natural factors contributing to malnutrition and famine in many parts of the region. This paper attempts to highlight the challenges of drought in SSA and reviews the current drought risk management strategies, especially the promising technological and policy options for managing drought risks to protect livelihoods and reduce vulnerability. The review suggests the possibilities of several ex ante and ex post drought management strategies in SSA although their effectiveness depends on agro-climatic and socio-economic conditions. A proactive approach that combines promising technological, institutional and policy solutions to manage the risks within vulnerable communities is considered to be the way forward.</v>
       </c>
       <c r="V110" t="str">
-        <v/>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="111" xml:space="preserve">
@@ -10424,13 +10424,13 @@
 Recognizes IITAâ€™s role via CoFCCA in linking rural institutions with regional adaptation knowledge.</v>
       </c>
       <c r="T112" t="str">
-        <v/>
+        <v>10.1080/17565529.2017.1291409</v>
       </c>
       <c r="U112" t="str">
-        <v/>
+        <v>Climate change will create challenges for forest-dependent communities in Africa. Local institutions play an important role in fostering community resilience in the context of change. The resilience of a community is influenced by social learning that can happen as people meet together and share their diverse experiences and knowledge. Surveys of 232 people from 13 villages, in three regions of Cameroon, provided insight about the role that internal village institutions can play in fostering community resilience. Almost all villagers, both men and women, are members of at least one group and the membership of these groups is very diverse in terms of family relations, gender, occupation, age, and level of education. While the groups were not currently working together to respond to climate change, the diverse social networks that villagers have in these groups have already fostered exchange of knowledge. Community resilience could be better fostered through a deliberate action-reflection process that includes both men and women, and builds on the social capital present in communities.</v>
       </c>
       <c r="V112" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="113" xml:space="preserve">
@@ -10506,13 +10506,13 @@
         <v>Supports Africa RISING and CGIAR resilience-building strategies. Uses robust econometrics to distinguish indirect vs. interaction effects.</v>
       </c>
       <c r="T113" t="str">
-        <v/>
+        <v>10.1016/j.ecolecon.2023.107894</v>
       </c>
       <c r="U113" t="str">
-        <v/>
+        <v>This paper examines how resilience capacity mediates or moderates the relationship between weather shocks and household food security based on two waves of farm household survey and satellite-based weather data in northern Ghana and applying econometric models. Results show that resilience capacity moderate or mediates the negative effects of heat stress and drought on food security. However, the mediating role of resilience capacity in the shock-food security nexus is more stable and stronger than its moderating role. A standard deviation (SD) increase in heat stress reduces household food consumption by 0.71 SD, but resilience capacity effectively moderates this effect by approximately 0.61 SD. For drought, household food consumption is reduced by 0.67 SD, but resilience capacity effectively dampens this negative effect by approximately 0.60 SD.</v>
       </c>
       <c r="V113" t="str">
-        <v/>
+        <v>Correlated random effects, Food security, Weather shocks, Resilience capacity, Ghana</v>
       </c>
     </row>
     <row r="114" xml:space="preserve">
@@ -10594,13 +10594,13 @@
         <v>Supports national REDD+ strategies; provides policy recommendations for farmer support systems and tenure security to enable CSA adoption.</v>
       </c>
       <c r="T114" t="str">
-        <v/>
+        <v>10.3390/land7010030</v>
       </c>
       <c r="U114" t="str">
-        <v/>
+        <v>Agriculture in Africa is not only exposed to climate change impacts but is also a source of greenhouse gases (GHGs). While GHG emissions in Africa are relatively minimal in global dimensions, agriculture in the continent constitutes a major source of GHG emissions. In Ghana, agricultural emissions are accelerating, mainly due to ensuing deforestation of which smallholder cocoa farming is largely associated. The sector is also bedevilled by soil degradation, pests, diseases and poor yields coupled with poor agronomic practices. Climate Smart Agriculture (CSA) thus offers a way to reduce the sector's GHG emissions and to adapt the sector to the adverse impacts of climate change. This study assesses the potential of CSA vis-à-vis conventional cocoa systems to enhance production, mitigate and/or remove GHG emissions and build resilience, in addition to understanding key determinants influencing CSA practices.</v>
       </c>
       <c r="V114" t="str">
-        <v/>
+        <v>climate smart agriculture, resilience, carbon balance, cocoa, mitigation, Ghana, Ex-ACT, agroforestry</v>
       </c>
     </row>
     <row r="115" xml:space="preserve">
@@ -10682,13 +10682,13 @@
         <v>Recommends better infrastructure (roads, rail), finance and insurance tools, and conflict mitigation strategies to protect trader resilience.</v>
       </c>
       <c r="T115" t="str">
-        <v/>
+        <v>10.1108/JADEE-08-2023-0214</v>
       </c>
       <c r="U115" t="str">
-        <v/>
+        <v>The study examines five exogenous shocks: climate, violence, price hikes, spoilage and the COVID-19 lockdown, and analyzes the association between these shocks and trader characteristics, reflecting trader vulnerability. Using primary survey data on 1,100 Nigerian maize traders for 2021 (controlling for shocks in 2017), the researchers use probit models to estimate the probabilities of experiencing climate, violence, disease and cost shocks associated with trader characteristics (gender, size and region) and to estimate the probability of vulnerability (experiencing severe impacts). Traders are prone to experiencing more than one shock, which increases the intensity of the shocks, with price shocks often accompanied by violence, climate and COVID-19 shocks.</v>
       </c>
       <c r="V115" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="116" xml:space="preserve">
@@ -10766,13 +10766,13 @@
         <v>The framework is proposed as a tool for CGIAR and national programs to guide breeding, agronomy, and policy strategies for long-term climate resilience planning.</v>
       </c>
       <c r="T116" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2022.103508</v>
       </c>
       <c r="U116" t="str">
-        <v/>
+        <v>Given the significance of climate change impacts on farming communities, large investments are made by research and development actors to adapt agricultural systems. A data-driven approach is required to guide these investments. In the African Great Lakes Region (GLR), root, tuber and banana (RT&amp;B) crops are vital for smallholder farming systems, but little is known about strategies to mitigate climate change impacts. The objective was to develop a spatial prioritisation and targeting framework based on the risk of climate-related impacts to guide research investments in climate-smart agriculture for RT&amp;B crops in the GLR. The framework is based on crop-specific socio-agroecological homologues (SAHs), defined as clusters of geographies with broadly similar risks of climate-change related impacts, determined by hazard, exposure, and vulnerability. Four SAHs were identified for banana, potato and sweetpotato, and five for cassava. For each crop, SAHs were prioritised for investment based on the level of risk. Scenario analysis showed that drought-tolerant varieties would increase banana suitability from 0.30 to 0.47 under baseline conditions and from 0.54 to 0.71 under future climates.</v>
       </c>
       <c r="V116" t="str">
-        <v/>
+        <v>Climate change adaptation, Root tuber and banana crops, African Great Lakes Region, Spatial prioritisation, Socio-agroecological homologues, Risk assessment, Climate-smart agriculture</v>
       </c>
     </row>
     <row r="117" xml:space="preserve">
@@ -10856,13 +10856,13 @@
 Contributes to empirical data gaps on cocoa heat tolerance</v>
       </c>
       <c r="T117" t="str">
-        <v/>
+        <v>10.1016/j.envexpbot.2022.105052</v>
       </c>
       <c r="U117" t="str">
-        <v/>
+        <v>Shade is one of the recommended management solutions to mitigate the effects of heat stress, which is a major challenge for cocoa production globally. Nevertheless, there are limited studies to verify this hypothesis. The study evaluated the effects of heat and shade on cocoa physiology using experimental plots with six-month old potted seedlings in a randomized complete block design. Infrared heaters were applied for one month to increase leaf temperatures by an average of 5-7°C (heat treatment) compared with no heat (unheated treatments), and shaded plants were placed under a shade net removing 60% of the light compared with no shade (sun treatments). Plants under heat treatments in sun and in shade showed severe reduction in photosynthesis. Measurements of chlorophyll fluorescence and photosynthetic light response curves indicated that heat caused damages at photosystem II and additionally resulted in lower rates of maximal photosynthesis. Heat treatments resulted in decreased concentrations of chlorophyll and changed pigment composition, reduced specific leaf areas, and plant biomass. While shade may benefit cocoa seedlings, the results indicate that the positive effects may not be sufficient to counteract the negative effects of increased temperatures on cocoa physiology.</v>
       </c>
       <c r="V117" t="str">
-        <v/>
+        <v>shade, cocoa (plant), heat, Stomatal conductance, water potential, photosynthesis, ghana</v>
       </c>
     </row>
     <row r="118" xml:space="preserve">
@@ -10944,13 +10944,13 @@
 Data used to guide donor incorporation into breeding pipelines for SSA.</v>
       </c>
       <c r="T118" t="str">
-        <v/>
+        <v>10.2135/cropsci2012.09.0545</v>
       </c>
       <c r="U118" t="str">
-        <v/>
+        <v>Low maize (Zea mays L.) yields and the impacts of climate change on maize production highlight the need to improve yields in eastern and southern Africa. Climate projections suggest higher temperatures within drought-prone areas. Research in model species suggests that tolerance to combined drought and heat stress is genetically distinct from tolerance to either stress alone, but this has not been confirmed in maize. In this study we evaluated 300 maize inbred lines testcrossed to CML539. Experiments were conducted under optimal conditions, reproductive stage drought stress, heat stress, and combined drought and heat stress. Lines with high levels of tolerance to drought and combined drought and heat stress were identified. Significant genotype × trial interaction and very large plot residuals were observed; consequently, the repeatability of individual managed stress trials was low. Tolerance to combined drought and heat stress in maize was genetically distinct from tolerance to individual stresses, and tolerance to either stress alone did not confer tolerance to combined drought and heat stress. This finding has major implications for maize drought breeding. Many current drought donors and key inbreds used in widely-grown African hybrids were susceptible to drought stress at elevated temperatures.</v>
       </c>
       <c r="V118" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="119" xml:space="preserve">
@@ -11034,13 +11034,13 @@
 Suggests targeting of strategies based on household type rather than blanket promotion</v>
       </c>
       <c r="T119" t="str">
-        <v/>
+        <v>10.1007/s10113-015-0838-6</v>
       </c>
       <c r="U119" t="str">
-        <v/>
+        <v>The paper examines adaptation strategies to reduce smallholder farmers' vulnerability to climate variability in West Africa, exploring linkages between agricultural adaptation strategies (crop diversity, soil and water conservation, trees on farm, small ruminants, improved crop varieties, fertilizers), food security, farm household characteristics and farm productivity in three contrasting agro-ecological sites (Burkina Faso, Ghana and Senegal). The study found that differences in land area per capita and land productivity largely explained variation in food security across sites, and distinguished four household types (subsistence, diversified, extensive, intensified) based on land size and market orientation, with contrasting levels of food security and agricultural adaptation strategies.</v>
       </c>
       <c r="V119" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="120" xml:space="preserve">
@@ -11132,13 +11132,13 @@
 Strong emphasis on the need for climate justice and support to smallholders who contribute least to climate change but are most affected.</v>
       </c>
       <c r="T120" t="str">
-        <v/>
+        <v>10.1016/j.cosust.2014.07.002</v>
       </c>
       <c r="U120" t="str">
-        <v/>
+        <v>The 'sustainable intensification' (SI) approach and 'climate-smart agriculture' (CSA) are highly complementary. SI is an essential means of adapting to climate change, also resulting in lower emissions per unit of output. With its emphasis on improving risk management, information flows and local institutions to support adaptive capacity, CSA provides the foundations for incentivizing and enabling intensification. But adaptation requires going beyond a narrow intensification lens to include diversified farming systems, local adaptation planning, building responsive governance systems, enhancing leadership skills, and building asset diversity. While SI and CSA are crucial for global food and nutritional security, they are only part of a multi-pronged approach, that includes reducing consumption and waste, building social safety nets, facilitating trade, and enhancing diets.</v>
       </c>
       <c r="V120" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="121" xml:space="preserve">
@@ -11210,13 +11210,13 @@
         <v>Data collected over 5 years; emphasizes need for conserving submontane forests and promoting less destructive agroforestry practices.</v>
       </c>
       <c r="T121" t="str">
-        <v/>
+        <v>10.1016/j.ecolind.2019.105741</v>
       </c>
       <c r="U121" t="str">
-        <v/>
+        <v>The conservation and sustainable management of biodiversity requires an understanding of the biotic and abiotic factors that condition the presence and survival of organisms in natural habitats. The global distribution and ecological hypersensitivity of pteridophytes have made them ideal candidates for studying the impact of biotic and abiotic factors on levels of biodiversity. This study aims to determine the effect of vegetation cover, human disturbance, and climatic factors on the distribution and diversity of pteridophytes in Togo with a view to guide conservation efforts. Our data comprises 130 plots of 500 m2 representing all ecological zones of the country, complemented by several opportunistic collections. After determining the patterns of pteridophyte distribution, multivariate analysis of variance and the calculation of diversity indicators made it possible to determine the influence of the factors studied. Submontane forests concentrate 90% of the local pteridophyte species in Togo. Humidity, insolation and disturbance are the main drivers of pteridophyte presence. Human disturbances are more damaging to terrestrial pteridophyte species. Pteridophyte species are reliable indicators of conditions of their habitat in Togo.</v>
       </c>
       <c r="V121" t="str">
-        <v/>
+        <v>climate change, vulnerability, protected areas, togo, west africa, biodiversity conservation, nature conservation, pteridophyta</v>
       </c>
     </row>
     <row r="122" xml:space="preserve">
@@ -11294,13 +11294,13 @@
         <v>CBA can mobilize youth and women, as in India, and influence policy reforms. The article argues for procedural justice and long-term institutional embedding of adaptation knowledge rather than one-off projects.</v>
       </c>
       <c r="T122" t="str">
-        <v/>
+        <v>10.1080/17565529.2014.965654</v>
       </c>
       <c r="U122" t="str">
-        <v/>
+        <v>Climate change creates widespread risks for food production. As climate impacts are often locally specific, it is imperative that large-scale initiatives to support smallholder farmers consider local priorities and integrate lessons from successful autonomous adaptation efforts. This article explores how large-scale programmes for smallholder adaptation to climate change might link effectively with community-led adaptation initiatives. Drawing on experiences in Bangladesh, Mozambique, Uganda and India, this article identifies key success factors and barriers for considering local priorities, capacities and lessons in large-scale adaptation programmes. It highlights the key roles of extension services and farmers' organizations as mechanisms for linking between national-level and community-level adaptation, and a range of other success factors which include participative and locally driven vulnerability assessments, tailoring of adaptation technologies to local contexts, mapping local institutions and working in partnership across institutions. Barriers include weak governance, gaps in the regulatory and policy environment, high opportunity costs, low literacy and underdeveloped markets. The article concludes that mainstreaming climate adaptation into large-scale agricultural initiatives requires not only integration of lessons from community-based adaptation, but also the building of inclusive governance to ensure smallholders can engage with those policies and processes affecting their vulnerability.</v>
       </c>
       <c r="V122" t="str">
-        <v/>
+        <v>climate change, community-based adaptation, mainstreaming, agriculture, adaptation</v>
       </c>
     </row>
     <row r="123" xml:space="preserve">
@@ -11378,13 +11378,13 @@
         <v>Significant gap between CSAâ€™s conceptual framework and its operationalization; stresses the need for institutional innovation to complement technical CSA solutions.</v>
       </c>
       <c r="T123" t="str">
-        <v/>
+        <v>10.3390/su10061990</v>
       </c>
       <c r="U123" t="str">
-        <v/>
+        <v>Climate-smart agriculture (CSA) is increasingly seen as a promising approach to feed the growing world population under climate change. The review explored how institutional perspectives are reflected in the CSA literature. In total, 137 publications were analyzed using institutional analysis framework, of which 55.5% make specific reference to institutional dimensions. While the CSA concept encompasses three pillars (productivity, adaptation, and mitigation), the literature has hardly addressed them in an integrated way. Mitigation was predominantly addressed in high-income countries, while productivity and adaptation were priorities for middle and low-income countries.</v>
       </c>
       <c r="V123" t="str">
-        <v/>
+        <v>climate-smart agriculture, institutions, adaptation, mitigation, systematic review</v>
       </c>
     </row>
     <row r="124" xml:space="preserve">
@@ -11478,13 +11478,13 @@
 Focused on research-for-development and donor alignment in CSA inv</v>
       </c>
       <c r="T124" t="str">
-        <v/>
+        <v>10.1016/j.agsy.2018.09.009</v>
       </c>
       <c r="U124" t="str">
-        <v/>
+        <v>Climate-smart agriculture (CSA) is widely promoted as an approach for reorienting agricultural development under the realities of climate change. Prioritising research-for-development activities is crucial, given the need to utilise scarce resources as effectively as possible. However, no framework exists for assessing and comparing different CSA research investments. Several aspects make it challenging to prioritise CSA research, including its multi-dimensional nature (productivity, adaptation and mitigation), the uncertainty surrounding many climate impacts, and the scale and temporal dependencies that may affect the benefits and costs of CSA adoption.</v>
       </c>
       <c r="V124" t="str">
-        <v/>
+        <v>Adaptation, Agriculture, Climate change, Mitigation, Research</v>
       </c>
     </row>
     <row r="125" xml:space="preserve">
@@ -11572,13 +11572,13 @@
 Calls for complementary pest control methods alongside biocontrol</v>
       </c>
       <c r="T125" t="str">
-        <v/>
+        <v>10.1002/ps.6478</v>
       </c>
       <c r="U125" t="str">
-        <v/>
+        <v>The southern armyworm (SAW) Spodoptera eridania (Stoll) (Lepidoptera: Noctuidae) is native to the tropical Americas where the pest can feed on more than 100 plant species. SAW was recently detected in West and Central Africa, feeding on various crops including cassava, cotton, amaranth and tomato. The current work was carried out to predict the potential spatial distribution of SAW and four of its co-evolved parasitoids at a global scale using the maximum entropy (Maxent) algorithm. SAW may not be a huge problem outside its native range (the Americas) for the time being, but may compromise crop yields in specific hotspots in coming years. The analysis of its potential distribution anticipates that the pest might easily migrate east and south from Cameroon and Gabon. The models used generally demonstrate that all the parasitoids considered are good candidates for the biological control of SAW globally, except they will not be able to establish in specific climates. The current paper discusses the potential role of biological control using parasitoids as a crucial component of a durable climate-smart integrated management of SAW to support decision making in Africa and in other regions of bioclimatic suitability.</v>
       </c>
       <c r="V125" t="str">
-        <v/>
+        <v>biological control, climate change, decision support, foresight analysis, southern armyworm</v>
       </c>
     </row>
     <row r="126" xml:space="preserve">
@@ -11666,13 +11666,13 @@
 Intended as an actionable strategy, not a research paper.</v>
       </c>
       <c r="T126" t="str">
-        <v/>
+        <v>Note: Published article found is from 2024, not 2022. DOI: 10.3390/su16156652</v>
       </c>
       <c r="U126" t="str">
-        <v/>
+        <v>The paper discusses how the One Health concept has evolved from its initial focus on zoonotic diseases to a broader framework addressing interconnected terrestrial and aquatic ecosystems. The paper describes Climate-Smart One Health (CS-OH) and Climate-Smart Integrated Pest Management (CS-IPM) approaches.</v>
       </c>
       <c r="V126" t="str">
-        <v/>
+        <v>Unable to locate 2022 version; 2024 version published with different DOI</v>
       </c>
     </row>
     <row r="127" xml:space="preserve">
@@ -11760,13 +11760,13 @@
 IITAâ€™s Biorisk Management Facility (BIMAF) acknowledged as key institutional supportâ€‹</v>
       </c>
       <c r="T127" t="str">
-        <v/>
+        <v>10.3390/insects12040273</v>
       </c>
       <c r="U127" t="str">
-        <v/>
+        <v>The fall armyworm (FAW), Spodoptera frugiperda has now become a pest of global importance. Its introduction and detection in Africa in 2016, and subsequent introduction and spread into Asia and Australia, has put several millions of food producers and maize farmers at risk. The present study was initiated to predict the habitats of high establishment potential of key parasitoids of FAW in South America, which might prove to be effective as classical biological control agents of FAW in regions where it is an invasive species under current and future climate scenarios. The prospective parasitoids are the following: Chelonus insularis, Cotesia marginiventris, Eiphosoma laphygmae, Telenomus remus and Trichogramma pretiosum. An adjusted procedure of a machine-learning algorithm, the maximum entropy (Maxent), was applied for the modeling experiments. Model predictions showed particularly high establishment potential of the five hymenopteran parasitoids in areas that are heavily affected by FAW (like the coastal belt of West Africa from Côte d'Ivoire to Nigeria, the Congo basin to Eastern Africa, Eastern, Southern and Southeastern Asia and some portions of Eastern Australia) and those of potential invasion risks (western &amp; southern Europe).</v>
       </c>
       <c r="V127" t="str">
-        <v/>
+        <v>Spodoptera Frugiperda, Climate Change, Pest Management, Biological Control, Machine Learning, Decision Support, Parasitoids</v>
       </c>
     </row>
     <row r="128" xml:space="preserve">
@@ -11858,13 +11858,13 @@
 Clear linkages to IITA-led innovations like the Farmer Interface Application (FIA)</v>
       </c>
       <c r="T128" t="str">
-        <v/>
+        <v>10.1016/j.cois.2022.100961</v>
       </c>
       <c r="U128" t="str">
-        <v/>
+        <v>IPM 3.0 relies on 3 pillars: farmer empowerment, nature-based solutions, integrative practices. It encompasses interactions occurring at cropping system/landscape and across trophic levels. Each year, Africa loses half of its harvest to pests (insects, pathogens, nematodes, weeds). Pest management in major cropping systems has long been dominated by chemical pesticides in Africa. Smallholder farmers have perceived pesticides as insurance to protect their crops. Hence, overuse of pesticides has been constantly increasing. Although African countries have a number of pesticide-related policies, they are inadequately implemented. However, significant investment has been made on integrated pest management (IPM) innovations in recent decades.</v>
       </c>
       <c r="V128" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="129" xml:space="preserve">
@@ -11946,13 +11946,13 @@
 Recommends continued support for digitization of African herbaria and database integration</v>
       </c>
       <c r="T129" t="str">
-        <v/>
+        <v>10.1186/s12915-017-0356-8</v>
       </c>
       <c r="U129" t="str">
-        <v/>
+        <v>Understanding the patterns of biodiversity distribution and what influences them is a fundamental pre-requisite for effective conservation and sustainable utilisation of biodiversity. Such knowledge is increasingly urgent as biodiversity responds to the ongoing effects of global climate change. Nowhere is this more acute than in species-rich tropical Africa, where so little is known about plant diversity and its distribution. In this paper, we use RAINBIO – one of the largest mega-databases of tropical African vascular plant species distributions ever compiled – to address questions about plant and growth form diversity across tropical Africa. The filtered RAINBIO dataset contains 609,776 georeferenced records representing 22,577 species. Growth form data are recorded for 97% of all species.</v>
       </c>
       <c r="V129" t="str">
-        <v/>
+        <v>Botanical exploration, Digitization, Floristic patterns, Herbarium specimens, Plant growth form, Species richness, Tropical forests</v>
       </c>
     </row>
     <row r="130" xml:space="preserve">
@@ -12042,13 +12042,13 @@
 IITA affiliation brings institutional weight to practical policy recommendations</v>
       </c>
       <c r="T130" t="str">
-        <v/>
+        <v>10.3389/fagro.2022.957011</v>
       </c>
       <c r="U130" t="str">
-        <v/>
+        <v>The paper discusses how recent discourse on food sovereignty emphasizes democracy in determining localized food systems and culturally appropriate food while leaning on sustainable agricultural practices such as organic agriculture, ecological intensification, agroecology, nature-based solutions, and regenerative agriculture. Sustainable agricultural practices focus on managing land without synthetic fertilizers and pesticides while improving soil and land health. However, the authors question the practicalities of food activism and relying entirely on nature while yields remain very low in much of sub-Saharan Africa.</v>
       </c>
       <c r="V130" t="str">
-        <v/>
+        <v>agroecology, regenerative agriculture, rainfed conditions, small farms, food systems, diets, activism, choices</v>
       </c>
     </row>
     <row r="131" xml:space="preserve">
@@ -12136,13 +12136,13 @@
 Potentially replicable across other smallholder-dominated regions in SSA</v>
       </c>
       <c r="T131" t="str">
-        <v/>
+        <v>10.1007/s10098-022-02272-7</v>
       </c>
       <c r="U131" t="str">
-        <v/>
+        <v>Models that enable the estimation of crop yields and greenhouse gas (GHG) emissions concurrently are still lacking. This study develops a biophysical modelling framework encompassing a farm typology, a crop model, and a farm-focused GHG calculator to assess productivity (crop yield) and GHG emissions of crop management practices concurrently. Using this modelling framework, the study developed cropping system scenarios based on the concept of conservation agriculture (CA) to identify and design cropping systems that deliver ecological intensification for different farm types. All farm types were found to be net sources of GHG with cropping system inefficiency across all farm types. However, the integration of CA-based practices independently and in combination into farm-type maize-based cropping systems showed significant potential in improving crop yields and lowering GHG emissions across all farm types.</v>
       </c>
       <c r="V131" t="str">
-        <v/>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="132" xml:space="preserve">
@@ -12228,13 +12228,13 @@
 Proposes molecular markers for future screening of drought tolerance linked to PGR use</v>
       </c>
       <c r="T132" t="str">
-        <v/>
+        <v>10.1111/ppl.14605</v>
       </c>
       <c r="U132" t="str">
-        <v/>
+        <v>As global climate change intensifies, the occurrence and severity of various abiotic stresses increases. Plants synthesize or accumulate various plant growth regulators (PGRs), including phytohormones, neurotransmitters, gasotransmitters, and polyamines, which present promising sustainable green chemical strategies to adapt or tolerate stress conditions. This comprehensive review examines how PGRs function as green chemical tools for enhancing drought stress tolerance in crops. The paper discusses the molecular mechanisms, signaling pathways, and practical applications of PGRs in improving plant resilience to water deficit. The findings provide insights for developing sustainable agricultural strategies that utilize natural plant compounds to combat drought stress in the context of climate change.</v>
       </c>
       <c r="V132" t="str">
-        <v/>
+        <v>plant growth regulators, drought stress tolerance, climate change, phytohormones, green chemistry, abiotic stress, crop resilience, sustainable agriculture, water stress, plant adaptation</v>
       </c>
     </row>
     <row r="133" xml:space="preserve">
@@ -12322,13 +12322,13 @@
 Strong argument for re-centering neglected legumes in food systems</v>
       </c>
       <c r="T133" t="str">
-        <v/>
+        <v>10.3389/fpls.2022.782140</v>
       </c>
       <c r="U133" t="str">
-        <v/>
+        <v>This paper discusses dietary diversification and incorporation of resilient crop species such as under-exploited leguminous species referred to as orphan, minor, or underutilized into food systems to ensure food and protein security in many parts of Africa. The study examines the potential of neglected and underutilized legumes to contribute to improved nutrition, income generation, and climate resilience in Sub-Saharan Africa. The research reviews the nutritional profiles, agronomic characteristics, and socioeconomic benefits of various orphan legumes, highlighting opportunities for their integration into modern agricultural systems. The findings emphasize the need for increased research investment, policy support, and value chain development to unlock the potential of these crops for sustainable food security.</v>
       </c>
       <c r="V133" t="str">
-        <v/>
+        <v>orphan legumes, underutilized crops, food security, nutrition security, Sub-Saharan Africa, dietary diversification, protein security, climate resilience, legumes, agricultural biodiversity</v>
       </c>
     </row>
     <row r="134" xml:space="preserve">
@@ -12416,13 +12416,13 @@
 Suggests insect farming as part of African climate resilience and nutrition strategies</v>
       </c>
       <c r="T134" t="str">
-        <v/>
+        <v>10.1371/journal.pone.0222941</v>
       </c>
       <c r="U134" t="str">
-        <v/>
+        <v>This paper focuses on integrating temperature-dependent life table data with the Insect Life Cycle Model (ILCYM) to predict the potential distribution of the edible cricket species Scapsipedus icipe in Africa. The study collected temperature-dependent life table data under controlled laboratory conditions and incorporated these data into ILCYM to forecast suitable habitats for mass rearing of this edible insect. The research demonstrates how insect phenology models can inform the development of climate-smart insect farming systems. The findings have implications for promoting edible insects as sustainable protein sources and for understanding how climate affects insect distribution and production potential across African landscapes.</v>
       </c>
       <c r="V134" t="str">
-        <v/>
+        <v>insect life cycle modeling, temperature-dependent, edible insects, cricket, ILCYM, species distribution, climate suitability, entomology, sustainable protein, Africa</v>
       </c>
     </row>
     <row r="135" xml:space="preserve">
@@ -12514,13 +12514,13 @@
 Data deposited at IITA repository and supported by the STMA project and WASCAL</v>
       </c>
       <c r="T135" t="str">
-        <v/>
+        <v>10.3390/genes11091054</v>
       </c>
       <c r="U135" t="str">
-        <v/>
+        <v>The study assessed the genetic diversity and population structure of a maize panel of 208 accessions, comprising landrace gene pools from Burkina Faso (58), Ghana (43), and Togo (89), together with reference populations (18) from the maize improvement program of the International Institute of Tropical Agriculture (IITA). The genomic analysis reveals the variability within West African maize landraces and their potential for genetic enhancement. The research identifies distinct genetic clusters and patterns of diversity that can inform breeding strategies for developing climate-resilient maize varieties adapted to diverse agroecological zones in West Africa. The findings provide valuable insights for conserving maize genetic resources and utilizing landrace diversity in modern breeding programs.</v>
       </c>
       <c r="V135" t="str">
-        <v/>
+        <v>maize, landraces, genomic analysis, genetic diversity, West Africa, Sahel, crop improvement, genetic enhancement, population structure, breeding</v>
       </c>
     </row>
     <row r="136" xml:space="preserve">
@@ -12608,13 +12608,13 @@
 Study underscores missed opportunities when farmer knowledge is excluded from intervention design</v>
       </c>
       <c r="T136" t="str">
-        <v/>
+        <v>10.1016/j.jssas.2024.06.003</v>
       </c>
       <c r="U136" t="str">
-        <v/>
+        <v>The study evaluated farmers' knowledge of soil quality and yield assessment among cassava farmers in southwestern Nigeria, collecting data on farmers' demography, farming experience, criteria for selecting sites for cassava cultivation, methods of yield prediction, and agronomic knowledge related to climate change and soil fertility decline. Farmers use a combination of soil and vegetation-based criteria to assess soil quality, with soil drainage, colour, and depth ranking as the most used soil-based criteria. The research highlights the value of local knowledge in agricultural decision-making and explores how farmers' indigenous assessment methods align with scientific soil quality indicators. The findings have implications for developing participatory approaches to soil management in cassava production systems.</v>
       </c>
       <c r="V136" t="str">
-        <v/>
+        <v>cassava, soil quality, farmer knowledge, indigenous knowledge, root yield, Nigeria, cropping systems, soil assessment, agricultural practices, local expertise</v>
       </c>
     </row>
     <row r="137" xml:space="preserve">
@@ -12698,13 +12698,13 @@
 Highlights digital inequality and the intersectionality of gender with age, class, literacy, and disability</v>
       </c>
       <c r="T137" t="str">
-        <v/>
+        <v>10.3390/su15010190</v>
       </c>
       <c r="U137" t="str">
-        <v/>
+        <v>This paper advances a gender equality and social inclusion (GESI) framework for incorporating climate information services (CIS), which is now becoming central due to the ongoing climate change and climate variability. The framework addresses the need to ensure that climate information services are accessible, relevant, and beneficial to all segments of society, particularly marginalized groups including women, youth, and other vulnerable populations. The study examines barriers to equitable access to climate information and proposes strategies for integrating GESI principles into the design, delivery, and evaluation of CIS. The research provides practical guidance for climate service providers, policymakers, and development practitioners seeking to enhance the inclusiveness and effectiveness of climate adaptation initiatives.</v>
       </c>
       <c r="V137" t="str">
-        <v/>
+        <v>gender equality, social inclusion, GESI, climate information services, climate adaptation, vulnerability, accessibility, marginalized groups, climate variability, equity</v>
       </c>
     </row>
     <row r="138" xml:space="preserve">
@@ -12792,13 +12792,13 @@
 Avelino and van Asten are long-standing contributors to coffee agroecology and systems disease management</v>
       </c>
       <c r="T138" t="str">
-        <v/>
+        <v>10.1080/17429145.2019.1643934</v>
       </c>
       <c r="U138" t="str">
-        <v/>
+        <v>Shade effects on coffee diseases are ambiguous because they vary depending on the season and environment. Using Coffee Leaf Rust (CLR) as an example, we demonstrate relationships between the environment and shading systems and their effects on disease intensity. The study explores direct, indirect and interactive effects of the altitude and coffee shading system on microclimatic indicators and CLR. The research provides insights into how altitude and microclimate interact with different shading systems to influence coffee disease dynamics, offering guidance for developing climate-adapted coffee agroforestry systems that balance disease management with other production objectives.</v>
       </c>
       <c r="V138" t="str">
-        <v/>
+        <v>coffee, coffee leaf rust, altitude, microclimate, shading systems, agroforestry, disease management, climate adaptation, environmental interactions, tropical crops</v>
       </c>
     </row>
     <row r="139" xml:space="preserve">
@@ -12986,13 +12986,13 @@
 Important case study for climate-resilient agroforestry planning in West Africa</v>
       </c>
       <c r="T140" t="str">
-        <v/>
+        <v>10.1016/j.heliyon.2023.e20199</v>
       </c>
       <c r="U140" t="str">
-        <v/>
+        <v>This study aimed to map the suitable areas for domestication and conservation of Ricinodendron heudelotii under current and future climate conditions in Benin. Ricinodendron heudelotii (Baill.) Heckel is an important nutraceutical reservoir. Occurrence data were recorded and combined with the environmental layers of two climatic scenarios (optimistic RCP 4.5 and pessimistic RCP 8.5) following the biodiversity modelling approach (biomod2). Currently, about four percent (5082 Km²) of the country's area mainly located in the sub-humid and the humid zones were potentially suitable for R. heudelotii. Under future climatic conditions the potentially suitable areas were mainly in the sub-humid zone, but almost all the highly suitable areas located in the humid zone will become medium suitable areas by 2055-time horizon.</v>
       </c>
       <c r="V140" t="str">
-        <v/>
+        <v>habitat distribution, species distribution modeling, Ricinodendron heudelotii, climate change, Benin, West Africa, conservation, biomod2, RCP scenarios, range shift</v>
       </c>
     </row>
     <row r="141" xml:space="preserve">
@@ -13078,13 +13078,13 @@
 Supported by CGIAR-PIM and Gates Foundation</v>
       </c>
       <c r="T141" t="str">
-        <v/>
+        <v>10.1002/fes3.172</v>
       </c>
       <c r="U141" t="str">
-        <v/>
+        <v>This study undertakes an ex-ante evaluation of the effects of alternative technology and policy options on soybean supply and demand in sub-Saharan Africa (SSA) to 2050. The research shows that a combination of promising innovations affecting the soybean value chain across SSA would be needed to close the soybean demand gap in SSA by 2050 under a drier future climate. The analysis examines various scenarios including improved varieties, enhanced agronomic practices, and policy interventions to assess their potential impacts on soybean production, consumption, and trade. The findings provide guidance for prioritizing investments in soybean research and development to enhance food and nutrition security in the region.</v>
       </c>
       <c r="V141" t="str">
-        <v/>
+        <v>soybean, ex-ante evaluation, sub-Saharan Africa, agricultural innovation, food security, climate change, crop modeling, value chain, technology adoption, policy analysis</v>
       </c>
     </row>
     <row r="142" xml:space="preserve">
@@ -13148,13 +13148,13 @@
         <v>Strong physiological focus with clear implications for adaptation but not broader food system themes.</v>
       </c>
       <c r="T142" t="str">
-        <v/>
+        <v>10.1017/S0021859621000617</v>
       </c>
       <c r="U142" t="str">
-        <v/>
+        <v>Field studies were conducted in 2017 and 2018 seasons in two agroecologies (Angonia and Ruace) in Mozambique to evaluate the effects of Bradyrhizobium diazoefficiens strain USDA110 (formerly known as Bradyrhizobium japonicum) inoculant, nitrogen and phosphorus on nodulation, physiology and yield of non-promiscuous (Safari) and promiscuous (TGx 1740-2F) soybean varieties. Data on transpiration, photosynthesis, leaf area index, radiation interception and WUE from the beginning of flowering to maturity were collected. Photosynthesis rate and water-use efficiency (WUE) were distinct with variety, growth stages and inputs within agroecologies. At one site in 2017, inoculated soybean photosynthesized more at 22.8 μmol/m2/s leading to better WUE of 3.6 that corresponded to 2894 kg/ha yield. Overall, soybean WUE was higher when inoculated than N-treated, while P application yielded better. Nitrogen is a key element in photosynthesis process as it affects leaf chloroplasts size, number and composition, and inoculation promotes BNF process that avails more N for plant uptake resulting in better leaf development.</v>
       </c>
       <c r="V142" t="str">
-        <v/>
+        <v>Soybean, Bradyrhizobium diazoefficiens, Inoculant, Nitrogen, Phosphorus, Photosynthesis, Water-use efficiency, Biological nitrogen fixation, Mozambique</v>
       </c>
     </row>
     <row r="143" xml:space="preserve">
@@ -13242,13 +13242,13 @@
 Authors stress that mitigation success requires legally binding tenure systems, simplified rules, and full local participation.</v>
       </c>
       <c r="T143" t="str">
-        <v/>
+        <v>10.1080/00207233.2017.1347358</v>
       </c>
       <c r="U143" t="str">
-        <v/>
+        <v>This paper focuses on developing a participatory model for forest governance and REDD+ implementation in Central Africa to enhance stakeholder involvement in carbon markets. The study examines current forest governance structures in the region and proposes mechanisms to increase participation of local communities, indigenous peoples, and other stakeholders in REDD+ programs. The research identifies barriers to effective stakeholder engagement in carbon markets and presents strategies for creating more inclusive and equitable forest governance systems that can deliver both climate mitigation and sustainable development outcomes in Central African countries.</v>
       </c>
       <c r="V143" t="str">
-        <v/>
+        <v>forest governance, REDD+, Central Africa, participatory model, carbon markets, stakeholder involvement, climate mitigation, community engagement, sustainable development, forest conservation</v>
       </c>
     </row>
     <row r="144" xml:space="preserve">
@@ -13326,13 +13326,13 @@
 It emphasizes the interplay between environmental change and biological invasion.</v>
       </c>
       <c r="T144" t="str">
-        <v/>
+        <v>10.1111/mec.13762</v>
       </c>
       <c r="U144" t="str">
-        <v/>
+        <v>The application of approximate Bayesian computation (ABC) to sequence data from four nuclear and one mitochondrial marker revealed that African populations of Ae. aegypti best fit a demographic model of lineage diversification, historical admixture and recent population structuring. This population history is consistent with the effects of forest fragmentation and expansion driven by Pleistocene climatic change. By increasing genetic diversity and forming novel allelic combinations, divergence and historical admixture within Africa could have provided the adaptive potential needed for the successful worldwide spread of Ae. aegypti. The study demonstrates how historical environmental change in Africa shaped the evolutionary trajectory of this important disease vector.</v>
       </c>
       <c r="V144" t="str">
-        <v/>
+        <v>Aedes aegypti, mosquito, population genetics, Africa, climatic change, Pleistocene, admixture, disease vector, evolutionary history, genetic diversity</v>
       </c>
     </row>
     <row r="145" xml:space="preserve">
@@ -13418,13 +13418,13 @@
 Supports policies promoting nature-based solutions, especially in agriculture and land management.</v>
       </c>
       <c r="T145" t="str">
-        <v/>
+        <v>10.1038/s41467-023-39338-z</v>
       </c>
       <c r="U145" t="str">
-        <v/>
+        <v>Using second-order meta-analysis, we synthesized findings from 230 first-order meta-analyses comprising over 25,000 primary studies to assess global patterns and drivers of soil organic carbon (SOC) change in the Anthropocene. This comprehensive analysis examines how human activities and land management practices have affected SOC stocks worldwide. The study provides a global panorama of the impacts of human activities on soil carbon, identifying key drivers of SOC change and their implications for climate change mitigation and sustainable soil management. The findings offer critical insights for developing evidence-based policies to enhance soil carbon sequestration and soil health under changing environmental conditions.</v>
       </c>
       <c r="V145" t="str">
-        <v/>
+        <v>soil organic carbon, meta-analysis, Anthropocene, land management, carbon sequestration, soil health, climate change mitigation, global assessment, agricultural practices, ecosystem services</v>
       </c>
     </row>
     <row r="146" xml:space="preserve">
@@ -13502,13 +13502,13 @@
         <v>Highlights role of climate-smart agroforestry and pruning practices. Recommends careful selection of shade tree species to balance benefits and risks.</v>
       </c>
       <c r="T146" t="str">
-        <v/>
+        <v>10.1016/j.agrformet.2022.109199</v>
       </c>
       <c r="U146" t="str">
-        <v/>
+        <v>Shade effects on cocoa diseases are ambiguous because they vary depending on the season and environment. This study explores direct, indirect and interactive effects of altitude and coffee shading system on microclimatic indicators and coffee leaf rust (CLR). Key findings include that rainfall and proximity to shade trees influence cocoa health and productivity, and black pod disease in cocoa doubles under rainfall from 1400 to 1850 mm. The research demonstrates relationships between the environment and shading systems and their effects on disease intensity in cocoa agroforestry systems in Ghana, providing insights for climate-adapted cocoa production strategies.</v>
       </c>
       <c r="V146" t="str">
-        <v/>
+        <v>cocoa, climate variability, agroforestry, Ghana, crop health, productivity, black pod disease, shade management, rainfall, microclimates</v>
       </c>
     </row>
     <row r="147" xml:space="preserve">
@@ -13584,13 +13584,13 @@
         <v>The study is part of the CGIAR CCAFS program. It recommends clearer national frameworks for gender mainstreaming and budget tracking. Includes a 5-point grading rubric for gender integration in policy documents and a proposal for harmonized gender strategies across levels of governance.</v>
       </c>
       <c r="T147" t="str">
-        <v/>
+        <v>10.1007/s10584-019-02447-0</v>
       </c>
       <c r="U147" t="str">
-        <v/>
+        <v>The study analyzes the extent of gender integration in agricultural and natural resource policies in Uganda and Tanzania, examining how gender is budgeted for in implementation plans at district and lower governance levels. A total of 155 policy documents, development plans, and annual action plans from national, district, and sub-county/ward levels were reviewed. Results show that while there is increasing gender responsiveness in both countries, gender issues are still interpreted as 'women issues,' there is disharmony in gender mainstreaming across governance levels, budgeting for gender is not yet fully embraced by governments, and gender activities do not address structural inequalities. The paper provides recommendations for strengthening gender integration in climate and agricultural policies.</v>
       </c>
       <c r="V147" t="str">
-        <v/>
+        <v>gender mainstreaming, climate change policy, agriculture policy, natural resources, East Africa, Uganda, Tanzania, policy analysis, gender budgeting, governance</v>
       </c>
     </row>
     <row r="148" xml:space="preserve">
@@ -13668,13 +13668,13 @@
         <v>Study recommends gender mainstreaming in climate adaptation policies. Supported by AGRA, IDRC, CORAF/WECARD, and IITA.</v>
       </c>
       <c r="T148" t="str">
-        <v/>
+        <v>10.1080/23311932.2020.1743625</v>
       </c>
       <c r="U148" t="str">
-        <v/>
+        <v>This study assesses the impact of climate change (CC) adaptation on farm-level revenue among 500 soybean farmers randomly selected in three districts in Togo using endogenous switching regression method. The survey results indicate that only 40.37% of the women have adapted to CC against 59.62% of the men. Moreover, being member of farmer-based organization (FBO), access to credit and extension services, agricultural training of women are the main factors that increase the likelihood of adaptation. The gender-differentiated impact shows that women would earn more than men from adaptation, while losing compared to men if they do not take any adaptation actions. The loss from non-adapting to CC will increase by 0.268% of the soybean revenue.</v>
       </c>
       <c r="V148" t="str">
-        <v/>
+        <v>gender, climate change adaptation, soybean, farmers revenue, Togo, West Africa, agricultural economics, endogenous switching regression, women empowerment, extension services</v>
       </c>
     </row>
     <row r="149" xml:space="preserve">
@@ -13752,13 +13752,13 @@
         <v>Recommends integrating gender into climate finance and adaptive capacity-building. Gender-informed policies should support womenâ€™s knowledge, access, and innovation.</v>
       </c>
       <c r="T149" t="str">
-        <v/>
+        <v>10.1016/j.crsust.2023.100219</v>
       </c>
       <c r="U149" t="str">
-        <v/>
+        <v>This study examines the gender-responsive approaches to rapid climate warming among crop smallholder farmers in Nasarawa, Nigeria. Temperature data for 36 years was used to establish change and analyze gender-differentiated impacts of climate warming on smallholder farming communities. The research reveals how men and women farmers experience and respond differently to increasing temperatures and explores gender-specific adaptation strategies. The findings demonstrate the importance of incorporating gender considerations into climate adaptation planning and highlight how gender-responsive interventions can enhance the effectiveness of climate warming adaptation among smallholder farmers in Sub-Saharan Africa.</v>
       </c>
       <c r="V149" t="str">
-        <v/>
+        <v>gender, climate warming, smallholder farmers, adaptation, Nigeria, temperature change, gender-responsive, climate change, agricultural resilience, vulnerability</v>
       </c>
     </row>
     <row r="150" xml:space="preserve">
@@ -13840,13 +13840,13 @@
         <v>Coordinated by the International Society for Plant Pathology and supported by IITA and global institutions; structured around the Millennium Ecosystem Assessment framework; emphasizes need for multidisciplinary research and policy engagement.</v>
       </c>
       <c r="T150" t="str">
-        <v/>
+        <v>10.1094/PDIS-01-23-0166-FE</v>
       </c>
       <c r="U150" t="str">
-        <v/>
+        <v>Among the 33 (Ecoregion × Plant System) considered, 18 are assessed as in fair or poor health, and 20 as in declining health. Much of the observed state of plant health and its trends are driven by a combination of forces, including climate change, species invasions, and human management. This comprehensive global assessment examines the current status of plant health across major agricultural systems and ecoregions worldwide. The study synthesizes evidence from multiple sources to evaluate trends in crop diseases, pest pressures, and overall plant system resilience. The findings highlight the urgent need for integrated approaches to plant health management in the context of global environmental change.</v>
       </c>
       <c r="V150" t="str">
-        <v/>
+        <v>plant health, global assessment, crop diseases, climate change, pest management, species invasions, agricultural systems, ecoregions, plant pathology, food security</v>
       </c>
     </row>
     <row r="151" xml:space="preserve">
@@ -13924,13 +13924,13 @@
         <v>Includes quantitative BNF data and lists constraints and potential of each legume crop.</v>
       </c>
       <c r="T151" t="str">
-        <v/>
+        <v>10.3389/fsufs.2022.708124</v>
       </c>
       <c r="U151" t="str">
-        <v/>
+        <v>Orphan legumes have the potential to improve food and nutrition security in Sub-Saharan Africa (SSA) due to their cultural linkage with the regional food habits of the communities, nutritionally rich food, untapped genetic diversity, and adaptation to harsh climate conditions and poor marginal soils. This review examines the potential of indigenous African legume species that have been neglected by mainstream agricultural research and development. The paper discusses how these underutilized legumes can contribute to dietary diversification, climate resilience, and sustainable agricultural systems across SSA. It highlights opportunities for incorporating these crops into modern breeding programs and agricultural policies to enhance regional food and nutrition security.</v>
       </c>
       <c r="V151" t="str">
-        <v/>
+        <v>orphan legumes, food security, nutrition security, Sub-Saharan Africa, underutilized crops, genetic diversity, climate adaptation, indigenous crops, dietary diversification, sustainable agriculture</v>
       </c>
     </row>
     <row r="152" xml:space="preserve">
@@ -14017,13 +14017,13 @@
 Limited progress in applying genomics to orphan crops and marginalized regions.</v>
       </c>
       <c r="T152" t="str">
-        <v/>
+        <v>10.1111/pbi.12467</v>
       </c>
       <c r="U152" t="str">
-        <v/>
+        <v>Agriculture is now facing the 'perfect storm' of climate change, increasing costs of fertilizer and rising food demands from a larger and wealthier human population. Genomics offers unprecedented opportunities to increase crop yield, quality and stability of production through advanced breeding strategies. This paper argues that genomic approaches can enhance the resilience of major crops to climate variability and increase the productivity and range of minor crops to diversify the food supply. The authors discuss how modern genomic tools, including marker-assisted selection, genomic selection, and gene editing, can accelerate the development of climate-resilient crop varieties to ensure global food security in the face of environmental change.</v>
       </c>
       <c r="V152" t="str">
-        <v/>
+        <v>genomics, climate change, agricultural intensification, crop improvement, breeding, food security, climate resilience, crop yield, genetic diversity, adaptation</v>
       </c>
     </row>
     <row r="153" xml:space="preserve">
@@ -14115,13 +14115,13 @@
 The IITA Aflasafe plant in Ibadan, Nigeria, is a key manufacturing and dissemination hub.</v>
       </c>
       <c r="T153" t="str">
-        <v/>
+        <v>10.3920/WMJ2016.2130</v>
       </c>
       <c r="U153" t="str">
-        <v/>
+        <v>Carefully selected atoxigenic genotypes in biological control (biocontrol) formulations efficiently reduce aflatoxin contamination of crops when applied prior to flowering in the field. This review discusses the current status of biocontrol for aflatoxin mitigation in Africa and examines potential challenges posed by climate change. The paper analyzes how environmental factors, particularly those influenced by climate variability, affect the efficacy of atoxigenic biocontrol agents. It provides insights into adapting biocontrol strategies to maintain effectiveness under changing climatic conditions across diverse African agroecologies.</v>
       </c>
       <c r="V153" t="str">
-        <v/>
+        <v>aflatoxin, biological control, biocontrol, atoxigenic, climate change, Africa, crop contamination, food safety, mycotoxin, fungal control</v>
       </c>
     </row>
     <row r="154" xml:space="preserve">
@@ -14209,13 +14209,13 @@
 Offers criteria to guide â€œREDD+ safeguard integrationâ€ at national and regional levels</v>
       </c>
       <c r="T154" t="str">
-        <v/>
+        <v>10.3390/su6096125</v>
       </c>
       <c r="U154" t="str">
-        <v/>
+        <v>This study examines cross-sectoral policies in Cameroon related to REDD+ (Reducing Emissions from Deforestation and Forest Degradation) strategy from a multi-criteria perspective. The paper develops a GIS-based decision support tool to compare different climate policies and sustainable development strategies in Cameroon. It analyzes how various policy interventions can contribute to optimal REDD+ strategy design while considering multiple environmental, social, and economic criteria. The research provides a framework for integrating spatial analysis with multi-criteria assessment to support evidence-based climate policy decision-making in Sub-Saharan Africa.</v>
       </c>
       <c r="V154" t="str">
-        <v/>
+        <v>REDD+, climate policy, sustainable development, multi-criteria assessment, GIS, Cameroon, decision support, deforestation, forest degradation, spatial analysis</v>
       </c>
     </row>
     <row r="155">
@@ -14238,13 +14238,13 @@
         <v>The details of study design are described elaborated by the theoretical basis for the Stepwise approach. The study considered action research and case study research design. It consisted of three main components that helped to shape the Stepwise logic: (a) co-design and co-development, (b) experiential learning, (c) farmers’ feedback, and (d) Hypothesis needed for field testing to ascertain its validity and practicality. The combination of these brought about the idea of breaking down the GAPs packages into smaller packages that could be implemented in phases. The process of development of the approach, tools, experiential learning, farmers’ feedback, assumptions, and data underpinning Stepwise approach.</v>
       </c>
       <c r="T155" t="str">
-        <v/>
+        <v>10.1080/14735903.2025.2513790</v>
       </c>
       <c r="U155" t="str">
-        <v/>
+        <v>Adoption of Climate-smart Agricultural Practices (CSA) enhances crop productivity and livelihoods. Smallholder coffee farmers in Uganda receive training on good agricultural practices (GAPs) through extension programs, but adoption remains low. Adopting all 'best practices' at once may be unrealistic for resource-limited, risk-averse smallholders. This study tested a Stepwise approach, breaking GAPs into manageable, incremental investments. Field trials were conducted in Luweero (Central) and Sironko (East) districts of Uganda, with 16 demonstration sites using randomized treatments and the control (farmer practice), divided into four steps. Each site served 25–30 farmers through experiential learning. A co-design method ensured farmer involvement in the design, development, and testing for sustainability. Results from two harvests (2018–2019) showed significant cumulative yield gains over the control. Arabica yields increased by 31%, 43%, 54% and 65% across Steps 1-4. Robusta showed gains of 7%, 22%, 23% and 39% respectively. Marginal rate of returns (MRR) was relatively high for Step 1 (563%), 2 (169%) and 4 (122%) for Robusta coffee, and 221%, 217% and 485% for Step 2, 3 and 4 for Arabica coffee respectively. The Stepwise approach demonstrated improved yield gains and increased farmer income.</v>
       </c>
       <c r="V155" t="str">
-        <v/>
+        <v>Coffee, productivity, GAPs, MRR, Stepwise approach, Uganda</v>
       </c>
       <c r="W155" t="str">
         <v>Adoption of Climate-smart Agricultural Practices (CSA) enhances crop productivity and livelihoods. Smallholder coffee farmers in Uganda receive training on good agricultural practices (GAPs) through extension programs, but adoption remains low. Adopting all ‘best practices’ at once may be unrealistic for resource-limited, risk-averse smallholders. This study tested a Stepwise approach, breaking GAPs into manageable, incremental investments. Field trials were conducted in Luweero (Central) and Sironko (East) districts of Uganda, with 16 demonstration sites using randomized treatments and the control (farmer practice), divided into four steps. Each site served 25–30 farmers through experiential learning. A co-design method ensured farmer involvement in the design, development, and testing for sustainability. Results from two harvests (2018–2019) showed significant cumulative yield gains over the control. Arabica yields increased by 31%, 43%, 54% and 65% across Steps 1-4,. Robusta showed gains of 7%, 22%, 23% and 39% respectively. Marginal rate of returns (MRR) was relatively high for Step 1 (563%), 2 (169%) and 4 (122%) for Robusta coffee , and 221%, 217% and 485% for Step 2, 3 and 4 for Arabica coffee respectively. The Stepwise approach demonstrated improved yield gains and increased farmer income.</v>

--- a/IITA climate publications - COMPLETE.xlsx
+++ b/IITA climate publications - COMPLETE.xlsx
@@ -544,7 +544,7 @@
         <v>Framework is scalable and adaptable, allowing for integration with broader data (e.g., RHoMIS) and future socioeconomic or climate data. Highlights need for context-specific, targeted policy and investment in adaptation.</v>
       </c>
       <c r="T2" t="str">
-        <v>10.1016/j.agsy.2019.102663</v>
+        <v>https://doi.org/10.1016/j.agsy.2019.102663</v>
       </c>
       <c r="U2" t="str">
         <v>Rural households in sub-Saharan Africa earn a substantial part of their living from rain-fed smallholder agriculture, which is highly sensitive to climate change. The framework combines crop suitability maps with a household food availability analysis to quantify household vulnerability to climate-related impacts on crop production and effects of adaptation options. The framework was tested for Uganda, identifying four hotspots of household vulnerability across the country. About 30% of households in the (central) southwest hotspots were vulnerable to a 3°C temperature increase and 10% rainfall decline through declining suitability for several key crops including highland banana, cassava, maize and sorghum. Options for adaptation to increasing temperatures were most beneficial in northern Uganda, while drought-related adaptation options were more beneficial in the southwest.</v>
@@ -624,7 +624,7 @@
         <v>Recommends coordinated global monitoring and phytosanitary controls; notes the additive threat with other pests like Tuta absoluta on tomatoes.</v>
       </c>
       <c r="T3" t="str">
-        <v>10.1127/entomologia/2022/1397</v>
+        <v>https://doi.org/10.1127/entomologia/2022/1397</v>
       </c>
       <c r="U3" t="str">
         <v>Spodoptera eridania (Stoll), a polyphagous lepidopteran pest from the Americas, has recently invaded western and central Africa. Like its congeners, S. eridania has developed pesticide resistance. The researchers fit a CLIMEX niche model for S. eridania and applied a climate change scenario for 2050 to investigate the sensitivity of the pest threat. The study found that S. eridania can potentially expand its range throughout the tropics and into the sub-tropics, threatening a range of important commercial and subsistence crops. Modelled climatic changes will mostly expand this species potential range poleward by around 200 km by 2050. These areas of emerging potential expansion are mostly into subtropical climates, supporting diverse cropping systems, including at risk crops beans, groundnut, potato, soybeans, tomato and sweet potato.</v>
@@ -700,7 +700,7 @@
         <v>Study provides a strong empirical foundation for informing national climate-smart agricultural policies and adaptation measures in southern Africa.</v>
       </c>
       <c r="T4" t="str">
-        <v>10.3390/cli11040084</v>
+        <v>https://doi.org/10.3390/cli11040084</v>
       </c>
       <c r="U4" t="str">
         <v>The study analyzed minimum and maximum temperatures' variability and trends using daily time series data from 23 meteorological stations across Malawi, Mozambique, South Africa and Zimbabwe, employing modified Mann–Kendall and Theil–Sen slope models. Temperature varied with location, with minimum temperature being more variable than maximum temperature, and semi-arid regions showing higher variation in minimum temperature compared to humid and coastal environments. The results showed an upward trend in minimum (0.01–0.83 °C over a 33–38 year period) and maximum (0.01–0.09 °C over a 38–57 year period) temperatures at 9 and 15 locations, respectively.</v>
@@ -796,7 +796,7 @@
 Funded through the African Climate Change Fellowship Programme (ACCFP), with IDRC and DFID support</v>
       </c>
       <c r="T5" t="str">
-        <v>10.1186/1476-072X-13-12</v>
+        <v>https://doi.org/10.1186/1476-072X-13-12</v>
       </c>
       <c r="U5" t="str">
         <v>Predicting anopheles vectors' population densities and boundary shifts is crucial in preparing for malaria risks and unanticipated outbreaks. Although shifts in the distribution and boundaries of the major malaria vectors (Anopheles gambiae s.s. and An. arabiensis) across Africa have been predicted, quantified areas of absolute change in zone of suitability for their survival have not been defined. We developed a model using CLIMEX simulation platform to estimate the potential geographical distribution and seasonal abundance of these malaria vectors in relation to climatic factors. Angola, Ethiopia, Kenya, Mozambique, Tanzania, South Africa and Zambia appear most likely to be affected in terms of absolute change of malaria vectors suitability zones under the selected climate change scenarios. The potential shifts of these malaria vectors have implications for human exposure to malaria, as recrudescence of the disease is likely to be recorded in several new areas and regions.</v>
@@ -884,7 +884,7 @@
 Strong contribution to African biodiversity mapping and historical ecology</v>
       </c>
       <c r="T6" t="str">
-        <v>10.1111/brv.12644</v>
+        <v>https://doi.org/10.1111/brv.12644</v>
       </c>
       <c r="U6" t="str">
         <v>Africa underwent numerous climatic fluctuations at ancient and more recent timescales, with tectonic, greenhouse gas, and orbital forcing stimulating diversification. Increased aridification since the Late Eocene led to important extinction events, but also provided unique diversification opportunities. The paper discusses three major models of speciation: (i) geographic speciation via vicariance (allopatry); (ii) ecological speciation impacted by climate and geological changes, and (iii) genomic speciation via genome duplication, with geographic speciation being the most widely documented. Two major geo-climatic factors shaped African biodiversity: climatic fluctuations at ancient and recent timescales, and increased aridification since the Late Eocene.</v>
@@ -988,7 +988,7 @@
 Emphasizes circular economy innovations like black soldier fly composting and CS pest management</v>
       </c>
       <c r="T7" t="str">
-        <v>10.1371/journal.pstr.0000052</v>
+        <v>https://doi.org/10.1371/journal.pstr.0000052</v>
       </c>
       <c r="U7" t="str">
         <v>This is a meta-analysis and scoping review of 43 studies and 11 reports on Climate-Smart (CS) One-Health innovations. The review identified determinants, challenges, and impacts related to the deployment of CS One-Health innovations, particularly in Ghana and Benin. Community participation, land tenure, political will, and age are critical adoption factors. Practices like composting, IPM, cover cropping, rotational grazing, and traditional ecological knowledge are promoted. Major barriers include cultural practices, lack of diagnostic tools, limited ICT access, and top-down implementation. Multi-disciplinary collaboration is essential for sustainable deployment.</v>
@@ -1088,7 +1088,7 @@
 Connects nitrogen with planetary boundaries and future GHG emission scenarios</v>
       </c>
       <c r="T8" t="str">
-        <v>10.1088/1748-9326/11/12/120205</v>
+        <v>https://doi.org/10.1088/1748-9326/11/12/120205</v>
       </c>
       <c r="U8" t="str">
         <v>This editorial synthesizes findings from the N2013 Kampala conference on nitrogen management and reviews research contributions focused on nitrogen flows, pollution, human health impacts, climate interactions, and sustainable food systems. Both nitrogen surplus (pollution) and deficit (yield loss) require tailored solutions. Integrated soil fertility management and BNF are crucial in SSA. Reducing meat consumption in high-N regions can reduce emissions and improve health. Technologies such as nitrification inhibitors and NUE metrics support sustainable intensification. Nitrogen neutrality and N footprints are proposed as accountability tools.</v>
@@ -1182,7 +1182,7 @@
 Suggests improved NARS and CGIAR collaboration could amplify RT&amp;B development impacts</v>
       </c>
       <c r="T9" t="str">
-        <v>10.1016/j.gfs.2018.12.005</v>
+        <v>https://doi.org/10.1016/j.gfs.2018.12.005</v>
       </c>
       <c r="U9" t="str">
         <v>The widely recognized role of roots, tubers and bananas (RT&amp;Bs) in achieving food security and providing income opportunities in the world's poorest regions, will be challenged by socioeconomic and climate related drivers that will affect demand and production patterns and increase pressure on farming systems. RT&amp;B contribution to food security will increase in developing countries by 2050. Overcoming productivity and market challenges in RT&amp;Bs are constrained by underinvestment in research. Investment in productivity improvement greatly benefits a subset of RT&amp;B crops. Investment in marketing improvements do not seem to offer large benefits.</v>
@@ -1282,7 +1282,7 @@
 Funded by Gates Foundation; linked to GREAT-RTB training and NextGen Cassava Breeding.</v>
       </c>
       <c r="T10" t="str">
-        <v>10.3390/su15107837</v>
+        <v>https://doi.org/10.3390/su15107837</v>
       </c>
       <c r="U10" t="str">
         <v>The study investigates cassava trait preferences in the context of climate change (CC) and conflict stressors among value-chain (VC) actors in Nigeria, to strengthen social inclusion and resilience within breeding. Multi-stage and purposive sampling procedures were used to select and interview 92 men and 95 women cassava farmers, 15 VC Key Informants and 63 VC participants in Focus Group Discussions (FGDs) in Osun, Benue and Abia States. Data were analyzed using descriptive (percentages), inferential (two way ANOVA) and thematic analysis. Preferred cassava attributes include drought-tolerance, early bulking, multiple-product use and inground storability. While CC manifests itself as drought and increased incidence of pest/diseases, farmer-herder and land conflicts exacerbate productivity; shape gendered coping strategies and stressor-related trait preferences. The major response strategies employed by men included frequent farm visits to prevent theft and engaging in non-agricultural livelihoods. Those employed by women included backyard farming, early harvesting, having preferences for food with fewer processing steps, and depending on remittances. The resilience capacity was higher for men than for women due to their better access to assets.</v>
@@ -1382,7 +1382,7 @@
 Funded by Sennar State Government; linked to IITA genotype sourcing.</v>
       </c>
       <c r="T11" t="str">
-        <v>10.18805/LRF-722</v>
+        <v>https://doi.org/10.18805/LRF-722</v>
       </c>
       <c r="U11" t="str">
         <v>The challenge to food security posed by climate change and coupled with the substantial rise in the global population, necessitate a shift in crop improvement programmes towards developing crop cultivars with stable and high yield potentials across a wide range of agro-ecological conditions. New high yielding crop varieties with stable performance across environments are enabling the expansion of their production area into non-traditional environments with semi-arid climates. This study examined genotype × environment interactions of soybean grain yield under contrasting environments in Sudan's semi-arid zone, with the goal of identifying high-yielding and stable soybean genotypes suitable for farmers in that region.</v>
@@ -1468,7 +1468,7 @@
 Suggests further research linking these trends to yield impacts</v>
       </c>
       <c r="T12" t="str">
-        <v>10.1109/ACCESS.2020.2999255</v>
+        <v>https://doi.org/10.1109/ACCESS.2020.2999255</v>
       </c>
       <c r="U12" t="str">
         <v>This article investigates the magnitude and significance of spatial-temporal trends of 37 years' time series of the gridded data for rainfall, maximum (Tmax) and minimum (Tmin) temperature for West Africa using a modified Mann-Kendall test and Theil-Sen's slope estimator. June to September rainfall showed a positive increase (0.1–5 mm/month/year) that mostly occurred north of 11° latitude, and October rainfall showed a positive trend across the region, but the magnitude was higher south of the same latitude.</v>
@@ -1560,7 +1560,7 @@
 Emphasizes importance of aligning sowing guidance with climate data to build farmer resilience</v>
       </c>
       <c r="T13" t="str">
-        <v>10.1371/journal.pone.0300427</v>
+        <v>https://doi.org/10.1371/journal.pone.0300427</v>
       </c>
       <c r="U13" t="str">
         <v>Climate change and inter-annual variability cause variation in rainfall commencement and cessation which has consequences for the maize growing season length and thus impact yields. This study therefore sought to determine the spatially explicit optimum maize sowing dates to enable site specific recommendations in Nigeria. Gridded weather and soil data, crop management and cultivar were used to simulate maize yield from 1981-2019 at a scale of 0.5°. A total of 37 potential sowing dates between 1 March and 7 November at an interval of 7 days for each year were evaluated. The results show that optimum sowing dates significantly vary across the country with northern Nigeria having notably delayed sowing dates compared to southern Nigeria which has earlier planting dates. The long-term optimal sowing dates significantly (p&lt;0.05), shifted between the 1980s (1981–1990), and current (2011–2019), for most of the country. The most optimum planting dates of southern Nigeria shifted to later sowing dates while most optimum sowing dates of central and northern Nigeria shifted to earlier sowing dates.</v>
@@ -1654,7 +1654,7 @@
 The paper frames 2015 (International Year of Soils) as a turning point for global soil governance</v>
       </c>
       <c r="T14" t="str">
-        <v>10.5194/soil-2-79-2016</v>
+        <v>https://doi.org/10.5194/soil-2-79-2016</v>
       </c>
       <c r="U14" t="str">
         <v>The Intergovernmental Technical Panel on Soils completed the first State of the World's Soil Resources Report. Globally soil erosion was identified as the gravest threat, leading to deteriorating water quality in developed regions and to lowering of crop yields in many developing regions. Stores of soil organic carbon are critical in the global carbon balance, and national governments must set specific targets to stabilize or ideally increase soil organic carbon stores.</v>
@@ -1748,7 +1748,7 @@
 Emphasizes practical, location-specific insights for planning low-carbon agriculture</v>
       </c>
       <c r="T15" t="str">
-        <v>10.1371/journal.pone.0301254</v>
+        <v>https://doi.org/10.1371/journal.pone.0301254</v>
       </c>
       <c r="U15" t="str">
         <v>This study presents an approach using decision-making tools to assess potential climate change impacts on groundnut, soybean and sunflower yields and greenhouse gas emissions in South Africa. The researchers used the Decision Support Tool for Agrotechnology Transfer (DSSAT v4.7) for crop modeling and the Cool Farm Tool for GHG calculations. The study examines climate change impacts on smallholder oil seed yields under different climate scenarios.</v>
@@ -1838,7 +1838,7 @@
 The framework is publicly accessible and adaptable for different stakeholders (govt., NGOs, private sector)</v>
       </c>
       <c r="T16" t="str">
-        <v>10.1016/j.gfs.2018.12.006</v>
+        <v>https://doi.org/10.1016/j.gfs.2018.12.006</v>
       </c>
       <c r="U16" t="str">
         <v>This study developed a data-rich spatial framework to guide agricultural research and development (AR&amp;D) prioritization and to perform ex-ante impact assessment, using technology extrapolation domains based on climate, soil, and socio-economic factors. The framework enables systematic assessment of agricultural technologies across different agro-ecological zones and farming systems.</v>
@@ -1930,7 +1930,7 @@
 Informs both research and policy communities on climate-food risk in the region</v>
       </c>
       <c r="T17" t="str">
-        <v>10.3389/fsufs.2023.1159901</v>
+        <v>https://doi.org/10.3389/fsufs.2023.1159901</v>
       </c>
       <c r="U17" t="str">
         <v>Southern Africa has been experiencing long-term changes in its climate with future projections implying droughts should last longer and become more intense, with the region already experiencing an increase in consecutive drought years. This foresight study contributes by quantifying the bio-economic impact of future droughts in southern Africa to support disaster policies in the region. The study recommends an integrated approach for enhancing regional food security under drought that includes breeding improved maize varieties with enhanced tolerance to abiotic stresses, diversifying the diet to incorporate more drought-tolerant food crops such as cassava and cowpea, and investing in rainwater harvesting technologies.</v>
@@ -2010,7 +2010,7 @@
 Strong contribution to climate-smart integrated pest management (IPM).</v>
       </c>
       <c r="T18" t="str">
-        <v>10.1016/j.jtherbio.2021.102877</v>
+        <v>https://doi.org/10.1016/j.jtherbio.2021.102877</v>
       </c>
       <c r="U18" t="str">
         <v>This study developed temperature-based phenology models to predict the development, survival, and reproduction of the oriental fruit fly Bactrocera dorsalis. Bactrocera dorsalis completed its development at temperatures ranging between 15 and 33 °C with developmental times varying across life stages, and the models predicted temperatures ranging between 20 and 30 °C as favorable for development and survival. The study provides important insights for pest management under changing climate conditions.</v>
@@ -2088,7 +2088,7 @@
         <v>Backed by the CGIAR-CCAFS and funded by Touton SA. Suggests combining crown attributes with farmer preferences to design better shade strategies.</v>
       </c>
       <c r="T19" t="str">
-        <v>10.1016/j.tfp.2021.100100</v>
+        <v>https://doi.org/10.1016/j.tfp.2021.100100</v>
       </c>
       <c r="U19" t="str">
         <v>This study examined species-specific crown architecture of upper canopy trees and its influence on shade provision in cocoa agroforestry systems in Ghana's Western Region. Five crown forms were identified and the study found that spreading to cylindrical and elongate crown forms are the most suitable crown forms to incorporate in cocoa agroforestry systems for shade provision.</v>
@@ -2168,7 +2168,7 @@
         <v>Funded by the Nigeria Soil Health Consortium (South) and supported by AGRA. Suggests demonstration plots and localized farmer training as key to scaling ISFM.</v>
       </c>
       <c r="T20" t="str">
-        <v>10.18488/journal.70/2017.4.2/70.2.28.44</v>
+        <v>https://doi.org/10.18488/journal.70/2017.4.2/70.2.28.44</v>
       </c>
       <c r="U20" t="str">
         <v>The soils of South western Nigeria are rapidly degrading due to nutrient mining, soil loss, inappropriate land use, low inherent soil fertility coupled with adverse effects of climate change. These have resulted to persistent low yields and farmers' poverty. This study assesses the status of Integrated Soil Fertility Management (ISFM) practices in southwestern Nigeria.</v>
@@ -2242,7 +2242,7 @@
         <v>Study suggests linking WII with advisory services and credit access to enhance uptake. Supported by AGRA, IDRC, CORAF/WECARD, and IITA.</v>
       </c>
       <c r="T21" t="str">
-        <v>10.1080/14693062.2020.1745742</v>
+        <v>https://doi.org/10.1080/14693062.2020.1745742</v>
       </c>
       <c r="U21" t="str">
         <v>This study assesses farmers' willingness to pay for weather index-based insurance (WII) as a market option for sharing climatic risks, using a choice modeling approach based on data collected from 704 randomly selected households in northern Togo, West Africa. The research found that respondents are willing to participate in a WII market and would prefer insuring crops, such as maize over sorghum and rice against drought by paying on average about $14.5 per hectare.</v>
@@ -2318,7 +2318,7 @@
         <v>Study supports precision nitrogen management in climate-vulnerable sorghum systems using APSIM; funded in part by CGIAR-CCAFS and GLDC.</v>
       </c>
       <c r="T22" t="str">
-        <v>10.1080/01904167.2020.1711939</v>
+        <v>https://doi.org/10.1080/01904167.2020.1711939</v>
       </c>
       <c r="U22" t="str">
         <v>This study used the Agricultural Production Systems simulator (APSIM) model to calibrate and evaluate two improved sorghum varieties in experiments conducted at two research stations in Nigeria from 2014-2016. The results showed that the model replicated observed yield and accounted for yield differences and variations in phenological development between the two sorghum cultivars, with the medium-maturing Improved-Deko cultivar showing better calibration compared to the early-maturing ICSV-400 cultivar.</v>
@@ -2396,7 +2396,7 @@
         <v>Highlights that education sometimes negatively influences adoption due to rural-to-urban labor shifts. The paper also finds agronomic practice adoption to be scale-neutral.</v>
       </c>
       <c r="T23" t="str">
-        <v>10.1111/1477-9552.12617</v>
+        <v>https://doi.org/10.1111/1477-9552.12617</v>
       </c>
       <c r="U23" t="str">
         <v>Black gram and green gram are important pulse crops in India, but their production has faced fluctuations and stagnancy in yields over the last few decades. This study analyses the determinants of the adoption of climate and plant management practices among black gram and green gram farmers and their impact on yield, crop revenue and net income across four major crop-producing Indian states using a multinomial endogenous treatment effects model. The analysis shows that information, contact with government extension services and access to off-farm activities are crucial in adopting climate and plant management practices.</v>
@@ -2478,7 +2478,7 @@
         <v>Emphasizes need for biophysical and policy integration. Highlights risk of environmental degradation if yield gap closure is not achieved and land is expanded unsustainably.</v>
       </c>
       <c r="T24" t="str">
-        <v>10.1073/pnas.1610359113</v>
+        <v>https://doi.org/10.1073/pnas.1610359113</v>
       </c>
       <c r="U24" t="str">
         <v>This study estimates it will not be feasible to meet future sub-Saharan Africa cereal demand on existing production area by yield gap closure alone, despite projections that by 2050 the region's population will increase 2.5-fold and demand for cereals will approximately triple. The analysis examines yield gaps, land availability, and sustainable intensification pathways for major cereal crops across sub-Saharan Africa.</v>
@@ -2560,7 +2560,7 @@
         <v>Findings emphasize that CA needs to be supported through access to inputs, harmonized training, and local bylaws to manage crop residues and livestock grazing.</v>
       </c>
       <c r="T25" t="str">
-        <v>10.3389/fsufs.2023.1151876</v>
+        <v>https://doi.org/10.3389/fsufs.2023.1151876</v>
       </c>
       <c r="U25" t="str">
         <v>This paper applies a multivariate probit model and other methods to survey data from 4,373 households and 278 focus groups to identify the drivers and barriers of conservation agriculture adoption in Malawi, Zambia, and Zimbabwe. The study uses a mixed-methods approach combining quantitative and qualitative data to understand adoption patterns and constraints.</v>
@@ -2654,7 +2654,7 @@
 Offers clear policy recommendations on variety deployment and planting calendar revision</v>
       </c>
       <c r="T26" t="str">
-        <v>10.1007/s10113-024-02313-5</v>
+        <v>https://doi.org/10.1007/s10113-024-02313-5</v>
       </c>
       <c r="U26" t="str">
         <v>This study used The Decision Support System for Agrotechnology Transfer (DSSAT) CERES-Millet model to assess the impact of climate change and adaptation strategies on millet in Niger. The research found that the impact of climate change varied with the agroecological zone (AEZ) with higher yield reduction in the Sahel than in the other AEZs.</v>
@@ -2746,7 +2746,7 @@
 Suggests more robust modeling for future stress combinations and regional variability</v>
       </c>
       <c r="T27" t="str">
-        <v>10.1038/s41598-021-88277-6</v>
+        <v>https://doi.org/10.1038/s41598-021-88277-6</v>
       </c>
       <c r="U27" t="str">
         <v>This study used DSSAT to assess climate change impacts on drought-tolerant versus non-drought-tolerant maize varieties in Nigeria's savanna zones, with projections for mid-century (2040–2069) and end-century (2070–2099) under RCP 4.5 and 8.5 scenarios. The research evaluates the effectiveness of drought-tolerant varieties as an adaptation strategy for maize production under changing climate conditions.</v>
@@ -2840,7 +2840,7 @@
 Suggests that without access to P, applying N may have diminishing returns under climate change</v>
       </c>
       <c r="T28" t="str">
-        <v>10.1007/s00704-016-1931-6</v>
+        <v>https://doi.org/10.1007/s00704-016-1931-6</v>
       </c>
       <c r="U28" t="str">
         <v>This study assesses the impact of current and future heat stress on maize and the benefit of heat-tolerant varieties in South Asia. Annual mean maximum temperatures may increase by 1.4–1.8 °C in 2030 and 2.1–2.6 °C in 2050, with large monthly, seasonal, and spatial variations across SA. The extent of heat stressed areas in SA could increase by up to 12% in 2030 and 21% in 2050 relative to the baseline. The research examines both rainfed and irrigated maize production systems.</v>
@@ -2934,7 +2934,7 @@
 Highlights the need for regional targeting of variety deployment</v>
       </c>
       <c r="T29" t="str">
-        <v>10.1016/j.gsd.2019.100218</v>
+        <v>https://doi.org/10.1016/j.gsd.2019.100218</v>
       </c>
       <c r="U29" t="str">
         <v>An overview of groundwater recharge estimation techniques is presented, covering numerical approach, tracer method, hydrologic budget method, and multiple methods. The norms of recharge estimation through rainfall, canal seepage, and field percolation are also covered in this study. The literature analysis revealed that the tracer techniques are extensively used in water-scarce areas for estimating groundwater recharge.</v>
@@ -3026,7 +3026,7 @@
 Strong emphasis on integrated modeling for policy formulation</v>
       </c>
       <c r="T30" t="str">
-        <v>10.1088/1748-9326/aac092</v>
+        <v>https://doi.org/10.1088/1748-9326/aac092</v>
       </c>
       <c r="U30" t="str">
         <v>This paper develops a global spatial framework to delineate technology extrapolation domains based on key climate and soil factors that govern crop yields and yield stability in rainfed crop production. A technology extrapolation domain (TED) is defined as a unique combination of biophysical and socio-economic circumstances. The framework adequately represents the spatial pattern of crop yields and stability when evaluated over the US Corn Belt, and facilitates evaluation of cropping system performance across continents.</v>
@@ -3118,7 +3118,7 @@
 Introduces a globally scalable strategy for agronomic R&amp;D efficiency and impact tracking</v>
       </c>
       <c r="T31" t="str">
-        <v>10.1016/j.pbi.2020.05.002</v>
+        <v>https://doi.org/10.1016/j.pbi.2020.05.002</v>
       </c>
       <c r="U31" t="str">
         <v>This paper addresses how West Africa is faced with significant challenges from climate change, including parts of the region becoming hotter with more variable rainfall. It discusses resilient alternative crops especially underutilized legumes particularly Bambara groundnut, African yam bean, winged bean and Kersting's groundnut and emphasizes using genomic tools for developing climate-resilient cultivars.</v>
@@ -3214,7 +3214,7 @@
 Paper is supported by CGIAR Genebank Platform and Crop Trust</v>
       </c>
       <c r="T32" t="str">
-        <v>10.3389/fpls.2021.798993</v>
+        <v>https://doi.org/10.3389/fpls.2021.798993</v>
       </c>
       <c r="U32" t="str">
         <v>This paper discusses the breeding potentials of Bambara groundnut for enhancing food and nutrition security in the context of climate change. Bambara groundnut is a balanced food that can help eradicate food and nutritional insecurity if it is incorporated into the major food system. The study examines genetic diversity, breeding strategies, and the role of this climate-resilient crop in African food systems.</v>
@@ -3316,7 +3316,7 @@
 Emphasizes importance of integrated omics approaches and bioinformatics tools</v>
       </c>
       <c r="T33" t="str">
-        <v>10.1111/ejss.70069</v>
+        <v>https://doi.org/10.1111/ejss.70069</v>
       </c>
       <c r="U33" t="str">
         <v>This paper is organized in three parts. The first part highlights and discusses current problems including soil erosion, desertification, nutrient imbalances, acidity, salinization, deforestation, and soil compaction. The authors concluded that integrated approaches promoting sustainable soil management, such as conservation agriculture, crop rotation, agroforestry, afforestation, organic farming, and community engagement, would have significant impact in resolving soil degradation in Africa.</v>
@@ -3418,7 +3418,7 @@
 Strong relevance to breeding for climate resilience in SSA maize systems.</v>
       </c>
       <c r="T34" t="str">
-        <v>10.1016/j.scitotenv.2023.165657</v>
+        <v>https://doi.org/10.1016/j.scitotenv.2023.165657</v>
       </c>
       <c r="U34" t="str">
         <v>For 33 months, twelve-year cocoa plants in Ghana were subjected to three levels of rainwater suppression under full sun or 40% uniform shade. The study found that rainwater suppression led to drought and decreased performance of cocoa trees, while shade enhanced physiology, growth, and yield compared to full sun conditions. However, shade will benefit cocoa but will not save it from the negative effects of drought. Rainwater suppression decreased leaf water potentials, reaching −1.5 MPa in full sun conditions indicating severe drought.</v>
@@ -3520,7 +3520,7 @@
 Funded by WASCAL and Gates Foundation; conducted under IITAâ€™s Maize Improvement Program</v>
       </c>
       <c r="T35" t="str">
-        <v>10.1007/s00425-019-03191-6</v>
+        <v>https://doi.org/10.1007/s00425-019-03191-6</v>
       </c>
       <c r="U35" t="str">
         <v>Bambara groundnut is a nitrogen-fixing, stress-tolerant legume with potential for climate-resilient agriculture. This paper discusses the crop's resilience characteristics including drought tolerance, heat tolerance, and ability to grow in marginal soils, making it an exemplar underutilised legume for adaptation to climate change.</v>
@@ -3614,7 +3614,7 @@
 Supports development of early warning systems and adaptation strategies in rainfed systems</v>
       </c>
       <c r="T36" t="str">
-        <v>10.1007/s10457-023-00950-z</v>
+        <v>https://doi.org/10.1007/s10457-023-00950-z</v>
       </c>
       <c r="U36" t="str">
         <v>The study evaluated farmer's local knowledge and perceptions of sustainable cocoa agroforestry and sustainable soil carbon management in Ghana and Côte d'Ivoire. About 83% and 50.5% of smallholder cocoa farmers from Côte d'Ivoire and Ghana respectively practiced agroforestry on their farms, though the respondents had limited knowledge about the term agroforestry.</v>
@@ -3697,7 +3697,7 @@
 Collaboration between IITA, ICRAF, UR, and IUCN is noteworthy.</v>
       </c>
       <c r="T37" t="str">
-        <v>10.5539/sar.v8n2p68</v>
+        <v>https://doi.org/10.5539/sar.v8n2p68</v>
       </c>
       <c r="U37" t="str">
         <v>Climate change resulted in a decrease of 100 mm isohyets between two 30-year periods. The rainy season structure changed slightly, with the average start delayed by 6 days and the end occurring 4 days earlier. Maximum temperatures increased significantly from +0.44°C to +1.53°C and minimum temperatures increased from +1.05°C to +1.93°C. Despite these climate changes, statistics of major agronomic food crop production in Mali from 1984 to 2013 showed an average increase from 985 to 4492 thousand tons, representing a 22% increase per year. This positive trend is attributed to a combination of agricultural extension, agronomic research application, and smallholder farmer management in the Sahel.</v>
@@ -3791,7 +3791,7 @@
 Builds directly on CGIAR systems modeling research across West and East Africa</v>
       </c>
       <c r="T38" t="str">
-        <v>10.3389/fpls.2015.00563</v>
+        <v>https://doi.org/10.3389/fpls.2015.00563</v>
       </c>
       <c r="U38" t="str">
         <v>This review discusses how molecular breeding approaches have proven helpful in enhancing the stress adaptation of crop plants, and recent advances in high-throughput sequencing and phenotyping platforms have transformed molecular breeding to genomics-assisted breeding (GAB), elaborating the progress and prospects of GAB for improving climate change resilience in crops.</v>
@@ -3889,7 +3889,7 @@
 Advocates for ratifying global conventions on pollution and land use</v>
       </c>
       <c r="T39" t="str">
-        <v>10.1094/PDIS-07-22-1672-RE</v>
+        <v>https://doi.org/10.1094/PDIS-07-22-1672-RE</v>
       </c>
       <c r="U39" t="str">
         <v>The study used the maximum entropy (Maxent) model on 1,022 georeferenced BXW datapoints and 20 environmental variables. Precipitation of the coldest quarter, average maximum monthly temperature, annual precipitation, and elevation were the strongest predictors. Banana Xanthomonas wilt (BXW) is a major threat to banana production in Rwanda, causing up to 100% yield loss.</v>
@@ -3977,7 +3977,7 @@
 Highlights physiological thresholds critical for yield under climate stress</v>
       </c>
       <c r="T40" t="str">
-        <v>10.1080/17565529.2023.2178840</v>
+        <v>https://doi.org/10.1080/17565529.2023.2178840</v>
       </c>
       <c r="U40" t="str">
         <v>This study used farm household survey data from Nigeria and examined whether and to what extent the yield and income impacts of adopting drought-tolerant maize varieties are heterogeneous, using stratification-multilevel, matching-smoothing and smoothing-differencing econometric methods. The results show that the adoption of drought-tolerant maize varieties significantly increased maize yield, crop and household income. The yield and income impacts are heterogeneous and depend on the farm households' propensity to adopt, with estimated yield effects being larger for farmers with the highest propensity to adopt the varieties.</v>
@@ -4077,7 +4077,7 @@
 Promotes integration of socio-cultural knowledge in breeding for adoption</v>
       </c>
       <c r="T41" t="str">
-        <v>10.5897/JSSEM15.0502</v>
+        <v>https://doi.org/10.5897/JSSEM15.0502</v>
       </c>
       <c r="U41" t="str">
         <v>Based on evidence from regional research, conservation agriculture has good potential for climate change adaptation in both high and low rainfall areas of Rwanda. However, decreased yield observed in high rainfall areas, increased labour requirements when herbicides are not used and lack of mulch due to priority given to feeding of livestock constrained CA adoption.</v>
@@ -4173,7 +4173,7 @@
 Proposes regional policy coordination to address cocoa-driven deforestation and emissions</v>
       </c>
       <c r="T42" t="str">
-        <v>10.1007/s10745-017-9899-0</v>
+        <v>https://doi.org/10.1007/s10745-017-9899-0</v>
       </c>
       <c r="U42" t="str">
         <v>This study assesses farmers' local knowledge of shade trees at two locations in Ghana with different climatic conditions and vulnerability to climate change, and found that cocoa farmers have detailed knowledge on the functions of shade trees in cocoa systems and prefer species that provide specific needs according to the location.</v>
@@ -4271,7 +4271,7 @@
 Refutes deterministic climate-crop decline narratives with empirical data</v>
       </c>
       <c r="T43" t="str">
-        <v>10.1016/j.fcr.2016.06.010</v>
+        <v>https://doi.org/10.1016/j.fcr.2016.06.010</v>
       </c>
       <c r="U43" t="str">
         <v>This study developed parameters for modern cultivars representing all 17 CIMMYT wheat Mega Environments (MEs) using field experimental data and genetic cultivar relationships for the CROPSIM-CERES model in DSSAT v 4.5. Crop simulations were carried out at 0.5 × 0.5° pixels for global wheat-growing areas, using cultivars representing MEs, soil information, region-specific crop management, and initial soil conditions. The simulated yields and production showed a Root Mean Square Error (RMSE) of 1.3 t/ha for yield and 2.2 M t/country for country production when compared to FAO statistics.</v>
@@ -4367,7 +4367,7 @@
 Important framing piece for genomics in climate-smart agriculture</v>
       </c>
       <c r="T44" t="str">
-        <v>10.1016/j.scitotenv.2017.08.041</v>
+        <v>https://doi.org/10.1016/j.scitotenv.2017.08.041</v>
       </c>
       <c r="U44" t="str">
         <v>This study focused on Cameroon and examined the relationship between climate change, agricultural productivity (particularly plantain crops), and school attendance rates from 1950-2013, with predictions extending to 2080. The research demonstrates how climate warming causes declines in crop yields and subsequently affects school attendance in Central Africa.</v>
@@ -4459,7 +4459,7 @@
 Promotes integration of ICT and climate risk mapping for crop disease surveillance</v>
       </c>
       <c r="T45" t="str">
-        <v>10.1371/journal.pone.0255326</v>
+        <v>https://doi.org/10.1371/journal.pone.0255326</v>
       </c>
       <c r="U45" t="str">
         <v>Collection missions and all surveys were undertaken by the Ministry of Agriculture in Tanzania (now Tanzanian Agricultural Research Institute (TARI)) in collaboration with the International Institute of Tropical Agriculture (IITA) from June 2016 to January 2017. SNP genotyping was used as the basis to identify duplicate samples and assess diversity among the collected landraces. The study documented farmer knowledge and eliminated viruses from cassava landraces in Tanzania.</v>
@@ -4551,7 +4551,7 @@
 No gender/youth-specific results or targeting despite existing literature on intra-household impacts</v>
       </c>
       <c r="T46" t="str">
-        <v>10.1093/plcell/koac303</v>
+        <v>https://doi.org/10.1093/plcell/koac303</v>
       </c>
       <c r="U46" t="str">
         <v>This comprehensive review addresses enhancing carbon sequestration capacity of crops, improving photosynthesis, engineering climate resilience in crops, and describes the vision of a sustainable global bioeconomy rooted in plant biology. The paper covers systems biology approaches for sustainable agriculture in the context of climate change challenges.</v>
@@ -4649,13 +4649,13 @@
 Supported by the SIMLESA project (Sustainable Intensification of Maize-Legume Systems in ESA)</v>
       </c>
       <c r="T47" t="str">
-        <v>10.1088/1748-9326/ac61c8</v>
+        <v>https://doi.org/10.1088/1748-9326/ac61c8</v>
       </c>
       <c r="U47" t="str">
         <v>The study systematically reviewed literature published between 2005 and 2020 and identified 35 relevant studies, analyzing yield changes of major staple crops (maize, sorghum, rice, millet, yam, cassava and groundnuts) caused by different climate change and field management scenarios. Yields declined by a median of 6% (-8% to +2% depending on the crop) due to climate change in all scenarios analysed. Common adaptation strategies could increase crop yields affected by climate change by 13% (-4% to +19% depending on the strategy) as compared to business-as-usual field management.</v>
       </c>
       <c r="V47" t="str">
-        <v>Climate change impacts, Adaptation strategies, West Africa, Crop yields, Systematic review, Food security</v>
+        <v>Climate change, West Africa, adaptation strategies, crop yields, systematic review</v>
       </c>
     </row>
     <row r="48" xml:space="preserve">
@@ -4735,7 +4735,7 @@
 Highlights the risk of losing agroecologically suitable species due to climate change and policy constraints</v>
       </c>
       <c r="T48" t="str">
-        <v>10.1007/s00267-018-1048-z</v>
+        <v>https://doi.org/10.1007/s00267-018-1048-z</v>
       </c>
       <c r="U48" t="str">
         <v>This study investigated the capacity of institutions to support the planning, implementation, and resource mobilization needed to integrate climate change mitigation, conservation, and livelihood goals in a forest mosaic landscape in East Cameroon, and found that diverse institutions are present in the landscape, including government agencies, local government, local non-government, private sector, and hybrid institutions.</v>
@@ -4821,7 +4821,7 @@
 Offers a foundational resource for future climate resilience studies in wheat systems</v>
       </c>
       <c r="T49" t="str">
-        <v>10.1111/agec.12363</v>
+        <v>https://doi.org/10.1111/agec.12363</v>
       </c>
       <c r="U49" t="str">
         <v>This study found the promotion of new maize and wheat varieties to be an effective adaptation option, on average, especially when accompanied by policy interventions such as credit and fertilizer subsidy. However, the effectiveness of available adaptation options is quite different across the heterogeneous smallholder population in Ethiopia, implying that policy assessments based on average farm households may mislead policy makers to adhere to interventions that are beneficial on average albeit ineffective in addressing the particular needs of poor and food insecure farmers.</v>
@@ -4909,13 +4909,13 @@
 Provides a strong case for including social vulnerability in climate impact assessments</v>
       </c>
       <c r="T50" t="str">
-        <v>10.1002/ece3.3668</v>
+        <v>https://doi.org/10.1002/ece3.3668</v>
       </c>
       <c r="U50" t="str">
         <v>This study investigates whether historical climate change has impacted the evolutionary history of African Aedes mosquitoes using a comparative phylogeographic approach. The research examines the role of past climatic change in shaping mosquito evolution within Africa.</v>
       </c>
       <c r="V50" t="str">
-        <v>Aedes mosquitoes, Phylogeography, Climate change evolution, Africa, Vector ecology, Palaeoclimate</v>
+        <v>Aedes mosquitoes, phylogeography, climate change, Africa, evolution</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
@@ -5005,13 +5005,13 @@
 The conservation strategy is active and ongoing via KEPHIS and IITA</v>
       </c>
       <c r="T51" t="str">
-        <v>10.3390/agriculture12111853</v>
+        <v>https://doi.org/10.3390/agriculture12111853</v>
       </c>
       <c r="U51" t="str">
         <v>This study evaluates the heterogeneous impacts of adopting climate-smart agricultural technologies on rural household welfare in Mali using farm household survey data and econometric methods. The analysis shows differential impacts across different farmer groups and household characteristics.</v>
       </c>
       <c r="V51" t="str">
-        <v>Climate-smart agriculture, Heterogeneous impacts, Mali, Rural welfare, Technology adoption, Household impacts</v>
+        <v>Climate-smart agriculture, Mali, household welfare, adoption, technology</v>
       </c>
     </row>
     <row r="52" xml:space="preserve">
@@ -5097,13 +5097,13 @@
 Emphasizes role of plant science in meeting IPCC climate targets</v>
       </c>
       <c r="T52" t="str">
-        <v>10.1016/j.eja.2024.127137</v>
+        <v>https://doi.org/10.1016/j.eja.2024.127137</v>
       </c>
       <c r="U52" t="str">
         <v>This study assessed the potential climate change impact on four key rainfed cereals (maize, millet, sorghum and wheat) in ten SSA countries namely Burkina Faso, Ghana, Mali, Niger, Nigeria, Ethiopia, Kenya, Tanzania, Uganda, and Zambia using local data and national expertise, and the potential of cultivar adaptation to climate change for the four crops. By 2050, climate change impact on rainfed potential yields was insignificant in West and modest in East and Southern Africa. By 2090, average impacts were much higher in West than in East and Southern Africa.</v>
       </c>
       <c r="V52" t="str">
-        <v>Climate change impact, Rainfed cereals, Sub-Saharan Africa, Crop adaptation, Maize, Millet, Sorghum, Wheat</v>
+        <v>Climate change, cereal crops, sub-Saharan Africa, rainfed agriculture, adaptation</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -5197,7 +5197,7 @@
 Highlights need for more robust data, better regional climate models, and expanded research on neglected crops and farming systems.</v>
       </c>
       <c r="T53" t="str">
-        <v>10.1088/1748-9326/ac61c8</v>
+        <v>https://doi.org/10.1088/1748-9326/ac61c8</v>
       </c>
       <c r="U53" t="str">
         <v>Agriculture in West Africa faces the challenge of meeting the rising demand for food as national incomes and populations increase while production becomes more uncertain due to climate change. Adaptation strategies (such as optimised planting dates, use of fertilisers and climate-resilient crop varieties) to mitigate the effects of climate change on crop yields. We systematically searched two databases for literature published between 2005 and 2020 and identified 35 relevant studies. We analysed yield changes of major staple crops (maize, sorghum, rice, millet, yam, cassava and groundnuts) caused by different climate change and field management scenarios. Yields declined by a median of 6% (−8% to +2% depending on the crop) due to climate change in all scenarios analysed. We show that the common adaptation strategies could increase crop yields affected by climate change by 13% (−4% to +19% depending on the strategy) as compared to business-as-usual field management practices.</v>
@@ -5289,13 +5289,13 @@
 Paper highlights how informal institutions can be key entry points for climate adaptation planning in forest-dependent regions.</v>
       </c>
       <c r="T54" t="str">
-        <v>10.1080/17565529.2017.1291409</v>
+        <v>https://doi.org/10.1080/17565529.2017.1291409</v>
       </c>
       <c r="U54" t="str">
         <v>Surveys of 232 people from 13 villages, in three regions of Cameroon, provided insight about the role that internal village institutions can play in fostering community resilience. Almost all villagers, both men and women, are members of at least one group and the membership of these groups is very diverse in terms of family relations, gender, occupation, age, and level of education. While the groups were not currently working together to respond to climate change, the diverse social networks that villagers have in these groups have already fostered exchange of knowledge. Their existence in villages provides opportunities for developing and sharing of knowledge that can be important for climate change adaptation in the future. Community resilience could be better fostered through a deliberate action-reflection process that includes both men and women, and builds on the social capital present in communities.</v>
       </c>
       <c r="V54" t="str">
-        <v>Climate change, community resilience, village institutions, social capital, Cameroon</v>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -5385,7 +5385,7 @@
 Demonstrates the usefulness of bioeconomic agent-based models in climate and food security policy design.</v>
       </c>
       <c r="T55" t="str">
-        <v>10.1111/agec.12358</v>
+        <v>https://doi.org/10.1111/agec.12358</v>
       </c>
       <c r="U55" t="str">
         <v>Climate variability with unexpected droughts and floods causes serious production losses and worsens food security, especially in Sub-Saharan Africa. This study applies stochastic bioeconomic modeling to analyze smallholder adaptation to climate and price variability in Ethiopia. It uses the agent-based simulation package Mathematical Programming-based Multi-Agent Systems (MPMAS) to capture nonseparable production and consumption decisions at household level, considering livestock and eucalyptus sales for consumption smoothing. The study found the promotion of new maize and wheat varieties to be an effective adaptation option, on average, especially when accompanied by policy interventions such as credit and fertilizer subsidy. The effectiveness of available adaptation options is quite different across the heterogeneous smallholder population in Ethiopia. This implies that policy assessments based on average farm households may mislead policy makers to adhere to interventions that are beneficial on average albeit ineffective in addressing the particular needs of poor and food insecure farmers.</v>
@@ -5469,7 +5469,7 @@
 Supports the use of molecular phylogeography in conservation and disease vector management strategies in Sub-Saharan Africa.</v>
       </c>
       <c r="T56" t="str">
-        <v>10.1002/ece3.3668</v>
+        <v>https://doi.org/10.1002/ece3.3668</v>
       </c>
       <c r="U56" t="str">
         <v>The primary aim was to determine whether historical climate change has impacted the evolutionary history of African Aedes mosquitoes. The study used a comparative phylogeographic approach to investigate the population histories of four species of Aedes (Stegomyia) mosquitoes. Inference of the demographic history of Ae. aegypti within Africa from nuclear sequence data revealed that this could have been influenced by past climatic change with historical divergence and admixture dated to the late Pleistocene and early Holocene, consistent with demography being shaped by historical changes in forest distribution.</v>
@@ -5561,7 +5561,7 @@
 Funded by the Royal Norwegian Embassy in Mali; conducted in collaboration with IITA and national partners.</v>
       </c>
       <c r="T57" t="str">
-        <v>10.3390/agriculture12111853</v>
+        <v>https://doi.org/10.3390/agriculture12111853</v>
       </c>
       <c r="U57" t="str">
         <v>Climate change is negatively affecting agricultural production in the Sahel region. Climate-Smart Agricultural Technologies (CSATs) are disseminated to reduce these negative effects, and particularly those on resource-poor farm households. This article investigates the distributional impacts of the adoption of CSAT on-farm households' welfare using a dataset that covers four regions, 32 communes, 320 villages, and 2240 households in Mali. Using an instrumental variable quantile treatment effects model, the paper addresses the potential endogeneity arising from the selection bias and the heterogeneity of the effect across the quantiles of the outcome variables' distribution. The results show that the adoption of CSAT is positively associated with improved households' welfare.</v>
@@ -5643,7 +5643,7 @@
         <v>Robust use of GYGA datasets and local agronomist input; results support cultivar-focused adaptation as a policy strategy. Study was part of CGIAR Excellence in Agronomy and Climate Resilience initiatives.</v>
       </c>
       <c r="T58" t="str">
-        <v>10.1016/j.eja.2024.127137</v>
+        <v>https://doi.org/10.1016/j.eja.2024.127137</v>
       </c>
       <c r="U58" t="str">
         <v>Sub-Saharan Africa's (SSA) demand for cereals is projected to more than double by 2050. Climate change is generally assumed to add to the future challenges of the needed productivity increase. This study aimed to assess (i) the potential climate change impact on four key rainfed cereals (maize, millet, sorghum and wheat) in ten SSA countries namely Burkina Faso, Ghana, Mali, Niger, Nigeria, Ethiopia, Kenya, Tanzania, Uganda, and Zambia using local data and national expertise, and (ii) the potential of cultivar adaptation to climate change for the four crops. The researchers assessed effects on rainfed potential cereal yields per crop and aggregated these to regional level in West (WA), East and Southern Africa (ESA), using a rigorous agronomic dataset for 120 locations in the ten countries with simulations using bias-corrected climate data from five GCMs, three time periods and two scenarios. Key findings show that by 2050, climate change impact on rainfed potential yields was insignificant in West and modest in East and Southern Africa, while by 2090, average impacts were much higher in West than in East and Southern Africa.</v>
@@ -5723,7 +5723,7 @@
         <v>Research funded by IITA and part of CGIAR programs on Climate Change, Agriculture and Food Security (CCAFS) and Cocoa Soils. Supports integration of cocoa agroforestry into carbon credit schemes.</v>
       </c>
       <c r="T59" t="str">
-        <v>10.22302/ICCRI.JUR.PELITAPERKEBUNAN.V37I1.395</v>
+        <v>https://doi.org/10.22302/ICCRI.JUR.PELITAPERKEBUNAN.V37I1.395</v>
       </c>
       <c r="U59" t="str">
         <v>Shade grown cocoa systems have been credited with stocking high quantities of carbon and therefore possess the potential to mitigate climate change and help achieve targets of the United Nations Collaborative Program on Reduced Emissions from Deforestation and Forest Degradation (REDD+). This study quantifies and compares carbon stored as well as estimated cocoa yields in two shade management types (i.e., shaded and full sun) across three agroecological zones: Dry Semi-Deciduous Fire Zone (DSFZ), Moist Evergreen Zone (MEZ) and Upland Evergreen Moist Zone (UEMZ) in Ghana. Results show that Soil organic carbon (SOC) stored decreased with increasing soil depth across all agroecological zones. Cocoa farms with shade trees stored 6 times more soil carbon (35.90±1.56 Mg C ha-1) compared to the full sun systems (5.98±1.56 Mg C ha-1).</v>
@@ -5803,7 +5803,7 @@
         <v>Serves as an introduction to a curated research topic; provides insight into key innovations and interventions promoted by IITA and partners in SSA.</v>
       </c>
       <c r="T60" t="str">
-        <v>10.3389/fsufs.2022.959604</v>
+        <v>https://doi.org/10.3389/fsufs.2022.959604</v>
       </c>
       <c r="U60" t="str">
         <v>Agriculture is the mainstay of the economies of sub-Saharan Africa as it employs 60% of the active population and contributes up to 35% of the GDP. Improving and maintaining soil fertility is critical for sub-Saharan Africa to achieve the sustainable development goals (SDGs) and, in particular, contribute to eradicating poverty (SDG 1), and ending hunger, achieving food security, improving nutrition and promoting sustainable agriculture (SDG 2).</v>
@@ -5885,13 +5885,13 @@
         <v>Model integrates empirical life table data with GIS for pest forecasting. Supported by BMZ/GIZ and IITA. Contributes to climate-smart pest management.</v>
       </c>
       <c r="T61" t="str">
-        <v>10.1080/14735903.2025.2513790</v>
+        <v>https://doi.org/10.1080/14735903.2025.2513790</v>
       </c>
       <c r="U61" t="str">
         <v>Adoption of Climate-smart Agricultural Practices (CSA) enhances crop productivity and livelihoods. Smallholder coffee farmers in Uganda receive training on good agricultural practices (GAPs) through extension programs, but adoption remains low. Adopting all 'best practices' at once may be unrealistic for resource-limited, risk-averse smallholders. This study tested a Stepwise approach, breaking GAPs into manageable, incremental investments. Field trials were conducted in Luweero (Central) and Sironko (East) districts of Uganda, with 16 demonstration sites using randomized treatments divided into four steps. Each site served 25-30 farmers through experiential learning. Results from two harvests (2018-2019) showed significant cumulative yield gains over the control.</v>
       </c>
       <c r="V61" t="str">
-        <v>climate-smart agriculture, coffee production, Uganda, stepwise approach, smallholder farmers, adoption</v>
+        <v>Coffee, productivity, GAPs, MRR, Stepwise approach, Uganda</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
@@ -5967,13 +5967,13 @@
         <v>Supports the CGIAR GENDER Impact Platform. Recommends systemic reforms including gender-responsive policy design, intersectional analysis, and recognition of women's roles in fisheries and aquaculture value chains globally.</v>
       </c>
       <c r="T62" t="str">
-        <v>10.3390/su6096125</v>
+        <v>https://doi.org/10.3390/su6096125</v>
       </c>
       <c r="U62" t="str">
         <v>Cameroon is committed to reducing emissions from deforestation and forest degradation plus conservation, sustainable management of forests and enhancement of carbon stocks (REDD+). To achieve this goal, the government has introduced a series of policy reforms and formulated key strategic planning documents to advance the REDD+ readiness process. This paper assesses the extent to which major cross-sectoral policies support or impede the development and implementation of an optimal REDD+ strategy in Cameroon from a comparative multi-criteria perspective. Study results reveal that a majority of the policy instruments reviewed appeared to be less prescriptive in terms of any tangible REDD+ strategy, as they do not have provisions for tangible measures to reduce deforestation and forest degradation.</v>
       </c>
       <c r="V62" t="str">
-        <v>multi-criteria analysis, policy instruments, GIS, REDD+, decision-support tool</v>
+        <v>REDD+, climate policy, sustainable development, multi-criteria assessment, GIS, Cameroon, decision support, deforestation, forest degradation, spatial analysis</v>
       </c>
     </row>
     <row r="63" xml:space="preserve">
@@ -6045,13 +6045,13 @@
         <v>Funded by BMZ; links to CGIAR climate programs; relevance for West Africa's cocoa adaptation planning under climate change.</v>
       </c>
       <c r="T63" t="str">
-        <v>10.3920/WMJ2016.2130</v>
+        <v>https://doi.org/10.3920/WMJ2016.2130</v>
       </c>
       <c r="U63" t="str">
         <v>Aflatoxin contamination of crops is frequent in warm regions across the globe, including large areas in sub-Saharan Africa, and crop contamination with these dangerous toxins transcends health, food security, and trade sectors. Carefully selected atoxigenic genotypes in biological control (biocontrol) formulations efficiently reduce aflatoxin contamination of crops when applied prior to flowering in the field. The technology has been improved for use in sub-Saharan Africa, where efforts are under way to develop biocontrol products. Benefits of aflatoxin biocontrol technologies are discussed along with potential challenges, including climate change, likely to be faced during the scaling-up of Aflasafe products.</v>
       </c>
       <c r="V63" t="str">
-        <v>aflatoxin, biological control, climate change, food safety, sub-Saharan Africa, Aflasafe</v>
+        <v>aflatoxin, biological control, biocontrol, atoxigenic, climate change, Africa, crop contamination, food safety, mycotoxin, fungal control</v>
       </c>
     </row>
     <row r="64" xml:space="preserve">
@@ -6123,13 +6123,13 @@
         <v>Research supported by IITA, CGIAR's CCAFS and FTA programs, with funding from the German Ministry for Economic Cooperation and Development (BMZ).</v>
       </c>
       <c r="T64" t="str">
-        <v>10.1111/pbi.12467</v>
+        <v>https://doi.org/10.1111/pbi.12467</v>
       </c>
       <c r="U64" t="str">
         <v>Agriculture is now facing the 'perfect storm' of climate change, increasing costs of fertilizer and rising food demands from a larger and wealthier human population. These factors point to a global food deficit unless the efficiency and resilience of crop production is increased. The intensification of agriculture has focused on improving production under optimized conditions, with significant agronomic inputs. A new agricultural paradigm is required, reducing dependence on high inputs and increasing crop diversity, yield stability and environmental resilience. Genomics offers unprecedented opportunities to increase crop yield, quality and stability of production through advanced breeding strategies, enhancing the resilience of major crops to climate variability, and increasing the productivity and range of minor crops to diversify the food supply.</v>
       </c>
       <c r="V64" t="str">
-        <v>genomics, climate change, agricultural intensification, crop improvement, breeding, resilience</v>
+        <v>genomics, climate change, agricultural intensification, crop improvement, breeding, food security, climate resilience, crop yield, genetic diversity, adaptation</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
@@ -6193,13 +6193,13 @@
         <v>Study promotes low-cost, scalable drought assessment tools like handheld infrared thermometers and recommends best practices for banana phenotyping in the field.</v>
       </c>
       <c r="T65" t="str">
-        <v>10.1094/PDIS-01-23-0166-FE</v>
+        <v>https://doi.org/10.1094/PDIS-01-23-0166-FE</v>
       </c>
       <c r="U65" t="str">
         <v>The Global Plant Health Assessment (GPHA) is a collective, volunteer-based effort to assemble expert opinions on plant health and disease impacts on ecosystem services based on published scientific evidence. The GPHA considers a range of forest, agricultural, and urban systems worldwide. Among the 33 (Ecoregion × Plant System) considered, 18 are assessed as in fair or poor health, and 20 as in declining health. Much of the observed state of plant health and its trends are driven by a combination of forces, including climate change, species invasions, and human management. Healthy plants ensure (i) provisioning, (ii) regulation, and (iii) cultural ecosystem services.</v>
       </c>
       <c r="V65" t="str">
-        <v>plant health, ecosystem services, climate change, disease, global assessment, food security</v>
+        <v>plant health, global assessment, crop diseases, climate change, pest management, species invasions, agricultural systems, ecoregions, plant pathology, food security</v>
       </c>
     </row>
     <row r="66" xml:space="preserve">
@@ -6273,13 +6273,13 @@
         <v>Chickpea offers off-season growth potential. Common bean is least water-limited and most widely grown legume in region. Calls for more data on legume intercropping systems.</v>
       </c>
       <c r="T66" t="str">
-        <v>10.1016/j.crsust.2023.100219</v>
+        <v>https://doi.org/10.1016/j.crsust.2023.100219</v>
       </c>
       <c r="U66" t="str">
         <v>This study examines how gender norms mediate crop farmers' responsive approaches to rapid climate warming, focusing on men and women crop smallholder farmers in Nasarawa state who experience the impacts of rapid climate warming differently. There has been an additional increase of 1.14°C in the minimum temperature over the study period. 63% of respondents perceived both heatwaves and dry spells. Major adaptation strategies used by farmers are traditional irrigation (56%), sustainable forestry (44%), and cover cropping (54%). 66% of women adopted traditional irrigation and 75% practiced cover cropping, while 74% of men practiced sustainable forestry. Gender norms constrain the adoption of responsive approaches due to unequal access to climate interventions in agriculture.</v>
       </c>
       <c r="V66" t="str">
-        <v>gender, climate warming, smallholder farmers, adaptation strategies, Nigeria, gender norms</v>
+        <v>gender, climate warming, smallholder farmers, adaptation, Nigeria, temperature change, gender-responsive, climate change, agricultural resilience, vulnerability</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -6367,13 +6367,13 @@
 Understory vegetation management in CAF contributes significantly to soil carbon</v>
       </c>
       <c r="T67" t="str">
-        <v>10.1007/s10584-019-02447-0</v>
+        <v>https://doi.org/10.1007/s10584-019-02447-0</v>
       </c>
       <c r="U67" t="str">
         <v>Gender mainstreaming was acknowledged as an indispensable strategy for achieving gender equality at the 1995 Beijing Platform for Action. This study analyzes the extent of gender integration in agricultural and natural resource policies in Uganda and Tanzania, and how gender is budgeted for in implementation plans at district and lower governance levels. A total of 155 policy documents, development plans, and annual action plans from national, district, and sub-county/ward levels were reviewed. Results show that whereas there is increasing gender responsiveness, (i) gender issues are still interpreted as 'women issues,' (ii) there is disharmony in gender mainstreaming across governance levels, (iii) budgeting for gender is not yet fully embraced, (iv) allocations to gender at sub-national level remain inconsistently low, and (v) gender activities do not address structural inequalities.</v>
       </c>
       <c r="V67" t="str">
-        <v>gender mainstreaming, climate change policy, agriculture policy, East Africa, Uganda, Tanzania</v>
+        <v>gender mainstreaming, climate change policy, agriculture policy, natural resources, East Africa, Uganda, Tanzania, policy analysis, gender budgeting, governance</v>
       </c>
     </row>
     <row r="68" xml:space="preserve">
@@ -6463,13 +6463,13 @@
 Provides detailed catalog of genotyping and molecular breeding efforts for multiple legumes</v>
       </c>
       <c r="T68" t="str">
-        <v>10.1038/s41467-023-39338-z</v>
+        <v>https://doi.org/10.1038/s41467-023-39338-z</v>
       </c>
       <c r="U68" t="str">
         <v>Anthropogenic activities profoundly impact soil organic carbon (SOC), affecting its contribution to ecosystem services such as climate regulation. This study conducted a thorough review of the impacts of land-use change, land management, and climate change on SOC using second-order meta-analysis, synthesizing findings from 230 first-order meta-analyses comprising over 25,000 primary studies. The study shows that: (i) land conversion for crop production leads to high SOC loss that can be partially restored through land management practices, particularly by introducing trees and incorporating exogenous carbon in the form of biochar or organic amendments, (ii) land management practices implemented in forests generally result in depletion of SOC, and (iii) indirect effects of climate change, such as through wildfires, have a greater impact on SOC than direct climate change effects.</v>
       </c>
       <c r="V68" t="str">
-        <v>soil organic carbon, land-use change, climate change, Anthropocene, meta-analysis, carbon sequestration</v>
+        <v>soil organic carbon, meta-analysis, Anthropocene, land management, carbon sequestration, soil health, climate change mitigation, global assessment, agricultural practices, ecosystem services</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
@@ -6551,13 +6551,13 @@
 Points to CRISPR/Cas9 as a future tool to reduce anti-nutritional factors, improve cooking time, and enhance stress tolerance.</v>
       </c>
       <c r="T69" t="str">
-        <v>10.1111/mec.13762</v>
+        <v>https://doi.org/10.1111/mec.13762</v>
       </c>
       <c r="U69" t="str">
         <v>The study applied approximate Bayesian computation to sequence data from four nuclear and one mitochondrial marker, revealing that African populations of Aedes aegypti best fit a demographic model of lineage diversification, historical admixture and recent population structuring. ABC analysis and haplotype networks support earlier inferences of a single out-of-Africa colonization event, while a cline of decreasing genetic diversity indicates that Ae. aegypti moved first from Africa to the Americas and then to Asia. By increasing genetic diversity and forming novel allelic combinations, divergence and historical admixture within Africa could have provided the adaptive potential needed for the successful worldwide spread of Ae. aegypti.</v>
       </c>
       <c r="V69" t="str">
-        <v>Pleistocene climatic change, approximate Bayesian computation, arbovirus, domestication, forest fragmentation, invasive species</v>
+        <v>Aedes aegypti, mosquito, population genetics, Africa, climatic change, Pleistocene, admixture, disease vector, evolutionary history, genetic diversity</v>
       </c>
     </row>
     <row r="70" xml:space="preserve">
@@ -6651,13 +6651,13 @@
 Focused on smallholder rice systems in ESA but methods applicable to other crops.</v>
       </c>
       <c r="T70" t="str">
-        <v>10.1080/00207233.2017.1398432</v>
+        <v>https://doi.org/10.1080/00207233.2017.1347358</v>
       </c>
       <c r="U70" t="str">
         <v>This paper evaluates the socio-technical interactions of REDD+ (Reducing Emissions from Deforestation and Forest Degradation) and measurement, reporting and verification (MRV) systems, particularly focusing on the degree of inclusiveness of transnational advocacy networks (TANs) and the empowerment of African state and non-state actors within these systems. The study examines forest governance challenges in Central Africa and proposes a participatory model to increase stakeholder involvement in carbon markets, addressing issues of equity, benefit sharing, and institutional capacity for effective REDD+ implementation in the context of climate change mitigation.</v>
       </c>
       <c r="V70" t="str">
-        <v>REDD+, forest governance, participatory model, carbon markets, Central Africa, climate change mitigation</v>
+        <v>forest governance, REDD+, Central Africa, participatory model, carbon markets, stakeholder involvement, climate mitigation, community engagement, sustainable development, forest conservation</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
@@ -6751,13 +6751,13 @@
 Funded by Gates Foundation and WASCAL.</v>
       </c>
       <c r="T71" t="str">
-        <v>10.1002/fes3.172</v>
+        <v>https://doi.org/10.1002/fes3.172</v>
       </c>
       <c r="U71" t="str">
         <v>This study undertakes an ex-ante evaluation of the effects of alternative technology and policy options on soybean supply and demand in sub-Saharan Africa (SSA) to 2050. Current soybean consumption in SSA is dominated by cooking oil followed by soybean cake used as animal feed. Due to weak processing sectors and low soybean yields, the region is currently importing about 70% of its consumption requirements. Sub-Saharan Africa spends more than US$1 billion on net imports of soybean-based agricultural products. A combination of promising innovations affecting the soybean value chain across SSA would be required to close the future soybean demand gap.</v>
       </c>
       <c r="V71" t="str">
-        <v>climate change, geospatial bio-economic modeling, IMPACT, import dependency, soybean, sub-Saharan Africa</v>
+        <v>soybean, ex-ante evaluation, sub-Saharan Africa, agricultural innovation, food security, climate change, crop modeling, value chain, technology adoption, policy analysis</v>
       </c>
     </row>
     <row r="72" xml:space="preserve">
@@ -6841,13 +6841,13 @@
 Funded by USAID via Africa RISING under Feed the Future</v>
       </c>
       <c r="T72" t="str">
-        <v>10.1016/j.heliyon.2023.e20199</v>
+        <v>https://doi.org/10.1016/j.heliyon.2023.e20199</v>
       </c>
       <c r="U72" t="str">
         <v>Ricinodendron heudelotii is an important nutraceutical reservoir whose sustainable exploitation requires information on its potential distribution in the current context of rapid population growth and climate change threats. This study aimed to map suitable areas for its domestication and conservation under current and future climate conditions in Benin. Currently, about four percent (5082 km²) of the country's area mainly located in the sub-humid and humid zones were potentially suitable. Under future climatic conditions, the potentially suitable areas were mainly in the sub-humid zone, but almost all highly suitable areas in the humid zone will become medium suitable by 2055 and 2085. This species will migrate following its ecological requirements linked mainly to isothermality, mean annual rainfall, and soil sand content.</v>
       </c>
       <c r="V72" t="str">
-        <v>biodiversity, modelling, climate change, habitats, spatial distribution</v>
+        <v>habitat distribution, species distribution modeling, Ricinodendron heudelotii, climate change, Benin, West Africa, conservation, biomod2, RCP scenarios, range shift</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
@@ -6933,7 +6933,7 @@
 Emphasizes combining conventional and modern tools to accelerate cassava improvement</v>
       </c>
       <c r="T73" t="str">
-        <v>10.17660/ActaHortic.2018.1225.4</v>
+        <v>https://doi.org/10.17660/ActaHortic.2018.1225.4</v>
       </c>
       <c r="U73" t="str">
         <v>This paper examines the sustainability of African vegetable production in the face of future climatic uncertainty and increasing biotic stressors. Climate change is expected to significantly affect vegetable production systems across Africa through changes in temperature, precipitation patterns, and increased pest and disease pressure. The study discusses how these factors will influence crop productivity, food security, and livelihoods of smallholder farmers. Adaptation strategies and the potential role of climate-resilient vegetable varieties are explored to address these challenges.</v>
@@ -7027,13 +7027,13 @@
 Potential for root traits to contribute to cost-effective breeding in resource-limited environments</v>
       </c>
       <c r="T74" t="str">
-        <v>10.1080/17429145.2019.1643934</v>
+        <v>https://doi.org/10.1080/17429145.2019.1643934</v>
       </c>
       <c r="U74" t="str">
         <v>The study examined how seasonal variations in microclimate and coffee leaf rust (CLR) incidence across different altitudes and shading systems affect coffee production. At mid and high altitudes, high CLR incidence occurred in the shading system showing a low diurnal temperature range and a high dew point temperature. The findings demonstrate that microclimate conditions created by shading systems significantly influence disease pressure and must be considered in climate adaptation strategies for coffee production.</v>
       </c>
       <c r="V74" t="str">
-        <v>coffee leaf rust, climate variability, altitude, microclimate, shading systems, agroforestry</v>
+        <v>coffee, coffee leaf rust, altitude, microclimate, shading systems, agroforestry, disease management, climate adaptation, environmental interactions, tropical crops</v>
       </c>
     </row>
     <row r="75" xml:space="preserve">
@@ -7123,13 +7123,13 @@
 Stresses the need to bridge researchâ€“practice divides through stakeholder co-production of knowledge</v>
       </c>
       <c r="T75" t="str">
-        <v>10.3390/su15010190</v>
+        <v>https://doi.org/10.3390/su15010190</v>
       </c>
       <c r="U75" t="str">
         <v>The paper advances a gender equality and social inclusion (GESI) framework for incorporating climate information services (CIS), which is becoming central due to ongoing climate change and climate variability. Gender is understood as a social construct of who women and men are supposed to be. Gender inequalities seem to be enduring such that, despite innovations in agricultural and climate information technologies, unequal gender power dynamics will still emerge. The framework has five indicators: (1) gender targeting by intentional design, (2) collection of sex-disaggregated data, (3) conduct analysis of sex-disaggregated data, (4) dissemination of technological options, and (5) continuous monitoring of gender and ongoing empowerment evaluation.</v>
       </c>
       <c r="V75" t="str">
-        <v>gender equality, social inclusion, climate information services, climate change adaptation, gender mainstreaming, Africa</v>
+        <v>gender equality, social inclusion, GESI, climate information services, climate adaptation, vulnerability, accessibility, marginalized groups, climate variability, equity</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -7215,13 +7215,13 @@
 Suggests shift in EU protein crop strategy for health, sustainability, and climate resilience</v>
       </c>
       <c r="T76" t="str">
-        <v>10.1016/j.jssas.2024.06.004</v>
+        <v>https://doi.org/10.1016/j.jssas.2024.06.003</v>
       </c>
       <c r="U76" t="str">
         <v>This study evaluated farmers' knowledge of soil quality and yield assessment among cassava farmers in southwestern Nigeria. Data were collected on farmers' demography, farming experience, criteria for selecting sites for cassava cultivation, and methods of yield prediction. Farmers use a combination of soil and vegetation-based criteria to assess soil quality from which the decision to cultivate a given land is made. Among the soil-based criteria, soil drainage, colour, and depth rank the most and are most used. The study highlights the importance of integrating local knowledge with scientific approaches for sustainable cassava production under changing climatic conditions.</v>
       </c>
       <c r="V76" t="str">
-        <v>soil quality, cassava, farmer assessment, indigenous knowledge, yield prediction, Nigeria</v>
+        <v>cassava, soil quality, farmer knowledge, indigenous knowledge, root yield, Nigeria, cropping systems, soil assessment, agricultural practices, local expertise</v>
       </c>
     </row>
     <row r="77" xml:space="preserve">
@@ -7305,13 +7305,13 @@
 Highlights pest-climate-resource dynamics as critical under climate change</v>
       </c>
       <c r="T77" t="str">
-        <v>10.3390/genes11091054</v>
+        <v>https://doi.org/10.3390/genes11091054</v>
       </c>
       <c r="U77" t="str">
         <v>Genetic adaptation of maize to the increasingly unpredictable climatic conditions is an essential prerequisite for achievement of food security and sustainable development goals in sub-Saharan Africa. The landraces of maize, which have not served as sources of improved germplasm, are invaluable sources of novel genetic variability crucial for achieving this objective. The overall goal of this study was to assess the genetic diversity and population structure of a maize panel of 208 accessions, comprising landrace gene pools from Burkina Faso (58), Ghana (43), and Togo (89), together with reference populations (18) from the International Institute of Tropical Agriculture (IITA). Genotyping with 5974 DArTseq-SNP markers revealed immense genetic diversity indicated by average expected heterozygosity (0.36), observed heterozygosity (0.5), and polymorphic information content (0.29).</v>
       </c>
       <c r="V77" t="str">
-        <v>landraces, genetic diversity, population structure, West Africa, maize improvement, DArTseq markers</v>
+        <v>maize, landraces, genomic analysis, genetic diversity, West Africa, Sahel, crop improvement, genetic enhancement, population structure, breeding</v>
       </c>
     </row>
     <row r="78" xml:space="preserve">
@@ -7403,13 +7403,13 @@
 Planned indicators: root biomass, microbial biomass, mineral-associated SOC, yield-SOC tradeoffs</v>
       </c>
       <c r="T78" t="str">
-        <v>10.1371/journal.pone.0222941</v>
+        <v>https://doi.org/10.1371/journal.pone.0222941</v>
       </c>
       <c r="U78" t="str">
         <v>Scapsipedus icipe Hugel and Tanga (Orthoptera: Gryllidae) is a newly described edible cricket species. Although there is substantial interest in mass production of S. icipe for human food and animal feed, no information exists on the impact of temperature on their bionomics. Temperature-dependent development, survival, reproductive and life table parameters of S. icipe was generated and integrated into advanced Insect Life Cycle Modeling software to describe relative S. icipe population increase and spatial spread based on nine constant temperature conditions. The lowest developmental threshold temperatures was 14.3, 12.67 and 19.12°C and the thermal constants for development were 185.2, 1111.1 and 40.7 degree days for egg, nymph and pre-adult stages, respectively. The highest total fecundity, intrinsic rate of natural increase, net reproductive rate and shortest doubling time was recorded at 30°C.</v>
       </c>
       <c r="V78" t="str">
-        <v>edible cricket, Scapsipedus icipe, temperature-dependent development, life table, climate modeling, Africa</v>
+        <v>insect life cycle modeling, temperature-dependent, edible insects, cricket, ILCYM, species distribution, climate suitability, entomology, sustainable protein, Africa</v>
       </c>
     </row>
     <row r="79" xml:space="preserve">
@@ -7501,13 +7501,13 @@
 Strong call for iterative modeling plus localized rural diagnostics</v>
       </c>
       <c r="T79" t="str">
-        <v>10.3389/fpls.2022.782140</v>
+        <v>https://doi.org/10.3389/fpls.2022.782140</v>
       </c>
       <c r="U79" t="str">
         <v>Dietary diversification and incorporation of resilient crop species such as under-exploited leguminous species referred to as orphan, minor, or underutilized into food systems in Sub-Saharan Africa (SSA) is critical for addressing the current challenges of malnutrition, food insecurity, and climate change. These crops have great potential for improved food security and nutrition, yet they remain neglected and underutilized despite their nutritional and health benefits. The exploitation of orphan legumes can contribute significantly to the achievement of the Sustainable Development Goals (SDGs), particularly those related to zero hunger, good health and well-being, and climate action.</v>
       </c>
       <c r="V79" t="str">
-        <v>climate change, food security, malnutrition, orphan legumes, sustainable development goals</v>
+        <v>orphan legumes, underutilized crops, food security, nutrition security, Sub-Saharan Africa, dietary diversification, protein security, climate resilience, legumes, agricultural biodiversity</v>
       </c>
     </row>
     <row r="80" xml:space="preserve">
@@ -7599,13 +7599,13 @@
 Funded in part by CCAFS and the NextGen Cassava project</v>
       </c>
       <c r="T80" t="str">
-        <v>10.1094/PHYTO-03-17-0082-FI</v>
+        <v>https://doi.org/10.3389/fagro.2022.957011</v>
       </c>
       <c r="U80" t="str">
         <v>Resistance genes are a major tool for managing crop diseases. The networks of crop breeders who exchange resistance genes and deploy them in varieties help to determine the global landscape of resistance and epidemics, an important system for maintaining food security. These networks function as a complex adaptive system, with associated strengths and vulnerabilities, and implications for policies to support resistance gene deployment strategies. Extensions of epidemic network analysis can be used to evaluate the multilayer agricultural networks that support and influence crop breeding networks. Here, we evaluate the general structure of crop breeding networks for cassava, potato, rice, and wheat. All four are clustered due to phytosanitary and intellectual property regulations, and linked through CGIAR hubs. Cassava networks primarily include public breeding groups, whereas others are more mixed.</v>
       </c>
       <c r="V80" t="str">
-        <v>resistance genes, crop breeding networks, disease resistance, cassava, potato, rice, wheat, CGIAR, phytopathology</v>
+        <v>agroecology, regenerative agriculture, rainfed conditions, small farms, food systems, diets, activism, choices</v>
       </c>
     </row>
     <row r="81" xml:space="preserve">
@@ -7683,13 +7683,13 @@
 Highlights the need for additional research into evolutionary and ecological resilience in tropical species.</v>
       </c>
       <c r="T81" t="str">
-        <v>10.1242/bio.058619</v>
+        <v>https://doi.org/10.1186/s12915-017-0356-8</v>
       </c>
       <c r="U81" t="str">
         <v>Thermal adaptation to habitat variability can determine species vulnerability to environmental change. For example, physiological tolerance to naturally low thermal variation in tropical forests species may alter their vulnerability to climate change impacts, compared with open habitat species. The study investigated the role of habitat in structuring thermal limits, critical thermal maximum (CTmax) and minimum (CTmin), for Bicyclus dorothea (Cramer, 1779), a nymphalid butterfly found in both forest and ecotone habitats in many tropical African countries.</v>
       </c>
       <c r="V81" t="str">
-        <v>thermal tolerance, climate change, tropical butterfly, habitat adaptation, Bicyclus dorothea, Africa</v>
+        <v>Botanical exploration, Digitization, Floristic patterns, Herbarium specimens, Plant growth form, Species richness, Tropical forests</v>
       </c>
     </row>
     <row r="82" xml:space="preserve">
@@ -7771,13 +7771,13 @@
 Open-access data can be linked with agronomic or socioeconomic datasets for future impact studies.</v>
       </c>
       <c r="T82" t="str">
-        <v>10.5194/essd-13-4133-2021</v>
+        <v>https://doi.org/10.1016/j.cois.2022.100961</v>
       </c>
       <c r="U82" t="str">
         <v>The African Tropics are hotspots of modern-day land use change and are, at the same time, of great relevance for the cycling of carbon (C) and nutrients between plants, soils, and the atmosphere. However, the consequences of land conversion on biogeochemical cycles are still largely unknown as they are not studied in a landscape context that defines the geomorphic, geochemical, and pedological framework in which biological processes take place. Thus, the response of tropical soils to disturbance by erosion and land conversion is one of the great uncertainties in assessing the carrying capacity of tropical landscapes to grow food for future generations and in predicting greenhouse gas fluxes from soils to the atmosphere and, hence, future earth system dynamics. Here we describe version 1.0 of an open-access database created as part of the project Tropical soil organic carbon dynamics along erosional disturbance gradients in relation to variability in soil geochemistry and land use (TropSOC). TropSOC v1.0 contains spatially and temporally explicit data on soil, vegetation, environmental properties, and land management collected from 136 pristine tropical forest and cropland plots between 2017 and 2020 as part of monitoring and sampling campaigns in the eastern Congo Basin and the East African Rift Valley system.</v>
       </c>
       <c r="V82" t="str">
-        <v>soil organic carbon, tropical soils, land use change, geochemistry, TropSOC, Africa, cropland, forest</v>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="83" xml:space="preserve">
@@ -7863,13 +7863,13 @@
 Recommends further refinement of repellent use and integration of biocontrol agents in net house systems.</v>
       </c>
       <c r="T83" t="str">
-        <v>10.1016/j.cropro.2020.105449</v>
+        <v>https://doi.org/10.3390/insects12040273</v>
       </c>
       <c r="U83" t="str">
         <v>The study investigated a push-pull strategy to prevent small insect pest outbreaks in a net house, where the push component consisted of two stimulus plants (Cymbopogon citratus and Tagetes minuta), and the pull stimuli consisted of visual cues from blue and yellow sticky traps. Field experiments were set up in central Kenya and conducted during a rainy and a dry season. Net house and net house + push-pull reduced insect pest infestations, except Aphis craccivora in the dry period. The push-pull strategy reduced Empoasca sp. infestations in the rainy period. Cowpea pod yields and quality were higher in the net house treatments in both periods. Cowpea pod and grain yield and quality were higher in the net house and net house + push-pull treatments than in the control irrespective of the period.</v>
       </c>
       <c r="V83" t="str">
-        <v>push-pull strategy, cowpea, integrated pest management, net houses, Cymbopogon citratus, Tagetes minuta, Kenya</v>
+        <v>Spodoptera Frugiperda, Climate Change, Pest Management, Biological Control, Machine Learning, Decision Support, Parasitoids</v>
       </c>
     </row>
     <row r="84" xml:space="preserve">
@@ -7961,13 +7961,13 @@
 IITA is identified as a central hub for research, diagnostics, and capacity development through its Nairobi office and broader regional platforms.</v>
       </c>
       <c r="T84" t="str">
-        <v>10.1146/annurev-phyto-080417-045833</v>
+        <v>https://doi.org/10.1016/j.agsy.2018.09.009</v>
       </c>
       <c r="U84" t="str">
         <v>Challenges in Sub-Saharan Africa including low agricultural productivity, exploding populations, and escalating urbanization have led to declining per capita food availability. Crop production intensification brings elevated threats from pests and diseases, including plant-parasitic nematodes. This review examines the impact of plant-parasitic nematodes on food security in Sub-Saharan Africa.</v>
       </c>
       <c r="V84" t="str">
-        <v>plant-parasitic nematodes, food security, Sub-Saharan Africa, agricultural productivity, crop pests</v>
+        <v>Adaptation, Agriculture, Climate change, Mitigation, Research</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
@@ -8059,13 +8059,13 @@
 Emphasizes seed system innovations and partnerships to accelerate delivery and adoption of new varieties.</v>
       </c>
       <c r="T85" t="str">
-        <v>10.1111/pbr.12682</v>
+        <v>https://doi.org/10.3390/su10061990</v>
       </c>
       <c r="U85" t="str">
         <v>Formal public sector soybean breeding in Africa spans over four decades, and it was initiated by the International Institute of Tropical Agricultural (IITA). As the demand of soybean continues to outstrip production, strategic projects such the Tropical Legume (TL) were initiated, in which the main goal was to enhance the productivity of soybean in the farmers' fields in Sub-Saharan Africa. One of the strategies to enhance the productivity of soybean in the farmers' fields is through developing and deploying improved soybean varieties in the target countries. Through the TL I and TL II projects, a number of varieties were released in the target countries, Kenya, Nigeria, Malawi and Mozambique by employing participatory variety selection (PVS). This review provides highlights of the achievements made by IITA breeding programme and insights of what needs to be done to enhance yield improvement for soybean in Africa using demand-driven breeding approaches.</v>
       </c>
       <c r="V85" t="str">
-        <v>soybean breeding, Glycine max, African tropics, IITA, Tropical Legume project, cultivar development, participatory variety selection</v>
+        <v>climate-smart agriculture, institutions, adaptation, mitigation, systematic review</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
@@ -8135,13 +8135,13 @@
         <v>Funded by the European Commission Erasmus Mundus program and CGIAR Roots, Tubers and Bananas. Suggests use of multi-species models for future studies.</v>
       </c>
       <c r="T86" t="str">
-        <v>10.1007/s10340-018-1059-9</v>
+        <v>https://doi.org/10.1016/j.cosust.2014.07.002</v>
       </c>
       <c r="U86" t="str">
         <v>Whiteflies (Hemiptera: Aleyrodidae) are important insect pests causing serious damage to plants and transmitting hundreds of plant viruses. Climate change is expected to influence life history and trophic interactions among plants, whiteflies and their natural enemies. Here, we review the potential impacts of climate change on whiteflies and the likely consequences for agricultural systems. This review concludes that while climatic stress tends to negatively affect life history traits, the effects differ with the tolerance of the whiteflies and the amount of stress experienced. Whiteflies also differ in their adaptability. Better adapted species will likely experience increased distribution and abundance provided their tolerance limits are not exceeded, while species with lower tolerance and adaptation limits will suffer reduced fitness, which will have overall effects on their distribution and abundance in space.</v>
       </c>
       <c r="V86" t="str">
-        <v>whiteflies, climate change, plant viruses, Bemisia tabaci, pest management, temperature tolerance</v>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
@@ -8211,13 +8211,13 @@
         <v>Funded by the International Potato Center and CGIAR. Results contribute to predictive modeling of pest behavior under climate change scenarios.</v>
       </c>
       <c r="T87" t="str">
-        <v>10.1007/s10340-020-01249-z</v>
+        <v>https://doi.org/10.1007/s10113-015-0838-6</v>
       </c>
       <c r="U87" t="str">
         <v>The whiteflies belonging to the species group Bemisia tabaci transmit viruses that are the greatest constraint to the production of cassava, Africa's most important food security crop. The study examined the life history of an endemic African population of B. tabaci SSA-ESA at six constant temperatures (16, 20, 24, 28, 32, 36 °C) in controlled environment chambers, and for 10 generations in the field. Oviposition occurred between 20 and 28 °C, with highest fecundity (114.5 ± 88.2) eggs per female at 20 °C. Similarly, B. tabaci adult females average survival time was longest (19.7 days) at 24 °C, and shortest (8.5 days) at 36 °C. Immature development time decreased with increasing temperature from 59.3 days at 16 °C to 16.3 days at 28 °C, and increased above 28 °C. A constant temperature of 36 °C was lethal to eggs and first instars and no immature stage developed further to adults at this temperature.</v>
       </c>
       <c r="V87" t="str">
-        <v>Bemisia tabaci, cassava, whiteflies, temperature dependence, life history, climate change, SSA-ESA</v>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="88" xml:space="preserve">
@@ -8291,13 +8291,13 @@
         <v>Study funded by Erasmus Mundus Joint Doctorate and supported by CGIAR-RTB. Emphasizes need for national adaptation strategies linked to cassava health.</v>
       </c>
       <c r="T88" t="str">
-        <v>10.31817/vjas.2021.4.1.03</v>
+        <v>https://doi.org/10.2135/cropsci2012.09.0545</v>
       </c>
       <c r="U88" t="str">
         <v>Study on production characteristics and adaptation strategies for managing cassava whiteflies and viruses under climate change conditions in Tanzania.</v>
       </c>
       <c r="V88" t="str">
-        <v>cassava, climate change, whiteflies, viruses, Tanzania, adaptation strategies, Bemisia tabaci</v>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="89" xml:space="preserve">
@@ -8377,13 +8377,13 @@
         <v>Backed by Gates Foundation and Stress Tolerant Maize for Africa (STMA) initiative. Data available via IITA CKAN repository.</v>
       </c>
       <c r="T89" t="str">
-        <v>10.3389/fsufs.2023.1238776</v>
+        <v>https://doi.org/10.1016/j.agsy.2022.103508</v>
       </c>
       <c r="U89" t="str">
         <v>In West and Central Africa (WCA), drought and low soil nitrogen (low N) impede increased maize (Zea mays L.) productivity and production. Due to climate change, the two stresses usually occur together, leading to food, nutritional, and economic insecurity in the sub-region. Moderate to high estimates of heritability were observed for most of the measured traits under stress conditions, indicating that the traits could be easily transmitted to the progenies. Fifty-seven out of the 96 QPM inbreds evaluated exhibited varying degrees of resilience to drought and low N.</v>
       </c>
       <c r="V89" t="str">
-        <v>climate change, drought, indirect selection for high yield, low soil nitrogen, quality protein maize, stress resilient maize</v>
+        <v>Climate change adaptation, Root tuber and banana crops, African Great Lakes Region, Spatial prioritisation, Socio-agroecological homologues, Risk assessment, Climate-smart agriculture</v>
       </c>
     </row>
     <row r="90" xml:space="preserve">
@@ -8469,13 +8469,13 @@
         <v>Funded by USAID and CGIAR Roots, Tubers and Bananas (RTB). Highlights knowledge gaps in pathogen-host dynamics and need for multi-environment resistance screening protocols.</v>
       </c>
       <c r="T90" t="str">
-        <v>10.1111/ppa.12824</v>
+        <v>https://doi.org/10.1108/JADEE-08-2023-0214</v>
       </c>
       <c r="U90" t="str">
         <v>Banana and plantain (Musa spp.) are important food crops in tropical and subtropical regions of the world where they generate millions of dollars annually to both subsistence farmers and exporters. Since 1902, Pseudocercospora banana pathogens, Pseudocercospora fijiensis, P. musae and P. eumusae, have emerged as major production constraints to banana and plantain. Despite concerted efforts to counter these pathogens, they have continued to negatively impact banana yield. In this review, the economic importance, distribution and the interactions between Pseudocercospora banana pathogens and Musa species are discussed. Interactions are further scrutinized in the light of an emerging climate change scenario and efforts towards the development of resistant banana germplasm are discussed.</v>
       </c>
       <c r="V90" t="str">
-        <v>Not available in search results</v>
+        <v>Not explicitly provided in search results</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
@@ -8553,13 +8553,13 @@
         <v>First national study assessing small grain mycotoxin risks in Zimbabwe. Supports regional policy reforms for grain safety and storage.</v>
       </c>
       <c r="T91" t="str">
-        <v>10.3390/foods10020287</v>
+        <v>https://doi.org/10.1016/j.ecolecon.2023.107894</v>
       </c>
       <c r="U91" t="str">
         <v>Maize and three small grain cereals (sorghum, pearl millet, and finger millet) produced by smallholder farmers in Zimbabwe during 2016 and 2017 were examined for fungal community structure, and total aflatoxin (AF) and fumonisin (FM) content. A total of 800 maize and 180 small grain samples were collected at harvest and during storage from four agroecological zones. Fusarium spp. dominated the fungi associated with maize. Across crops, Aspergillus flavus constituted the main Aspergillus spp. Small grain cereals were less susceptible to both AF and FM. AF (52%) and FM (89%) prevalence was higher in maize than in small grains (13–25% for AF and 0–32% for FM). Less than 2% of small grain samples exceeded the EU regulatory limit for AF (4 µg/kg), while &lt;10% exceeded the EU regulatory limit for FM (1000 µg/kg).</v>
       </c>
       <c r="V91" t="str">
-        <v>Not available in search results</v>
+        <v>Correlated random effects, Food security, Weather shocks, Resilience capacity, Ghana</v>
       </c>
     </row>
     <row r="92" xml:space="preserve">
@@ -8633,13 +8633,13 @@
         <v>Supports selection and development of drought- and heat-tolerant cowpea varieties suited to low-input environments in West Africa.</v>
       </c>
       <c r="T92" t="str">
-        <v>10.25081/jpsp.2022.v8.7896</v>
+        <v>https://doi.org/10.1371/journal.pstr.0000052</v>
       </c>
       <c r="U92" t="str">
         <v>The study investigated the morpho-physiological responses of two cowpea varieties (IT89KD-288 and IT99K573-1-1) to a combination of stresses (water deficit stress and high light intensity) at different growth stages. Exposure to W4 under L1 considerably reduced cowpea yield by 80% compared to those grown under L3 and full watering. Reduced light intensity enhanced cowpea grain yield irrespective of water deficit stress and IT89KD-288 was superior to IT99K573-1-1. In conclusion, reduced light intensity enhanced cowpea tolerance to water deficit and increased yield. Cowpea response was dependent on growth stage, variety and severity of stress.</v>
       </c>
       <c r="V92" t="str">
-        <v>Not available in search results</v>
+        <v>Climate-Smart agriculture, One-Health, Ghana, Benin, socio-economic determinants, innovation adoption, meta-analysis</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
@@ -8709,13 +8709,13 @@
         <v>Highlights ideational power in shaping resistance to gender policy in climate adaptation; relevant to broader gender policy efforts beyond Uganda.</v>
       </c>
       <c r="T93" t="str">
-        <v>10.1111/dpr.12458</v>
+        <v>https://doi.org/10.1016/j.wace.2014.04.004</v>
       </c>
       <c r="U93" t="str">
         <v>Expectations that gender-mainstreaming efforts would effectively advance gender equality have been disappointed in contemporary sub-Saharan Africa. Examining this apparent disconnect, we focus on the narratives through which policy-makers relate to, and dis/engage with, gender issues. The research found that narrative shifts exercise four distinct power effects: They (1) shift blame for ineffective gender implementation; (2) legitimize policy inaction; (3) foreground and naturalize patriarchy; and (4) promote the diversion of resources.</v>
       </c>
       <c r="V93" t="str">
-        <v>Africa, climate change, gender mainstreaming, ideational power, policy narrative, Uganda</v>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -8788,13 +8788,13 @@
         <v>Part of CGIAR Climate Change, Agriculture and Food Security (CCAFS) and Forest, Trees and Agroforestry (FTA) programs.</v>
       </c>
       <c r="T94" t="str">
-        <v>10.1016/j.agsy.2020.102812</v>
+        <v>https://doi.org/10.1111/ecog.06139</v>
       </c>
       <c r="U94" t="str">
         <v>Improving management practices of cocoa (Theobroma cacao L.) cultivation especially under future climate change requires knowledge of yield gaps and their determining factors. The study assessed yield gaps and their determining factors through multiple regression modelling in smallholder cocoa agroforestry systems in Ghana along a climatic gradient. The studied zones referred to as dry, mid and wet with annual rainfall of 1200, 1200–1400 and 1400–2000 mm respectively. High relative yield gap in dry zone due to low intensification and climatic risk. Labour and available P significantly determined yield gap in the dry and mid zones. Access to trainings and use of hybrid seeds reduced yield gaps in the wet zone.</v>
       </c>
       <c r="V94" t="str">
-        <v>theobroma cacao; yield gap; yield factors; climate change; smallholders; intensification</v>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -8872,13 +8872,13 @@
         <v>Religious and spiritual beliefs influence climate perceptions. Radio/TV is the main source of climate info. The study suggests scaling up institutional support to enhance resilience.</v>
       </c>
       <c r="T95" t="str">
-        <v>10.3390/su14052847</v>
+        <v>https://doi.org/10.3390/su16135766</v>
       </c>
       <c r="U95" t="str">
         <v>Sahelian countries, particularly Niger, are more vulnerable to climate change due to the high dependence of most of their populations on rain-fed agriculture and limited capacities to respond to climate variability and change. This paper examines the factors influencing climate change adaptation strategies and the impacts on household income and food security in rural Niger. The results showed that crop diversification (72.74%), income diversification (67.97%) and changing planting times (55%) are the main adaptation strategies adopted by households. The majority of respondents had noticed changes in rain patterns (93.21%), in the amount of rain (91.25%) and in the intensity of rain (81.82%) during the last five years.</v>
       </c>
       <c r="V95" t="str">
-        <v>adaptation strategies; climate change; households; logit regression; matching techniques</v>
+        <v>climate change adaptation; food insecurity; vulnerability; multinomial endogenous treatment effect; smallholder farmers; Ethiopia</v>
       </c>
     </row>
     <row r="96" xml:space="preserve">
@@ -8956,7 +8956,7 @@
         <v>Stresses need for integrated, tailored adaptation packages and policies that consider inequality. Highlights the role of livestock as coping assets and the limitations of self-reliance in the face of compound shocks.</v>
       </c>
       <c r="T96" t="str">
-        <v>10.1016/j.agsy.2017.02.006</v>
+        <v>https://doi.org/Not available in search results</v>
       </c>
       <c r="U96" t="str">
         <v>This paper provides an ex-ante assessment of the impacts of climate and price variability on household income and food security in Ethiopia and Ghana. The study applies an agent-based modelling approach to highlight the role of coping and adaptation strategies under climate and price variability. Our simulation results show that climate and price variability adversely affects income and food security of households in both countries. Self-coping mechanisms are found to be important but insufficient to mitigate the adverse effects of variability, implying the need for policy interventions. Adaptation strategies composed of a portfolio of actions such as the provision of production credit and access to improved seeds are found to be effective in reducing the impacts of climate and price variability in Ethiopia.</v>
@@ -9054,7 +9054,7 @@
 Strong connection to farmer memory recall and context-specific responses to climate threats</v>
       </c>
       <c r="T97" t="str">
-        <v>10.1007/s10113-012-0351-0</v>
+        <v>https://doi.org/10.3390/agronomy13030727</v>
       </c>
       <c r="U97" t="str">
         <v>The savanna region of Africa is a potential breadbasket of the continent but is severely affected by climate change. Understanding farmers' perceptions of climate change and the types of adjustments they have made in their farming practices in response to these changes will offer some insights into necessary interventions to ensure a successful adaptation in the region. This paper explores how smallholder farmers in the Nigerian savanna perceive and adapt to climate change. The results show that most of the farmers have noticed changes in climate and have consequently adjusted their farming practices to adapt. There are no large differences in the adaptation practices across the region, but farmers in Sudan savanna agro-ecological zone are more likely to adapt to changes in temperature than those in northern Guinea savanna.</v>
@@ -9140,7 +9140,7 @@
 Grounded in national policy relevance (SDGs 1, 2, and 13)</v>
       </c>
       <c r="T98" t="str">
-        <v>10.1016/j.jclepro.2018.06.221</v>
+        <v>https://doi.org/10.1016/j.gfs.2016.08.003</v>
       </c>
       <c r="U98" t="str">
         <v>The paper explores the nexus of rainfall variability and food poverty, which is important for appropriate understanding of the temporal and spatial conditions of the situation, and for policy intervention for Nigeria, which is Africa's most populous and largest economy. The study focuses on Nigeria's agrarian economy which is largely rain-fed, noting that changes in the mean and variability of rainfall affect the hydrological cycle (onset and cessation) of rainfall, with significant effects on rain-fed agricultural and food production systems, and that variability in rainfall can be expected to intensify the cycle of poverty in an agrarian economy like Nigeria.</v>
@@ -9238,13 +9238,13 @@
 Emphasizes value of African breeding programs using IITA germplasm in drought-prone zones.</v>
       </c>
       <c r="T99" t="str">
-        <v>10.3389/fphys.2013.00093</v>
+        <v>https://doi.org/10.1111/wre.12304</v>
       </c>
       <c r="U99" t="str">
         <v>Cassava is an important crop in Africa, Asia, Latin America, and the Caribbean. Cassava can be produced adequately in drought conditions making it the ideal food security crop in marginal environments. Although cassava can tolerate drought stress, it can be genetically improved to enhance productivity in such environments. Drought adaptation studies in over three decades in cassava have identified relevant mechanisms which have been explored in conventional breeding. This paper highlights some modified traits suitable for early-growth phase phenotyping that may be used to reduce drought phenotyping cycle in cassava. The need for metabolite profiling, improved phenomics to take advantage of next generation sequencing technologies and high throughput phenotyping are basic steps for future direction to improve genetic gain and maximize speed for drought tolerance breeding.</v>
       </c>
       <c r="V99" t="str">
-        <v>adaptation; drought tolerance; modern breeding; phenotyping; storage roots</v>
+        <v>agroecology; integrated weed management; invasive plants; transdisciplinary research; weed adaptation</v>
       </c>
     </row>
     <row r="100" xml:space="preserve">
@@ -9328,13 +9328,13 @@
 A rare example of interdisciplinary agenda-setting within agricultural science.</v>
       </c>
       <c r="T100" t="str">
-        <v>10.1111/wre.12304</v>
+        <v>https://doi.org/10.1016/j.jclepro.2018.06.221</v>
       </c>
       <c r="U100" t="str">
         <v>Weedy plants pose a major threat to food security, biodiversity, ecosystem services and consequently to human health and wellbeing. However, many currently used weed management approaches are increasingly unsustainable. To address this knowledge and practice gap, in June 2014, 35 weed and invasion ecologists, weed scientists, evolutionary biologists and social scientists convened a workshop to explore current and future perspectives and approaches in weed ecology and management. A horizon scanning exercise ranked a list of 124 pre-submitted questions to identify a priority list of 30 questions.</v>
       </c>
       <c r="V100" t="str">
-        <v>agroecology; integrated weed management; invasive plants; transdisciplinary research; weed adaptation</v>
+        <v>Not available in search results</v>
       </c>
     </row>
     <row r="101" xml:space="preserve">
@@ -9418,13 +9418,13 @@
 Supports use of ex-ante modeling for climate-resilient agricultural investments</v>
       </c>
       <c r="T101" t="str">
-        <v>10.1016/j.gfs.2016.08.003</v>
+        <v>https://doi.org/10.1016/j.agsy.2020.102812</v>
       </c>
       <c r="U101" t="str">
         <v>Achieving and maintaining global food security is challenged by changes in population, income, and climate, among other drivers. Assessing these threats and weighing possible solutions requires a robust multidisciplinary approach. The paper uses the IMPACT system of models to run alternative scenarios for drought and heat tolerant crop varieties under two extreme future climate scenarios. Detailed, location-specific data on climate, soil type, and physiological crop parameters are incorporated into the DSSAT crop models. The structural approach captures key knowledge across multiple areas of expertise. Economic responses reduce yield shocks from crop models. Drought and heat tolerant crops improve productivity with or without climate change.</v>
       </c>
       <c r="V101" t="str">
-        <v>Not available in search results</v>
+        <v>theobroma cacao; yield gap; yield factors; climate change; smallholders; intensification</v>
       </c>
     </row>
     <row r="102" xml:space="preserve">
@@ -9510,13 +9510,13 @@
 Recommends integrating indigenous knowledge with scientific forecasts for better targeting of adaptation policies</v>
       </c>
       <c r="T102" t="str">
-        <v>10.1080/17565529.2017.1374236</v>
+        <v>https://doi.org/10.1111/dpr.12458</v>
       </c>
       <c r="U102" t="str">
         <v>Not available in search results</v>
       </c>
       <c r="V102" t="str">
-        <v>Not available in search results</v>
+        <v>Africa, climate change, gender mainstreaming, ideational power, policy narrative, Uganda</v>
       </c>
     </row>
     <row r="103" xml:space="preserve">
@@ -9606,7 +9606,7 @@
 Suggests that adaptation will require moving coffee production upslope, which may threaten biodiversity conservation areas.</v>
       </c>
       <c r="T103" t="str">
-        <v>10.1016/j.agrformet.2015.03.005</v>
+        <v>https://doi.org/10.1111/ppa.12824</v>
       </c>
       <c r="U103" t="str">
         <v>Coffee is the world's most valuable tropical export crop. Recent studies predict severe climate change impacts on Coffea arabica (C. arabica) production. However, quantitative production figures are necessary to provide coffee stakeholders and policy makers with evidence to justify immediate action. Using data from the northern Tanzanian highlands, we demonstrate for the first time that increasing night time (Tmin) temperature is the most significant climatic variable responsible for diminishing C. arabica yields between 1961 and 2012. Projecting this forward, every 1 °C rise in Tmin will result in annual yield losses of 137 ± 16.87 kg ha−1. According to our ARIMA model, average coffee production will drop to 145 ± 41 kg ha−1 by 2060. Consequently, without adequate adaptation strategies and/or substantial external inputs, coffee production will be severely reduced in the Tanzanian highlands in the near future.</v>
@@ -9692,13 +9692,13 @@
         <v>Supports climate-smart decision-making for sorghum intensification. Combines APSIM modeling, field trials, and policy relevance. Funded through CGIAR and TAMASA initiative.</v>
       </c>
       <c r="T104" t="str">
-        <v>10.3390/agronomy13030727</v>
+        <v>https://doi.org/10.1111/pbr.12682</v>
       </c>
       <c r="U104" t="str">
         <v>In the context of climate change, the sowing date and cultivar choice can influence the productivity of sorghum, especially where production is constrained by low soil fertility and early terminal drought across the challenging agro-ecologies of north-eastern Nigeria. The APSIM crop model was calibrated and validated to simulate the growth and yield of sorghum cultivars with differing maturing periods sown within varying planting time windows under improved agricultural practices. The seasonal climate simulations across sites and AEZs suggested increased yields when using adapted sorghum cultivars based on the average grain yield threshold of ≥1500 kgha−1. The optimal PWs ranged from 25 May to 30 June for some cultivars while the PWs could be extended to 10 July for others.</v>
       </c>
       <c r="V104" t="str">
-        <v>Not available in search results</v>
+        <v>soybean breeding, Glycine max, African tropics, IITA, Tropical Legume project, cultivar development, participatory variety selection</v>
       </c>
     </row>
     <row r="105" xml:space="preserve">
@@ -9780,13 +9780,13 @@
 Highlights role of human-induced disturbance in driving rapid forest composition shifts</v>
       </c>
       <c r="T105" t="str">
-        <v>10.1038/s41586-021-03483-6</v>
+        <v>https://doi.org/10.1016/j.cropro.2020.105449</v>
       </c>
       <c r="U105" t="str">
         <v>Africa is forecasted to experience large and rapid climate change and population growth during the twenty-first century, which threatens the world's second largest rainforest. Protecting and sustainably managing these African forests requires an increased understanding of their compositional heterogeneity, the environmental drivers of forest composition and their vulnerability to ongoing changes. The study uses a dataset of 6 million trees in more than 180,000 field plots to jointly model the distribution in abundance of the most dominant tree taxa in central Africa, producing continuous maps of the floristic and functional composition of central African forests. The results show that the uncertainty in taxon-specific distributions averages out at the community level, and reveal highly deterministic assemblages.</v>
       </c>
       <c r="V105" t="str">
-        <v>Climate-change impacts; Community ecology; Forest ecology; Tropical ecology; Floristic composition of forest; Functional composition of forest; Soil types; Anthropogenic gradients; African rainforest</v>
+        <v>push-pull strategy, cowpea, integrated pest management, net houses, Cymbopogon citratus, Tagetes minuta, Kenya</v>
       </c>
     </row>
     <row r="106" xml:space="preserve">
@@ -9878,13 +9878,13 @@
 The project linked closely with Africa RISINGâ€™s technology park and on-farm trials</v>
       </c>
       <c r="T106" t="str">
-        <v>Not available in search results</v>
+        <v>https://doi.org/10.5194/essd-13-4133-2021</v>
       </c>
       <c r="U106" t="str">
         <v>Smallholder farmers in Northern Ghana regularly face shocks, challenging the sustainability of their farms and livelihoods. Different farm households and household members may be differently affected and respond with different coping strategies. We combined whole-farm modelling and farmer consultations to investigate the vulnerability, buffer and adaptive capacity of three farm types in Northern Ghana towards severe climate, economic and social shocks. Our model results indicate that the drought shock would most severely affect all farm types, drastically reducing their operating profits and soil organic matter balance.</v>
       </c>
       <c r="V106" t="str">
-        <v>Not available in search results</v>
+        <v>soil organic carbon, tropical soils, land use change, geochemistry, TropSOC, Africa, cropland, forest</v>
       </c>
     </row>
     <row r="107" xml:space="preserve">
@@ -9966,13 +9966,13 @@
 Highlights relevance for informing early warning, planning, and climate adaptation priorities in vulnerable Sahelian states</v>
       </c>
       <c r="T107" t="str">
-        <v>10.1080/01431161.2023.2234094</v>
+        <v>https://doi.org/10.1094/PHYTO-03-17-0082-FI</v>
       </c>
       <c r="U107" t="str">
         <v>Agricultural drought is a complex phenomenon with numerous consequences and negative implications for agriculture and food systems. The Sahel is frequently affected by severe droughts, leading to significant losses in agricultural yields. The study develops a new multivariate agricultural drought vulnerability index (MADVI) that combines static and dynamic factors extracted from satellite data. The results showed statistical agreement between the predicted MADVI spatial variability and the reference model (R=0.86 for RF). The overall vulnerability situation in the watershed is 21.8% extreme, 10% very high, 16.8% high, 27.7% moderate, 22.2% low and 1.5% relatively low.</v>
       </c>
       <c r="V107" t="str">
-        <v>Not available in search results</v>
+        <v>resistance genes, crop breeding networks, disease resistance, cassava, potato, rice, wheat, CGIAR, phytopathology</v>
       </c>
     </row>
     <row r="108" xml:space="preserve">
@@ -10060,13 +10060,13 @@
 IITAâ€™s support of this research underlines its focus on resilience and sustainable development in smallholder agriculture in Sub-Saharan Africa.</v>
       </c>
       <c r="T108" t="str">
-        <v>10.3390/su16135766</v>
+        <v>https://doi.org/10.3389/fpls.2022.782140</v>
       </c>
       <c r="U108" t="str">
         <v>Smallholder farmers in Ethiopia face increasing challenges from climate change and variability, which threaten their food security and livelihoods. The study focuses on how climate change adaptation strategies impact household vulnerability to food insecurity in Southwest Ethiopia.</v>
       </c>
       <c r="V108" t="str">
-        <v>climate change adaptation; food insecurity; vulnerability; multinomial endogenous treatment effect; smallholder farmers; Ethiopia</v>
+        <v>orphan legumes, underutilized crops, food security, nutrition security, Sub-Saharan Africa, dietary diversification, protein security, climate resilience, legumes, agricultural biodiversity</v>
       </c>
     </row>
     <row r="109" xml:space="preserve">
@@ -10134,13 +10134,13 @@
         <v>Suggests spatial self-organization may be useful for resilience monitoring, but transient effects mean these systems need long-term observation and caution in interpretation.</v>
       </c>
       <c r="T109" t="str">
-        <v>10.1111/ecog.06139</v>
+        <v>https://doi.org/10.3390/genes11091054</v>
       </c>
       <c r="U109" t="str">
         <v>Regular vegetation patterns have been predicted to indicate a system slowing down and possibly desertification of drylands. However, these predictions have not yet been observed in dryland vegetation due to the inherent logistic difficulty to gather longer-term in situ data. Here, we evaluate the theoretical prediction that regular vegetation patterns are associated with empirically derived temporal indicators of critical slowing down in a dryland ecosystem in Sudan using different remote sensing products. Overall, three temporal indicators show slowing down as vegetation patterns change from gaps to labyrinths to spots towards more arid conditions. Our findings suggest that spatial self-organization of dryland vegetation is associated with critical slowing down, but this transition towards reduced resilience happens in a non-linear way.</v>
       </c>
       <c r="V109" t="str">
-        <v>Not available in search results</v>
+        <v>maize, landraces, genomic analysis, genetic diversity, West Africa, Sahel, crop improvement, genetic enhancement, population structure, breeding</v>
       </c>
     </row>
     <row r="110" xml:space="preserve">
@@ -10234,13 +10234,13 @@
 Emphasizes integrated approaches across institutions, geographies, and farming systems</v>
       </c>
       <c r="T110" t="str">
-        <v>10.1016/j.wace.2014.04.004</v>
+        <v>https://doi.org/10.1016/j.jssas.2024.06.004</v>
       </c>
       <c r="U110" t="str">
         <v>Agriculture and the economies of Sub-Saharan Africa (SSA) are highly sensitive to climatic variability. Drought, in particular, represents one of the most important natural factors contributing to malnutrition and famine in many parts of the region. This paper attempts to highlight the challenges of drought in SSA and reviews the current drought risk management strategies, especially the promising technological and policy options for managing drought risks to protect livelihoods and reduce vulnerability. The review suggests the possibilities of several ex ante and ex post drought management strategies in SSA although their effectiveness depends on agro-climatic and socio-economic conditions. A proactive approach that combines promising technological, institutional and policy solutions to manage the risks within vulnerable communities is considered to be the way forward.</v>
       </c>
       <c r="V110" t="str">
-        <v>Not available in search results</v>
+        <v>soil quality, cassava, farmer assessment, indigenous knowledge, yield prediction, Nigeria</v>
       </c>
     </row>
     <row r="111" xml:space="preserve">
@@ -10332,13 +10332,13 @@
 Links to projects funded by the Royal Norwegian Embassy, USAID, and AICCRA (CGIAR)</v>
       </c>
       <c r="T111" t="str">
-        <v>10.1371/journal.pstr.0000052</v>
+        <v>https://doi.org/10.3390/su15010190</v>
       </c>
       <c r="U111" t="str">
         <v>This is a meta-analysis and scoping review of 43 studies and 11 reports on Climate-Smart (CS) One-Health innovations. The review identified determinants, challenges, and impacts related to the deployment of CS One-Health innovations, particularly in Ghana and Benin. Community participation, land tenure, political will, and age are critical adoption factors. Practices like composting, IPM, cover cropping, rotational grazing, and traditional ecological knowledge are promoted. Major barriers include cultural practices, lack of diagnostic tools, limited ICT access, and top-down implementation. Multi-disciplinary collaboration is essential for sustainable deployment.</v>
       </c>
       <c r="V111" t="str">
-        <v>Climate-Smart agriculture, One-Health, Ghana, Benin, socio-economic determinants, innovation adoption, meta-analysis</v>
+        <v>gender equality, social inclusion, GESI, climate information services, climate adaptation, vulnerability, accessibility, marginalized groups, climate variability, equity</v>
       </c>
     </row>
     <row r="112" xml:space="preserve">
@@ -10424,13 +10424,13 @@
 Recognizes IITAâ€™s role via CoFCCA in linking rural institutions with regional adaptation knowledge.</v>
       </c>
       <c r="T112" t="str">
-        <v>10.1080/17565529.2017.1291409</v>
+        <v>https://doi.org/10.1016/j.heliyon.2023.e20199</v>
       </c>
       <c r="U112" t="str">
         <v>Climate change will create challenges for forest-dependent communities in Africa. Local institutions play an important role in fostering community resilience in the context of change. The resilience of a community is influenced by social learning that can happen as people meet together and share their diverse experiences and knowledge. Surveys of 232 people from 13 villages, in three regions of Cameroon, provided insight about the role that internal village institutions can play in fostering community resilience. Almost all villagers, both men and women, are members of at least one group and the membership of these groups is very diverse in terms of family relations, gender, occupation, age, and level of education. While the groups were not currently working together to respond to climate change, the diverse social networks that villagers have in these groups have already fostered exchange of knowledge. Community resilience could be better fostered through a deliberate action-reflection process that includes both men and women, and builds on the social capital present in communities.</v>
       </c>
       <c r="V112" t="str">
-        <v>Not explicitly provided in search results</v>
+        <v>habitat distribution, species distribution modeling, Ricinodendron heudelotii, climate change, Benin, West Africa, conservation, biomod2, RCP scenarios, range shift</v>
       </c>
     </row>
     <row r="113" xml:space="preserve">
@@ -10506,13 +10506,13 @@
         <v>Supports Africa RISING and CGIAR resilience-building strategies. Uses robust econometrics to distinguish indirect vs. interaction effects.</v>
       </c>
       <c r="T113" t="str">
-        <v>10.1016/j.ecolecon.2023.107894</v>
+        <v>https://doi.org/10.1111/mec.13762</v>
       </c>
       <c r="U113" t="str">
         <v>This paper examines how resilience capacity mediates or moderates the relationship between weather shocks and household food security based on two waves of farm household survey and satellite-based weather data in northern Ghana and applying econometric models. Results show that resilience capacity moderate or mediates the negative effects of heat stress and drought on food security. However, the mediating role of resilience capacity in the shock-food security nexus is more stable and stronger than its moderating role. A standard deviation (SD) increase in heat stress reduces household food consumption by 0.71 SD, but resilience capacity effectively moderates this effect by approximately 0.61 SD. For drought, household food consumption is reduced by 0.67 SD, but resilience capacity effectively dampens this negative effect by approximately 0.60 SD.</v>
       </c>
       <c r="V113" t="str">
-        <v>Correlated random effects, Food security, Weather shocks, Resilience capacity, Ghana</v>
+        <v>Aedes aegypti, mosquito, population genetics, Africa, climatic change, Pleistocene, admixture, disease vector, evolutionary history, genetic diversity</v>
       </c>
     </row>
     <row r="114" xml:space="preserve">
@@ -10594,13 +10594,13 @@
         <v>Supports national REDD+ strategies; provides policy recommendations for farmer support systems and tenure security to enable CSA adoption.</v>
       </c>
       <c r="T114" t="str">
-        <v>10.3390/land7010030</v>
+        <v>https://doi.org/10.1038/s41467-023-39338-z</v>
       </c>
       <c r="U114" t="str">
         <v>Agriculture in Africa is not only exposed to climate change impacts but is also a source of greenhouse gases (GHGs). While GHG emissions in Africa are relatively minimal in global dimensions, agriculture in the continent constitutes a major source of GHG emissions. In Ghana, agricultural emissions are accelerating, mainly due to ensuing deforestation of which smallholder cocoa farming is largely associated. The sector is also bedevilled by soil degradation, pests, diseases and poor yields coupled with poor agronomic practices. Climate Smart Agriculture (CSA) thus offers a way to reduce the sector's GHG emissions and to adapt the sector to the adverse impacts of climate change. This study assesses the potential of CSA vis-à-vis conventional cocoa systems to enhance production, mitigate and/or remove GHG emissions and build resilience, in addition to understanding key determinants influencing CSA practices.</v>
       </c>
       <c r="V114" t="str">
-        <v>climate smart agriculture, resilience, carbon balance, cocoa, mitigation, Ghana, Ex-ACT, agroforestry</v>
+        <v>soil organic carbon, meta-analysis, Anthropocene, land management, carbon sequestration, soil health, climate change mitigation, global assessment, agricultural practices, ecosystem services</v>
       </c>
     </row>
     <row r="115" xml:space="preserve">
@@ -10682,13 +10682,13 @@
         <v>Recommends better infrastructure (roads, rail), finance and insurance tools, and conflict mitigation strategies to protect trader resilience.</v>
       </c>
       <c r="T115" t="str">
-        <v>10.1108/JADEE-08-2023-0214</v>
+        <v>https://doi.org/10.1111/pbi.12467</v>
       </c>
       <c r="U115" t="str">
         <v>The study examines five exogenous shocks: climate, violence, price hikes, spoilage and the COVID-19 lockdown, and analyzes the association between these shocks and trader characteristics, reflecting trader vulnerability. Using primary survey data on 1,100 Nigerian maize traders for 2021 (controlling for shocks in 2017), the researchers use probit models to estimate the probabilities of experiencing climate, violence, disease and cost shocks associated with trader characteristics (gender, size and region) and to estimate the probability of vulnerability (experiencing severe impacts). Traders are prone to experiencing more than one shock, which increases the intensity of the shocks, with price shocks often accompanied by violence, climate and COVID-19 shocks.</v>
       </c>
       <c r="V115" t="str">
-        <v>Not explicitly provided in search results</v>
+        <v>genomics, climate change, agricultural intensification, crop improvement, breeding, food security, climate resilience, crop yield, genetic diversity, adaptation</v>
       </c>
     </row>
     <row r="116" xml:space="preserve">
@@ -10766,13 +10766,13 @@
         <v>The framework is proposed as a tool for CGIAR and national programs to guide breeding, agronomy, and policy strategies for long-term climate resilience planning.</v>
       </c>
       <c r="T116" t="str">
-        <v>10.1016/j.agsy.2022.103508</v>
+        <v>https://doi.org/10.3920/WMJ2016.2130</v>
       </c>
       <c r="U116" t="str">
         <v>Given the significance of climate change impacts on farming communities, large investments are made by research and development actors to adapt agricultural systems. A data-driven approach is required to guide these investments. In the African Great Lakes Region (GLR), root, tuber and banana (RT&amp;B) crops are vital for smallholder farming systems, but little is known about strategies to mitigate climate change impacts. The objective was to develop a spatial prioritisation and targeting framework based on the risk of climate-related impacts to guide research investments in climate-smart agriculture for RT&amp;B crops in the GLR. The framework is based on crop-specific socio-agroecological homologues (SAHs), defined as clusters of geographies with broadly similar risks of climate-change related impacts, determined by hazard, exposure, and vulnerability. Four SAHs were identified for banana, potato and sweetpotato, and five for cassava. For each crop, SAHs were prioritised for investment based on the level of risk. Scenario analysis showed that drought-tolerant varieties would increase banana suitability from 0.30 to 0.47 under baseline conditions and from 0.54 to 0.71 under future climates.</v>
       </c>
       <c r="V116" t="str">
-        <v>Climate change adaptation, Root tuber and banana crops, African Great Lakes Region, Spatial prioritisation, Socio-agroecological homologues, Risk assessment, Climate-smart agriculture</v>
+        <v>aflatoxin, biological control, biocontrol, atoxigenic, climate change, Africa, crop contamination, food safety, mycotoxin, fungal control</v>
       </c>
     </row>
     <row r="117" xml:space="preserve">
@@ -10856,13 +10856,13 @@
 Contributes to empirical data gaps on cocoa heat tolerance</v>
       </c>
       <c r="T117" t="str">
-        <v>10.1016/j.envexpbot.2022.105052</v>
+        <v>https://doi.org/10.3389/fsufs.2022.959604</v>
       </c>
       <c r="U117" t="str">
         <v>Shade is one of the recommended management solutions to mitigate the effects of heat stress, which is a major challenge for cocoa production globally. Nevertheless, there are limited studies to verify this hypothesis. The study evaluated the effects of heat and shade on cocoa physiology using experimental plots with six-month old potted seedlings in a randomized complete block design. Infrared heaters were applied for one month to increase leaf temperatures by an average of 5-7°C (heat treatment) compared with no heat (unheated treatments), and shaded plants were placed under a shade net removing 60% of the light compared with no shade (sun treatments). Plants under heat treatments in sun and in shade showed severe reduction in photosynthesis. Measurements of chlorophyll fluorescence and photosynthetic light response curves indicated that heat caused damages at photosystem II and additionally resulted in lower rates of maximal photosynthesis. Heat treatments resulted in decreased concentrations of chlorophyll and changed pigment composition, reduced specific leaf areas, and plant biomass. While shade may benefit cocoa seedlings, the results indicate that the positive effects may not be sufficient to counteract the negative effects of increased temperatures on cocoa physiology.</v>
       </c>
       <c r="V117" t="str">
-        <v>shade, cocoa (plant), heat, Stomatal conductance, water potential, photosynthesis, ghana</v>
+        <v>Soil fertility management, sub-Saharan Africa, sustainable agriculture, food production, SDGs</v>
       </c>
     </row>
     <row r="118" xml:space="preserve">
@@ -10944,13 +10944,13 @@
 Data used to guide donor incorporation into breeding pipelines for SSA.</v>
       </c>
       <c r="T118" t="str">
-        <v>10.2135/cropsci2012.09.0545</v>
+        <v>https://doi.org/10.22302/ICCRI.JUR.PELITAPERKEBUNAN.V37I1.395</v>
       </c>
       <c r="U118" t="str">
         <v>Low maize (Zea mays L.) yields and the impacts of climate change on maize production highlight the need to improve yields in eastern and southern Africa. Climate projections suggest higher temperatures within drought-prone areas. Research in model species suggests that tolerance to combined drought and heat stress is genetically distinct from tolerance to either stress alone, but this has not been confirmed in maize. In this study we evaluated 300 maize inbred lines testcrossed to CML539. Experiments were conducted under optimal conditions, reproductive stage drought stress, heat stress, and combined drought and heat stress. Lines with high levels of tolerance to drought and combined drought and heat stress were identified. Significant genotype × trial interaction and very large plot residuals were observed; consequently, the repeatability of individual managed stress trials was low. Tolerance to combined drought and heat stress in maize was genetically distinct from tolerance to individual stresses, and tolerance to either stress alone did not confer tolerance to combined drought and heat stress. This finding has major implications for maize drought breeding. Many current drought donors and key inbreds used in widely-grown African hybrids were susceptible to drought stress at elevated temperatures.</v>
       </c>
       <c r="V118" t="str">
-        <v>Not explicitly provided in search results</v>
+        <v>Carbon storage, cocoa agroforestry, agroecological zones, Ghana, climate change mitigation</v>
       </c>
     </row>
     <row r="119" xml:space="preserve">
@@ -11034,7 +11034,7 @@
 Suggests targeting of strategies based on household type rather than blanket promotion</v>
       </c>
       <c r="T119" t="str">
-        <v>10.1007/s10113-015-0838-6</v>
+        <v>https://doi.org/10.1080/17565529.2017.1291409</v>
       </c>
       <c r="U119" t="str">
         <v>The paper examines adaptation strategies to reduce smallholder farmers' vulnerability to climate variability in West Africa, exploring linkages between agricultural adaptation strategies (crop diversity, soil and water conservation, trees on farm, small ruminants, improved crop varieties, fertilizers), food security, farm household characteristics and farm productivity in three contrasting agro-ecological sites (Burkina Faso, Ghana and Senegal). The study found that differences in land area per capita and land productivity largely explained variation in food security across sites, and distinguished four household types (subsistence, diversified, extensive, intensified) based on land size and market orientation, with contrasting levels of food security and agricultural adaptation strategies.</v>
@@ -11132,13 +11132,13 @@
 Strong emphasis on the need for climate justice and support to smallholders who contribute least to climate change but are most affected.</v>
       </c>
       <c r="T120" t="str">
-        <v>10.1016/j.cosust.2014.07.002</v>
+        <v>https://doi.org/10.1016/j.eja.2024.127137</v>
       </c>
       <c r="U120" t="str">
         <v>The 'sustainable intensification' (SI) approach and 'climate-smart agriculture' (CSA) are highly complementary. SI is an essential means of adapting to climate change, also resulting in lower emissions per unit of output. With its emphasis on improving risk management, information flows and local institutions to support adaptive capacity, CSA provides the foundations for incentivizing and enabling intensification. But adaptation requires going beyond a narrow intensification lens to include diversified farming systems, local adaptation planning, building responsive governance systems, enhancing leadership skills, and building asset diversity. While SI and CSA are crucial for global food and nutritional security, they are only part of a multi-pronged approach, that includes reducing consumption and waste, building social safety nets, facilitating trade, and enhancing diets.</v>
       </c>
       <c r="V120" t="str">
-        <v>Not explicitly provided in search results</v>
+        <v>Climate change, cereal crops, sub-Saharan Africa, rainfed agriculture, adaptation</v>
       </c>
     </row>
     <row r="121" xml:space="preserve">
@@ -11210,13 +11210,13 @@
         <v>Data collected over 5 years; emphasizes need for conserving submontane forests and promoting less destructive agroforestry practices.</v>
       </c>
       <c r="T121" t="str">
-        <v>10.1016/j.ecolind.2019.105741</v>
+        <v>https://doi.org/10.3390/agriculture12111853</v>
       </c>
       <c r="U121" t="str">
         <v>The conservation and sustainable management of biodiversity requires an understanding of the biotic and abiotic factors that condition the presence and survival of organisms in natural habitats. The global distribution and ecological hypersensitivity of pteridophytes have made them ideal candidates for studying the impact of biotic and abiotic factors on levels of biodiversity. This study aims to determine the effect of vegetation cover, human disturbance, and climatic factors on the distribution and diversity of pteridophytes in Togo with a view to guide conservation efforts. Our data comprises 130 plots of 500 m2 representing all ecological zones of the country, complemented by several opportunistic collections. After determining the patterns of pteridophyte distribution, multivariate analysis of variance and the calculation of diversity indicators made it possible to determine the influence of the factors studied. Submontane forests concentrate 90% of the local pteridophyte species in Togo. Humidity, insolation and disturbance are the main drivers of pteridophyte presence. Human disturbances are more damaging to terrestrial pteridophyte species. Pteridophyte species are reliable indicators of conditions of their habitat in Togo.</v>
       </c>
       <c r="V121" t="str">
-        <v>climate change, vulnerability, protected areas, togo, west africa, biodiversity conservation, nature conservation, pteridophyta</v>
+        <v>Climate-smart agriculture, Mali, household welfare, adoption, technology</v>
       </c>
     </row>
     <row r="122" xml:space="preserve">
@@ -11294,13 +11294,13 @@
         <v>CBA can mobilize youth and women, as in India, and influence policy reforms. The article argues for procedural justice and long-term institutional embedding of adaptation knowledge rather than one-off projects.</v>
       </c>
       <c r="T122" t="str">
-        <v>10.1080/17565529.2014.965654</v>
+        <v>https://doi.org/10.1002/ece3.3668</v>
       </c>
       <c r="U122" t="str">
         <v>Climate change creates widespread risks for food production. As climate impacts are often locally specific, it is imperative that large-scale initiatives to support smallholder farmers consider local priorities and integrate lessons from successful autonomous adaptation efforts. This article explores how large-scale programmes for smallholder adaptation to climate change might link effectively with community-led adaptation initiatives. Drawing on experiences in Bangladesh, Mozambique, Uganda and India, this article identifies key success factors and barriers for considering local priorities, capacities and lessons in large-scale adaptation programmes. It highlights the key roles of extension services and farmers' organizations as mechanisms for linking between national-level and community-level adaptation, and a range of other success factors which include participative and locally driven vulnerability assessments, tailoring of adaptation technologies to local contexts, mapping local institutions and working in partnership across institutions. Barriers include weak governance, gaps in the regulatory and policy environment, high opportunity costs, low literacy and underdeveloped markets. The article concludes that mainstreaming climate adaptation into large-scale agricultural initiatives requires not only integration of lessons from community-based adaptation, but also the building of inclusive governance to ensure smallholders can engage with those policies and processes affecting their vulnerability.</v>
       </c>
       <c r="V122" t="str">
-        <v>climate change, community-based adaptation, mainstreaming, agriculture, adaptation</v>
+        <v>Aedes mosquitoes, phylogeography, climate change, Africa, evolution</v>
       </c>
     </row>
     <row r="123" xml:space="preserve">
@@ -11378,13 +11378,13 @@
         <v>Significant gap between CSAâ€™s conceptual framework and its operationalization; stresses the need for institutional innovation to complement technical CSA solutions.</v>
       </c>
       <c r="T123" t="str">
-        <v>10.3390/su10061990</v>
+        <v>https://doi.org/10.1111/agec.12363</v>
       </c>
       <c r="U123" t="str">
         <v>Climate-smart agriculture (CSA) is increasingly seen as a promising approach to feed the growing world population under climate change. The review explored how institutional perspectives are reflected in the CSA literature. In total, 137 publications were analyzed using institutional analysis framework, of which 55.5% make specific reference to institutional dimensions. While the CSA concept encompasses three pillars (productivity, adaptation, and mitigation), the literature has hardly addressed them in an integrated way. Mitigation was predominantly addressed in high-income countries, while productivity and adaptation were priorities for middle and low-income countries.</v>
       </c>
       <c r="V123" t="str">
-        <v>climate-smart agriculture, institutions, adaptation, mitigation, systematic review</v>
+        <v>Smallholder farmers, Climate adaptation, Policy interventions, Ethiopia, Agent-based modeling, Agricultural policy</v>
       </c>
     </row>
     <row r="124" xml:space="preserve">
@@ -11478,13 +11478,13 @@
 Focused on research-for-development and donor alignment in CSA inv</v>
       </c>
       <c r="T124" t="str">
-        <v>10.1016/j.agsy.2018.09.009</v>
+        <v>https://doi.org/10.1088/1748-9326/ac61c8</v>
       </c>
       <c r="U124" t="str">
         <v>Climate-smart agriculture (CSA) is widely promoted as an approach for reorienting agricultural development under the realities of climate change. Prioritising research-for-development activities is crucial, given the need to utilise scarce resources as effectively as possible. However, no framework exists for assessing and comparing different CSA research investments. Several aspects make it challenging to prioritise CSA research, including its multi-dimensional nature (productivity, adaptation and mitigation), the uncertainty surrounding many climate impacts, and the scale and temporal dependencies that may affect the benefits and costs of CSA adoption.</v>
       </c>
       <c r="V124" t="str">
-        <v>Adaptation, Agriculture, Climate change, Mitigation, Research</v>
+        <v>Climate change, West Africa, adaptation strategies, crop yields, systematic review</v>
       </c>
     </row>
     <row r="125" xml:space="preserve">
@@ -11572,13 +11572,13 @@
 Calls for complementary pest control methods alongside biocontrol</v>
       </c>
       <c r="T125" t="str">
-        <v>10.1002/ps.6478</v>
+        <v>https://doi.org/10.1093/plcell/koac303</v>
       </c>
       <c r="U125" t="str">
         <v>The southern armyworm (SAW) Spodoptera eridania (Stoll) (Lepidoptera: Noctuidae) is native to the tropical Americas where the pest can feed on more than 100 plant species. SAW was recently detected in West and Central Africa, feeding on various crops including cassava, cotton, amaranth and tomato. The current work was carried out to predict the potential spatial distribution of SAW and four of its co-evolved parasitoids at a global scale using the maximum entropy (Maxent) algorithm. SAW may not be a huge problem outside its native range (the Americas) for the time being, but may compromise crop yields in specific hotspots in coming years. The analysis of its potential distribution anticipates that the pest might easily migrate east and south from Cameroon and Gabon. The models used generally demonstrate that all the parasitoids considered are good candidates for the biological control of SAW globally, except they will not be able to establish in specific climates. The current paper discusses the potential role of biological control using parasitoids as a crucial component of a durable climate-smart integrated management of SAW to support decision making in Africa and in other regions of bioclimatic suitability.</v>
       </c>
       <c r="V125" t="str">
-        <v>biological control, climate change, decision support, foresight analysis, southern armyworm</v>
+        <v>Systems biology, Sustainable agriculture, Climate resilience, Plant biology, Crop improvement, Photosynthesis</v>
       </c>
     </row>
     <row r="126" xml:space="preserve">
@@ -11666,13 +11666,13 @@
 Intended as an actionable strategy, not a research paper.</v>
       </c>
       <c r="T126" t="str">
-        <v>Note: Published article found is from 2024, not 2022. DOI: 10.3390/su16156652</v>
+        <v>https://doi.org/10.1371/journal.pone.0255326</v>
       </c>
       <c r="U126" t="str">
         <v>The paper discusses how the One Health concept has evolved from its initial focus on zoonotic diseases to a broader framework addressing interconnected terrestrial and aquatic ecosystems. The paper describes Climate-Smart One Health (CS-OH) and Climate-Smart Integrated Pest Management (CS-IPM) approaches.</v>
       </c>
       <c r="V126" t="str">
-        <v>Unable to locate 2022 version; 2024 version published with different DOI</v>
+        <v>Cassava, Landraces, Genotyping, Virus elimination, Tanzania, Farmer knowledge, Genetic diversity</v>
       </c>
     </row>
     <row r="127" xml:space="preserve">
@@ -11760,13 +11760,13 @@
 IITAâ€™s Biorisk Management Facility (BIMAF) acknowledged as key institutional supportâ€‹</v>
       </c>
       <c r="T127" t="str">
-        <v>10.3390/insects12040273</v>
+        <v>https://doi.org/10.1016/j.scitotenv.2017.08.041</v>
       </c>
       <c r="U127" t="str">
         <v>The fall armyworm (FAW), Spodoptera frugiperda has now become a pest of global importance. Its introduction and detection in Africa in 2016, and subsequent introduction and spread into Asia and Australia, has put several millions of food producers and maize farmers at risk. The present study was initiated to predict the habitats of high establishment potential of key parasitoids of FAW in South America, which might prove to be effective as classical biological control agents of FAW in regions where it is an invasive species under current and future climate scenarios. The prospective parasitoids are the following: Chelonus insularis, Cotesia marginiventris, Eiphosoma laphygmae, Telenomus remus and Trichogramma pretiosum. An adjusted procedure of a machine-learning algorithm, the maximum entropy (Maxent), was applied for the modeling experiments. Model predictions showed particularly high establishment potential of the five hymenopteran parasitoids in areas that are heavily affected by FAW (like the coastal belt of West Africa from Côte d'Ivoire to Nigeria, the Congo basin to Eastern Africa, Eastern, Southern and Southeastern Asia and some portions of Eastern Australia) and those of potential invasion risks (western &amp; southern Europe).</v>
       </c>
       <c r="V127" t="str">
-        <v>Spodoptera Frugiperda, Climate Change, Pest Management, Biological Control, Machine Learning, Decision Support, Parasitoids</v>
+        <v>Climate warming, Crop yields, School attendance, Central Africa, Cameroon, Plantain, Climate impacts</v>
       </c>
     </row>
     <row r="128" xml:space="preserve">
@@ -11858,13 +11858,13 @@
 Clear linkages to IITA-led innovations like the Farmer Interface Application (FIA)</v>
       </c>
       <c r="T128" t="str">
-        <v>10.1016/j.cois.2022.100961</v>
+        <v>https://doi.org/10.1016/j.fcr.2016.06.010</v>
       </c>
       <c r="U128" t="str">
         <v>IPM 3.0 relies on 3 pillars: farmer empowerment, nature-based solutions, integrative practices. It encompasses interactions occurring at cropping system/landscape and across trophic levels. Each year, Africa loses half of its harvest to pests (insects, pathogens, nematodes, weeds). Pest management in major cropping systems has long been dominated by chemical pesticides in Africa. Smallholder farmers have perceived pesticides as insurance to protect their crops. Hence, overuse of pesticides has been constantly increasing. Although African countries have a number of pesticide-related policies, they are inadequately implemented. However, significant investment has been made on integrated pest management (IPM) innovations in recent decades.</v>
       </c>
       <c r="V128" t="str">
-        <v>Not explicitly provided in search results</v>
+        <v>Wheat production, CIMMYT, Mega-environments, DSSAT, Crop modeling, Global agriculture, Climate change</v>
       </c>
     </row>
     <row r="129" xml:space="preserve">
@@ -11946,13 +11946,13 @@
 Recommends continued support for digitization of African herbaria and database integration</v>
       </c>
       <c r="T129" t="str">
-        <v>10.1186/s12915-017-0356-8</v>
+        <v>https://doi.org/10.1007/s10745-017-9899-0</v>
       </c>
       <c r="U129" t="str">
         <v>Understanding the patterns of biodiversity distribution and what influences them is a fundamental pre-requisite for effective conservation and sustainable utilisation of biodiversity. Such knowledge is increasingly urgent as biodiversity responds to the ongoing effects of global climate change. Nowhere is this more acute than in species-rich tropical Africa, where so little is known about plant diversity and its distribution. In this paper, we use RAINBIO – one of the largest mega-databases of tropical African vascular plant species distributions ever compiled – to address questions about plant and growth form diversity across tropical Africa. The filtered RAINBIO dataset contains 609,776 georeferenced records representing 22,577 species. Growth form data are recorded for 97% of all species.</v>
       </c>
       <c r="V129" t="str">
-        <v>Botanical exploration, Digitization, Floristic patterns, Herbarium specimens, Plant growth form, Species richness, Tropical forests</v>
+        <v>Shade trees, Cocoa agroforestry, Farmer knowledge, Ghana, Climate vulnerability, Traditional knowledge, Tree species selection</v>
       </c>
     </row>
     <row r="130" xml:space="preserve">
@@ -12042,13 +12042,13 @@
 IITA affiliation brings institutional weight to practical policy recommendations</v>
       </c>
       <c r="T130" t="str">
-        <v>10.3389/fagro.2022.957011</v>
+        <v>https://doi.org/10.5897/JSSEM15.0502</v>
       </c>
       <c r="U130" t="str">
         <v>The paper discusses how recent discourse on food sovereignty emphasizes democracy in determining localized food systems and culturally appropriate food while leaning on sustainable agricultural practices such as organic agriculture, ecological intensification, agroecology, nature-based solutions, and regenerative agriculture. Sustainable agricultural practices focus on managing land without synthetic fertilizers and pesticides while improving soil and land health. However, the authors question the practicalities of food activism and relying entirely on nature while yields remain very low in much of sub-Saharan Africa.</v>
       </c>
       <c r="V130" t="str">
-        <v>agroecology, regenerative agriculture, rainfed conditions, small farms, food systems, diets, activism, choices</v>
+        <v>Conservation agriculture, Climate change adaptation, Rwanda, Smallholder farming, Mulching, Agricultural sustainability</v>
       </c>
     </row>
     <row r="131" xml:space="preserve">
@@ -12136,13 +12136,13 @@
 Potentially replicable across other smallholder-dominated regions in SSA</v>
       </c>
       <c r="T131" t="str">
-        <v>10.1007/s10098-022-02272-7</v>
+        <v>https://doi.org/10.1080/17565529.2023.2178840</v>
       </c>
       <c r="U131" t="str">
         <v>Models that enable the estimation of crop yields and greenhouse gas (GHG) emissions concurrently are still lacking. This study develops a biophysical modelling framework encompassing a farm typology, a crop model, and a farm-focused GHG calculator to assess productivity (crop yield) and GHG emissions of crop management practices concurrently. Using this modelling framework, the study developed cropping system scenarios based on the concept of conservation agriculture (CA) to identify and design cropping systems that deliver ecological intensification for different farm types. All farm types were found to be net sources of GHG with cropping system inefficiency across all farm types. However, the integration of CA-based practices independently and in combination into farm-type maize-based cropping systems showed significant potential in improving crop yields and lowering GHG emissions across all farm types.</v>
       </c>
       <c r="V131" t="str">
-        <v>Not explicitly provided in search results</v>
+        <v>Drought-tolerant maize, Impact heterogeneity, Nigeria, Adoption, Climate adaptation, Yield impacts, Income effects</v>
       </c>
     </row>
     <row r="132" xml:space="preserve">
@@ -12228,13 +12228,13 @@
 Proposes molecular markers for future screening of drought tolerance linked to PGR use</v>
       </c>
       <c r="T132" t="str">
-        <v>10.1111/ppl.14605</v>
+        <v>https://doi.org/10.1094/PDIS-07-22-1672-RE</v>
       </c>
       <c r="U132" t="str">
         <v>As global climate change intensifies, the occurrence and severity of various abiotic stresses increases. Plants synthesize or accumulate various plant growth regulators (PGRs), including phytohormones, neurotransmitters, gasotransmitters, and polyamines, which present promising sustainable green chemical strategies to adapt or tolerate stress conditions. This comprehensive review examines how PGRs function as green chemical tools for enhancing drought stress tolerance in crops. The paper discusses the molecular mechanisms, signaling pathways, and practical applications of PGRs in improving plant resilience to water deficit. The findings provide insights for developing sustainable agricultural strategies that utilize natural plant compounds to combat drought stress in the context of climate change.</v>
       </c>
       <c r="V132" t="str">
-        <v>plant growth regulators, drought stress tolerance, climate change, phytohormones, green chemistry, abiotic stress, crop resilience, sustainable agriculture, water stress, plant adaptation</v>
+        <v>Banana Xanthomonas wilt, BXW, Disease modeling, Climate risk, Rwanda, Maxent, Plant disease</v>
       </c>
     </row>
     <row r="133" xml:space="preserve">
@@ -12322,13 +12322,13 @@
 Strong argument for re-centering neglected legumes in food systems</v>
       </c>
       <c r="T133" t="str">
-        <v>10.3389/fpls.2022.782140</v>
+        <v>https://doi.org/10.5539/sar.v8n2p68</v>
       </c>
       <c r="U133" t="str">
         <v>This paper discusses dietary diversification and incorporation of resilient crop species such as under-exploited leguminous species referred to as orphan, minor, or underutilized into food systems to ensure food and protein security in many parts of Africa. The study examines the potential of neglected and underutilized legumes to contribute to improved nutrition, income generation, and climate resilience in Sub-Saharan Africa. The research reviews the nutritional profiles, agronomic characteristics, and socioeconomic benefits of various orphan legumes, highlighting opportunities for their integration into modern agricultural systems. The findings emphasize the need for increased research investment, policy support, and value chain development to unlock the potential of these crops for sustainable food security.</v>
       </c>
       <c r="V133" t="str">
-        <v>orphan legumes, underutilized crops, food security, nutrition security, Sub-Saharan Africa, dietary diversification, protein security, climate resilience, legumes, agricultural biodiversity</v>
+        <v>Cereal production, Climate change, Sahel, Mali, Agricultural adaptation, Temperature trends, Rainfall variability</v>
       </c>
     </row>
     <row r="134" xml:space="preserve">
@@ -12416,13 +12416,13 @@
 Suggests insect farming as part of African climate resilience and nutrition strategies</v>
       </c>
       <c r="T134" t="str">
-        <v>10.1371/journal.pone.0222941</v>
+        <v>https://doi.org/10.1007/s10457-023-00950-z</v>
       </c>
       <c r="U134" t="str">
         <v>This paper focuses on integrating temperature-dependent life table data with the Insect Life Cycle Model (ILCYM) to predict the potential distribution of the edible cricket species Scapsipedus icipe in Africa. The study collected temperature-dependent life table data under controlled laboratory conditions and incorporated these data into ILCYM to forecast suitable habitats for mass rearing of this edible insect. The research demonstrates how insect phenology models can inform the development of climate-smart insect farming systems. The findings have implications for promoting edible insects as sustainable protein sources and for understanding how climate affects insect distribution and production potential across African landscapes.</v>
       </c>
       <c r="V134" t="str">
-        <v>insect life cycle modeling, temperature-dependent, edible insects, cricket, ILCYM, species distribution, climate suitability, entomology, sustainable protein, Africa</v>
+        <v>Cocoa agroforestry, Farmer perceptions, Soil carbon management, Ghana, Côte d'Ivoire, West Africa, Climate-smart agriculture</v>
       </c>
     </row>
     <row r="135" xml:space="preserve">
@@ -12514,13 +12514,13 @@
 Data deposited at IITA repository and supported by the STMA project and WASCAL</v>
       </c>
       <c r="T135" t="str">
-        <v>10.3390/genes11091054</v>
+        <v>https://doi.org/10.1016/j.scitotenv.2023.165657</v>
       </c>
       <c r="U135" t="str">
         <v>The study assessed the genetic diversity and population structure of a maize panel of 208 accessions, comprising landrace gene pools from Burkina Faso (58), Ghana (43), and Togo (89), together with reference populations (18) from the maize improvement program of the International Institute of Tropical Agriculture (IITA). The genomic analysis reveals the variability within West African maize landraces and their potential for genetic enhancement. The research identifies distinct genetic clusters and patterns of diversity that can inform breeding strategies for developing climate-resilient maize varieties adapted to diverse agroecological zones in West Africa. The findings provide valuable insights for conserving maize genetic resources and utilizing landrace diversity in modern breeding programs.</v>
       </c>
       <c r="V135" t="str">
-        <v>maize, landraces, genomic analysis, genetic diversity, West Africa, Sahel, crop improvement, genetic enhancement, population structure, breeding</v>
+        <v>Cocoa, Drought stress, Shade effects, Climate change, Ghana, Agroforestry, Water relations</v>
       </c>
     </row>
     <row r="136" xml:space="preserve">
@@ -12608,13 +12608,13 @@
 Study underscores missed opportunities when farmer knowledge is excluded from intervention design</v>
       </c>
       <c r="T136" t="str">
-        <v>10.1016/j.jssas.2024.06.003</v>
+        <v>https://doi.org/10.3389/fpls.2021.798993</v>
       </c>
       <c r="U136" t="str">
         <v>The study evaluated farmers' knowledge of soil quality and yield assessment among cassava farmers in southwestern Nigeria, collecting data on farmers' demography, farming experience, criteria for selecting sites for cassava cultivation, methods of yield prediction, and agronomic knowledge related to climate change and soil fertility decline. Farmers use a combination of soil and vegetation-based criteria to assess soil quality, with soil drainage, colour, and depth ranking as the most used soil-based criteria. The research highlights the value of local knowledge in agricultural decision-making and explores how farmers' indigenous assessment methods align with scientific soil quality indicators. The findings have implications for developing participatory approaches to soil management in cassava production systems.</v>
       </c>
       <c r="V136" t="str">
-        <v>cassava, soil quality, farmer knowledge, indigenous knowledge, root yield, Nigeria, cropping systems, soil assessment, agricultural practices, local expertise</v>
+        <v>Bambara groundnut, Breeding, Food security, Nutrition security, Climate change, Sahel, Underutilized crops</v>
       </c>
     </row>
     <row r="137" xml:space="preserve">
@@ -12698,13 +12698,13 @@
 Highlights digital inequality and the intersectionality of gender with age, class, literacy, and disability</v>
       </c>
       <c r="T137" t="str">
-        <v>10.3390/su15010190</v>
+        <v>https://doi.org/10.1016/j.pbi.2020.05.002</v>
       </c>
       <c r="U137" t="str">
         <v>This paper advances a gender equality and social inclusion (GESI) framework for incorporating climate information services (CIS), which is now becoming central due to the ongoing climate change and climate variability. The framework addresses the need to ensure that climate information services are accessible, relevant, and beneficial to all segments of society, particularly marginalized groups including women, youth, and other vulnerable populations. The study examines barriers to equitable access to climate information and proposes strategies for integrating GESI principles into the design, delivery, and evaluation of CIS. The research provides practical guidance for climate service providers, policymakers, and development practitioners seeking to enhance the inclusiveness and effectiveness of climate adaptation initiatives.</v>
       </c>
       <c r="V137" t="str">
-        <v>gender equality, social inclusion, GESI, climate information services, climate adaptation, vulnerability, accessibility, marginalized groups, climate variability, equity</v>
+        <v>Legumes, West Africa, Climate change, Underutilized crops, Bambara groundnut, African yam bean, Genomics</v>
       </c>
     </row>
     <row r="138" xml:space="preserve">
@@ -12792,13 +12792,13 @@
 Avelino and van Asten are long-standing contributors to coffee agroecology and systems disease management</v>
       </c>
       <c r="T138" t="str">
-        <v>10.1080/17429145.2019.1643934</v>
+        <v>https://doi.org/10.1088/1748-9326/aac092</v>
       </c>
       <c r="U138" t="str">
         <v>Shade effects on coffee diseases are ambiguous because they vary depending on the season and environment. Using Coffee Leaf Rust (CLR) as an example, we demonstrate relationships between the environment and shading systems and their effects on disease intensity. The study explores direct, indirect and interactive effects of the altitude and coffee shading system on microclimatic indicators and CLR. The research provides insights into how altitude and microclimate interact with different shading systems to influence coffee disease dynamics, offering guidance for developing climate-adapted coffee agroforestry systems that balance disease management with other production objectives.</v>
       </c>
       <c r="V138" t="str">
-        <v>coffee, coffee leaf rust, altitude, microclimate, shading systems, agroforestry, disease management, climate adaptation, environmental interactions, tropical crops</v>
+        <v>Technology extrapolation domains, Agronomic science, Spatial framework, Crop yields, Rainfed agriculture, Scaling</v>
       </c>
     </row>
     <row r="139" xml:space="preserve">
@@ -12894,13 +12894,13 @@
 IITA and AVRDC data sources contributed to the climate analysis</v>
       </c>
       <c r="T139" t="str">
-        <v/>
+        <v>https://doi.org/10.1038/s41598-021-88277-6</v>
       </c>
       <c r="U139" t="str">
         <v/>
       </c>
       <c r="V139" t="str">
-        <v/>
+        <v>Drought-tolerant maize, Climate change adaptation, Nigeria, DSSAT, Savannas, Crop modeling, RCP scenarios</v>
       </c>
     </row>
     <row r="140" xml:space="preserve">
@@ -12986,13 +12986,13 @@
 Important case study for climate-resilient agroforestry planning in West Africa</v>
       </c>
       <c r="T140" t="str">
-        <v>10.1016/j.heliyon.2023.e20199</v>
+        <v>https://doi.org/10.1007/s10113-024-02313-5</v>
       </c>
       <c r="U140" t="str">
         <v>This study aimed to map the suitable areas for domestication and conservation of Ricinodendron heudelotii under current and future climate conditions in Benin. Ricinodendron heudelotii (Baill.) Heckel is an important nutraceutical reservoir. Occurrence data were recorded and combined with the environmental layers of two climatic scenarios (optimistic RCP 4.5 and pessimistic RCP 8.5) following the biodiversity modelling approach (biomod2). Currently, about four percent (5082 Km²) of the country's area mainly located in the sub-humid and the humid zones were potentially suitable for R. heudelotii. Under future climatic conditions the potentially suitable areas were mainly in the sub-humid zone, but almost all the highly suitable areas located in the humid zone will become medium suitable areas by 2055-time horizon.</v>
       </c>
       <c r="V140" t="str">
-        <v>habitat distribution, species distribution modeling, Ricinodendron heudelotii, climate change, Benin, West Africa, conservation, biomod2, RCP scenarios, range shift</v>
+        <v>Millet, Climate change, DSSAT, Niger, Sahel, Adaptation strategies, Crop modeling</v>
       </c>
     </row>
     <row r="141" xml:space="preserve">
@@ -13078,13 +13078,13 @@
 Supported by CGIAR-PIM and Gates Foundation</v>
       </c>
       <c r="T141" t="str">
-        <v>10.1002/fes3.172</v>
+        <v>https://doi.org/10.1111/1477-9552.12617</v>
       </c>
       <c r="U141" t="str">
         <v>This study undertakes an ex-ante evaluation of the effects of alternative technology and policy options on soybean supply and demand in sub-Saharan Africa (SSA) to 2050. The research shows that a combination of promising innovations affecting the soybean value chain across SSA would be needed to close the soybean demand gap in SSA by 2050 under a drier future climate. The analysis examines various scenarios including improved varieties, enhanced agronomic practices, and policy interventions to assess their potential impacts on soybean production, consumption, and trade. The findings provide guidance for prioritizing investments in soybean research and development to enhance food and nutrition security in the region.</v>
       </c>
       <c r="V141" t="str">
-        <v>soybean, ex-ante evaluation, sub-Saharan Africa, agricultural innovation, food security, climate change, crop modeling, value chain, technology adoption, policy analysis</v>
+        <v>Black gram, Green gram, Pulses, Climate-smart practices, Adoption, India, Crop management, Agricultural extension</v>
       </c>
     </row>
     <row r="142" xml:space="preserve">
@@ -13148,13 +13148,13 @@
         <v>Strong physiological focus with clear implications for adaptation but not broader food system themes.</v>
       </c>
       <c r="T142" t="str">
-        <v>10.1017/S0021859621000617</v>
+        <v>https://doi.org/10.1080/01904167.2020.1711939</v>
       </c>
       <c r="U142" t="str">
         <v>Field studies were conducted in 2017 and 2018 seasons in two agroecologies (Angonia and Ruace) in Mozambique to evaluate the effects of Bradyrhizobium diazoefficiens strain USDA110 (formerly known as Bradyrhizobium japonicum) inoculant, nitrogen and phosphorus on nodulation, physiology and yield of non-promiscuous (Safari) and promiscuous (TGx 1740-2F) soybean varieties. Data on transpiration, photosynthesis, leaf area index, radiation interception and WUE from the beginning of flowering to maturity were collected. Photosynthesis rate and water-use efficiency (WUE) were distinct with variety, growth stages and inputs within agroecologies. At one site in 2017, inoculated soybean photosynthesized more at 22.8 μmol/m2/s leading to better WUE of 3.6 that corresponded to 2894 kg/ha yield. Overall, soybean WUE was higher when inoculated than N-treated, while P application yielded better. Nitrogen is a key element in photosynthesis process as it affects leaf chloroplasts size, number and composition, and inoculation promotes BNF process that avails more N for plant uptake resulting in better leaf development.</v>
       </c>
       <c r="V142" t="str">
-        <v>Soybean, Bradyrhizobium diazoefficiens, Inoculant, Nitrogen, Phosphorus, Photosynthesis, Water-use efficiency, Biological nitrogen fixation, Mozambique</v>
+        <v>Sorghum, APSIM model, Nitrogen fertilization, Nigeria, Crop modeling, Semi-arid agriculture, Climate adaptation</v>
       </c>
     </row>
     <row r="143" xml:space="preserve">
@@ -13242,13 +13242,13 @@
 Authors stress that mitigation success requires legally binding tenure systems, simplified rules, and full local participation.</v>
       </c>
       <c r="T143" t="str">
-        <v>10.1080/00207233.2017.1347358</v>
+        <v>https://doi.org/10.1080/14693062.2020.1745742</v>
       </c>
       <c r="U143" t="str">
         <v>This paper focuses on developing a participatory model for forest governance and REDD+ implementation in Central Africa to enhance stakeholder involvement in carbon markets. The study examines current forest governance structures in the region and proposes mechanisms to increase participation of local communities, indigenous peoples, and other stakeholders in REDD+ programs. The research identifies barriers to effective stakeholder engagement in carbon markets and presents strategies for creating more inclusive and equitable forest governance systems that can deliver both climate mitigation and sustainable development outcomes in Central African countries.</v>
       </c>
       <c r="V143" t="str">
-        <v>forest governance, REDD+, Central Africa, participatory model, carbon markets, stakeholder involvement, climate mitigation, community engagement, sustainable development, forest conservation</v>
+        <v>Weather index insurance, Climate risk management, Willingness to pay, Togo, West Africa, Agricultural insurance, Climate adaptation</v>
       </c>
     </row>
     <row r="144" xml:space="preserve">
@@ -13326,13 +13326,13 @@
 It emphasizes the interplay between environmental change and biological invasion.</v>
       </c>
       <c r="T144" t="str">
-        <v>10.1111/mec.13762</v>
+        <v>https://doi.org/10.1016/j.tfp.2021.100100</v>
       </c>
       <c r="U144" t="str">
         <v>The application of approximate Bayesian computation (ABC) to sequence data from four nuclear and one mitochondrial marker revealed that African populations of Ae. aegypti best fit a demographic model of lineage diversification, historical admixture and recent population structuring. This population history is consistent with the effects of forest fragmentation and expansion driven by Pleistocene climatic change. By increasing genetic diversity and forming novel allelic combinations, divergence and historical admixture within Africa could have provided the adaptive potential needed for the successful worldwide spread of Ae. aegypti. The study demonstrates how historical environmental change in Africa shaped the evolutionary trajectory of this important disease vector.</v>
       </c>
       <c r="V144" t="str">
-        <v>Aedes aegypti, mosquito, population genetics, Africa, climatic change, Pleistocene, admixture, disease vector, evolutionary history, genetic diversity</v>
+        <v>Cocoa, Agroforestry, Crown architecture, Shade management, Ghana, Tree species, Climate adaptation</v>
       </c>
     </row>
     <row r="145" xml:space="preserve">
@@ -13418,13 +13418,13 @@
 Supports policies promoting nature-based solutions, especially in agriculture and land management.</v>
       </c>
       <c r="T145" t="str">
-        <v>10.1038/s41467-023-39338-z</v>
+        <v>https://doi.org/10.1016/j.jtherbio.2021.102877</v>
       </c>
       <c r="U145" t="str">
         <v>Using second-order meta-analysis, we synthesized findings from 230 first-order meta-analyses comprising over 25,000 primary studies to assess global patterns and drivers of soil organic carbon (SOC) change in the Anthropocene. This comprehensive analysis examines how human activities and land management practices have affected SOC stocks worldwide. The study provides a global panorama of the impacts of human activities on soil carbon, identifying key drivers of SOC change and their implications for climate change mitigation and sustainable soil management. The findings offer critical insights for developing evidence-based policies to enhance soil carbon sequestration and soil health under changing environmental conditions.</v>
       </c>
       <c r="V145" t="str">
-        <v>soil organic carbon, meta-analysis, Anthropocene, land management, carbon sequestration, soil health, climate change mitigation, global assessment, agricultural practices, ecosystem services</v>
+        <v>Bactrocera dorsalis, Oriental fruit fly, Phenology model, Temperature, Pest management, Climate change, Thermal biology</v>
       </c>
     </row>
     <row r="146" xml:space="preserve">
@@ -13502,13 +13502,13 @@
         <v>Highlights role of climate-smart agroforestry and pruning practices. Recommends careful selection of shade tree species to balance benefits and risks.</v>
       </c>
       <c r="T146" t="str">
-        <v>10.1016/j.agrformet.2022.109199</v>
+        <v>https://doi.org/10.1371/journal.pone.0301254</v>
       </c>
       <c r="U146" t="str">
         <v>Shade effects on cocoa diseases are ambiguous because they vary depending on the season and environment. This study explores direct, indirect and interactive effects of altitude and coffee shading system on microclimatic indicators and coffee leaf rust (CLR). Key findings include that rainfall and proximity to shade trees influence cocoa health and productivity, and black pod disease in cocoa doubles under rainfall from 1400 to 1850 mm. The research demonstrates relationships between the environment and shading systems and their effects on disease intensity in cocoa agroforestry systems in Ghana, providing insights for climate-adapted cocoa production strategies.</v>
       </c>
       <c r="V146" t="str">
-        <v>cocoa, climate variability, agroforestry, Ghana, crop health, productivity, black pod disease, shade management, rainfall, microclimates</v>
+        <v>Oil seeds, Climate change, Crop modeling, DSSAT, South Africa, Smallholder farming, Greenhouse gas emissions</v>
       </c>
     </row>
     <row r="147" xml:space="preserve">
@@ -13584,13 +13584,13 @@
         <v>The study is part of the CGIAR CCAFS program. It recommends clearer national frameworks for gender mainstreaming and budget tracking. Includes a 5-point grading rubric for gender integration in policy documents and a proposal for harmonized gender strategies across levels of governance.</v>
       </c>
       <c r="T147" t="str">
-        <v>10.1007/s10584-019-02447-0</v>
+        <v>https://doi.org/10.5194/soil-2-79-2016</v>
       </c>
       <c r="U147" t="str">
         <v>The study analyzes the extent of gender integration in agricultural and natural resource policies in Uganda and Tanzania, examining how gender is budgeted for in implementation plans at district and lower governance levels. A total of 155 policy documents, development plans, and annual action plans from national, district, and sub-county/ward levels were reviewed. Results show that while there is increasing gender responsiveness in both countries, gender issues are still interpreted as 'women issues,' there is disharmony in gender mainstreaming across governance levels, budgeting for gender is not yet fully embraced by governments, and gender activities do not address structural inequalities. The paper provides recommendations for strengthening gender integration in climate and agricultural policies.</v>
       </c>
       <c r="V147" t="str">
-        <v>gender mainstreaming, climate change policy, agriculture policy, natural resources, East Africa, Uganda, Tanzania, policy analysis, gender budgeting, governance</v>
+        <v>Soil degradation, Soil erosion, Soil organic carbon, Food security, Climate change, Soil resources</v>
       </c>
     </row>
     <row r="148" xml:space="preserve">
@@ -13668,13 +13668,13 @@
         <v>Study recommends gender mainstreaming in climate adaptation policies. Supported by AGRA, IDRC, CORAF/WECARD, and IITA.</v>
       </c>
       <c r="T148" t="str">
-        <v>10.1080/23311932.2020.1743625</v>
+        <v>https://doi.org/10.1371/journal.pone.0300427</v>
       </c>
       <c r="U148" t="str">
         <v>This study assesses the impact of climate change (CC) adaptation on farm-level revenue among 500 soybean farmers randomly selected in three districts in Togo using endogenous switching regression method. The survey results indicate that only 40.37% of the women have adapted to CC against 59.62% of the men. Moreover, being member of farmer-based organization (FBO), access to credit and extension services, agricultural training of women are the main factors that increase the likelihood of adaptation. The gender-differentiated impact shows that women would earn more than men from adaptation, while losing compared to men if they do not take any adaptation actions. The loss from non-adapting to CC will increase by 0.268% of the soybean revenue.</v>
       </c>
       <c r="V148" t="str">
-        <v>gender, climate change adaptation, soybean, farmers revenue, Togo, West Africa, agricultural economics, endogenous switching regression, women empowerment, extension services</v>
+        <v>Maize, Sowing dates, Climate change, Nigeria, Crop modeling, DSSAT, Agro-ecological zones</v>
       </c>
     </row>
     <row r="149" xml:space="preserve">
@@ -13752,13 +13752,13 @@
         <v>Recommends integrating gender into climate finance and adaptive capacity-building. Gender-informed policies should support womenâ€™s knowledge, access, and innovation.</v>
       </c>
       <c r="T149" t="str">
-        <v>10.1016/j.crsust.2023.100219</v>
+        <v>https://doi.org/10.1109/ACCESS.2020.2999255</v>
       </c>
       <c r="U149" t="str">
         <v>This study examines the gender-responsive approaches to rapid climate warming among crop smallholder farmers in Nasarawa, Nigeria. Temperature data for 36 years was used to establish change and analyze gender-differentiated impacts of climate warming on smallholder farming communities. The research reveals how men and women farmers experience and respond differently to increasing temperatures and explores gender-specific adaptation strategies. The findings demonstrate the importance of incorporating gender considerations into climate adaptation planning and highlight how gender-responsive interventions can enhance the effectiveness of climate warming adaptation among smallholder farmers in Sub-Saharan Africa.</v>
       </c>
       <c r="V149" t="str">
-        <v>gender, climate warming, smallholder farmers, adaptation, Nigeria, temperature change, gender-responsive, climate change, agricultural resilience, vulnerability</v>
+        <v>Rainfall trends, Temperature trends, West Africa, Climate variability, Mann-Kendall test, Spatial-temporal analysis</v>
       </c>
     </row>
     <row r="150" xml:space="preserve">
@@ -13840,13 +13840,13 @@
         <v>Coordinated by the International Society for Plant Pathology and supported by IITA and global institutions; structured around the Millennium Ecosystem Assessment framework; emphasizes need for multidisciplinary research and policy engagement.</v>
       </c>
       <c r="T150" t="str">
-        <v>10.1094/PDIS-01-23-0166-FE</v>
+        <v>https://doi.org/10.18805/LRF-722</v>
       </c>
       <c r="U150" t="str">
         <v>Among the 33 (Ecoregion × Plant System) considered, 18 are assessed as in fair or poor health, and 20 as in declining health. Much of the observed state of plant health and its trends are driven by a combination of forces, including climate change, species invasions, and human management. This comprehensive global assessment examines the current status of plant health across major agricultural systems and ecoregions worldwide. The study synthesizes evidence from multiple sources to evaluate trends in crop diseases, pest pressures, and overall plant system resilience. The findings highlight the urgent need for integrated approaches to plant health management in the context of global environmental change.</v>
       </c>
       <c r="V150" t="str">
-        <v>plant health, global assessment, crop diseases, climate change, pest management, species invasions, agricultural systems, ecoregions, plant pathology, food security</v>
+        <v>Soybean, Genotype-environment interaction, Yield stability, Semi-arid zone, Sudan, Climate change adaptation</v>
       </c>
     </row>
     <row r="151" xml:space="preserve">
@@ -13924,13 +13924,13 @@
         <v>Includes quantitative BNF data and lists constraints and potential of each legume crop.</v>
       </c>
       <c r="T151" t="str">
-        <v>10.3389/fsufs.2022.708124</v>
+        <v>https://doi.org/10.3390/su15107837</v>
       </c>
       <c r="U151" t="str">
         <v>Orphan legumes have the potential to improve food and nutrition security in Sub-Saharan Africa (SSA) due to their cultural linkage with the regional food habits of the communities, nutritionally rich food, untapped genetic diversity, and adaptation to harsh climate conditions and poor marginal soils. This review examines the potential of indigenous African legume species that have been neglected by mainstream agricultural research and development. The paper discusses how these underutilized legumes can contribute to dietary diversification, climate resilience, and sustainable agricultural systems across SSA. It highlights opportunities for incorporating these crops into modern breeding programs and agricultural policies to enhance regional food and nutrition security.</v>
       </c>
       <c r="V151" t="str">
-        <v>orphan legumes, food security, nutrition security, Sub-Saharan Africa, underutilized crops, genetic diversity, climate adaptation, indigenous crops, dietary diversification, sustainable agriculture</v>
+        <v>breeding, cassava, climate change, conflict, trait preferences, response strategies, gender disparity</v>
       </c>
     </row>
     <row r="152" xml:space="preserve">
@@ -14017,13 +14017,13 @@
 Limited progress in applying genomics to orphan crops and marginalized regions.</v>
       </c>
       <c r="T152" t="str">
-        <v>10.1111/pbi.12467</v>
+        <v>https://doi.org/10.1016/j.gfs.2018.12.005</v>
       </c>
       <c r="U152" t="str">
         <v>Agriculture is now facing the 'perfect storm' of climate change, increasing costs of fertilizer and rising food demands from a larger and wealthier human population. Genomics offers unprecedented opportunities to increase crop yield, quality and stability of production through advanced breeding strategies. This paper argues that genomic approaches can enhance the resilience of major crops to climate variability and increase the productivity and range of minor crops to diversify the food supply. The authors discuss how modern genomic tools, including marker-assisted selection, genomic selection, and gene editing, can accelerate the development of climate-resilient crop varieties to ensure global food security in the face of environmental change.</v>
       </c>
       <c r="V152" t="str">
-        <v>genomics, climate change, agricultural intensification, crop improvement, breeding, food security, climate resilience, crop yield, genetic diversity, adaptation</v>
+        <v>Roots, Tubers, Bananas, Food security, Climate change, Production frontiers, Agricultural investment</v>
       </c>
     </row>
     <row r="153" xml:space="preserve">
@@ -14115,13 +14115,13 @@
 The IITA Aflasafe plant in Ibadan, Nigeria, is a key manufacturing and dissemination hub.</v>
       </c>
       <c r="T153" t="str">
-        <v>10.3920/WMJ2016.2130</v>
+        <v>https://doi.org/10.1371/journal.pstr.0000052</v>
       </c>
       <c r="U153" t="str">
         <v>Carefully selected atoxigenic genotypes in biological control (biocontrol) formulations efficiently reduce aflatoxin contamination of crops when applied prior to flowering in the field. This review discusses the current status of biocontrol for aflatoxin mitigation in Africa and examines potential challenges posed by climate change. The paper analyzes how environmental factors, particularly those influenced by climate variability, affect the efficacy of atoxigenic biocontrol agents. It provides insights into adapting biocontrol strategies to maintain effectiveness under changing climatic conditions across diverse African agroecologies.</v>
       </c>
       <c r="V153" t="str">
-        <v>aflatoxin, biological control, biocontrol, atoxigenic, climate change, Africa, crop contamination, food safety, mycotoxin, fungal control</v>
+        <v>Climate-Smart agriculture, One-Health, Ghana, Benin, socio-economic determinants, innovation adoption, meta-analysis</v>
       </c>
     </row>
     <row r="154" xml:space="preserve">
@@ -14209,7 +14209,7 @@
 Offers criteria to guide â€œREDD+ safeguard integrationâ€ at national and regional levels</v>
       </c>
       <c r="T154" t="str">
-        <v>10.3390/su6096125</v>
+        <v>https://doi.org/10.3390/su6096125</v>
       </c>
       <c r="U154" t="str">
         <v>This study examines cross-sectoral policies in Cameroon related to REDD+ (Reducing Emissions from Deforestation and Forest Degradation) strategy from a multi-criteria perspective. The paper develops a GIS-based decision support tool to compare different climate policies and sustainable development strategies in Cameroon. It analyzes how various policy interventions can contribute to optimal REDD+ strategy design while considering multiple environmental, social, and economic criteria. The research provides a framework for integrating spatial analysis with multi-criteria assessment to support evidence-based climate policy decision-making in Sub-Saharan Africa.</v>
@@ -14238,7 +14238,7 @@
         <v>The details of study design are described elaborated by the theoretical basis for the Stepwise approach. The study considered action research and case study research design. It consisted of three main components that helped to shape the Stepwise logic: (a) co-design and co-development, (b) experiential learning, (c) farmers’ feedback, and (d) Hypothesis needed for field testing to ascertain its validity and practicality. The combination of these brought about the idea of breaking down the GAPs packages into smaller packages that could be implemented in phases. The process of development of the approach, tools, experiential learning, farmers’ feedback, assumptions, and data underpinning Stepwise approach.</v>
       </c>
       <c r="T155" t="str">
-        <v>10.1080/14735903.2025.2513790</v>
+        <v>https://doi.org/10.1080/14735903.2025.2513790</v>
       </c>
       <c r="U155" t="str">
         <v>Adoption of Climate-smart Agricultural Practices (CSA) enhances crop productivity and livelihoods. Smallholder coffee farmers in Uganda receive training on good agricultural practices (GAPs) through extension programs, but adoption remains low. Adopting all 'best practices' at once may be unrealistic for resource-limited, risk-averse smallholders. This study tested a Stepwise approach, breaking GAPs into manageable, incremental investments. Field trials were conducted in Luweero (Central) and Sironko (East) districts of Uganda, with 16 demonstration sites using randomized treatments and the control (farmer practice), divided into four steps. Each site served 25–30 farmers through experiential learning. A co-design method ensured farmer involvement in the design, development, and testing for sustainability. Results from two harvests (2018–2019) showed significant cumulative yield gains over the control. Arabica yields increased by 31%, 43%, 54% and 65% across Steps 1-4. Robusta showed gains of 7%, 22%, 23% and 39% respectively. Marginal rate of returns (MRR) was relatively high for Step 1 (563%), 2 (169%) and 4 (122%) for Robusta coffee, and 221%, 217% and 485% for Step 2, 3 and 4 for Arabica coffee respectively. The Stepwise approach demonstrated improved yield gains and increased farmer income.</v>
